--- a/output/yearly_surface_area_iteration_94_growth_param_0.5.xlsx
+++ b/output/yearly_surface_area_iteration_94_growth_param_0.5.xlsx
@@ -735,10 +735,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>10.84497636884631</v>
+        <v>10.84497646883049</v>
       </c>
       <c r="C21" t="n">
-        <v>37.78907206955024</v>
+        <v>37.78907241794284</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.202681995431348</v>
+        <v>5.59890715731956</v>
       </c>
       <c r="C2" t="n">
-        <v>10.11887358767187</v>
+        <v>4.202861921880595</v>
       </c>
       <c r="D2" t="n">
-        <v>29.89716283742811</v>
+        <v>23.99882263031328</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.39518666092173</v>
+        <v>19.44351328260808</v>
       </c>
       <c r="C3" t="n">
-        <v>26.80662106445916</v>
+        <v>10.96612185643687</v>
       </c>
       <c r="D3" t="n">
-        <v>79.09450379264428</v>
+        <v>59.47427592327178</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>35.69732827411827</v>
+        <v>35.65904011365264</v>
       </c>
       <c r="C4" t="n">
-        <v>67.52755234120836</v>
+        <v>32.22586839190155</v>
       </c>
       <c r="D4" t="n">
-        <v>96.28196085089319</v>
+        <v>71.81582631335841</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>44.05592822807562</v>
+        <v>45.99487994396307</v>
       </c>
       <c r="C5" t="n">
-        <v>137.9110087540707</v>
+        <v>64.05903770210439</v>
       </c>
       <c r="D5" t="n">
-        <v>71.61849502480483</v>
+        <v>58.65942532874693</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>41.13719230334986</v>
+        <v>44.71958967614647</v>
       </c>
       <c r="C6" t="n">
-        <v>160.684610249484</v>
+        <v>95.27566945404023</v>
       </c>
       <c r="D6" t="n">
-        <v>49.54978838104078</v>
+        <v>44.63908636439822</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>28.44613973055133</v>
+        <v>30.72183090899544</v>
       </c>
       <c r="C7" t="n">
-        <v>127.6183658227471</v>
+        <v>90.18923459833748</v>
       </c>
       <c r="D7" t="n">
-        <v>39.34550274309942</v>
+        <v>40.00425545264903</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>14.10280577150543</v>
+        <v>15.43798264928109</v>
       </c>
       <c r="C8" t="n">
-        <v>73.76852249710534</v>
+        <v>59.33192250615598</v>
       </c>
       <c r="D8" t="n">
-        <v>36.04977569994287</v>
+        <v>36.46701847424777</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>7.09999939711293</v>
+        <v>7.432811868852599</v>
       </c>
       <c r="C9" t="n">
-        <v>40.93593402397924</v>
+        <v>35.83280945730432</v>
       </c>
       <c r="D9" t="n">
-        <v>33.9468721174462</v>
+        <v>34.39062207976576</v>
       </c>
     </row>
     <row r="10">
@@ -892,13 +892,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>5.267076433284139</v>
+        <v>5.551783267515713</v>
       </c>
       <c r="C10" t="n">
-        <v>30.17892442854695</v>
+        <v>30.03657101143117</v>
       </c>
       <c r="D10" t="n">
-        <v>35.01894061048373</v>
+        <v>35.73070769606267</v>
       </c>
     </row>
     <row r="11">
@@ -906,13 +906,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.442408361716816</v>
+        <v>4.797801030654161</v>
       </c>
       <c r="C11" t="n">
-        <v>29.14219885286231</v>
+        <v>29.67528785626833</v>
       </c>
       <c r="D11" t="n">
-        <v>35.7169632282032</v>
+        <v>35.53926689373453</v>
       </c>
     </row>
     <row r="12">
@@ -920,13 +920,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.688426124855267</v>
+        <v>3.905392367493811</v>
       </c>
       <c r="C12" t="n">
-        <v>27.33774657245668</v>
+        <v>28.42257778564941</v>
       </c>
       <c r="D12" t="n">
-        <v>35.1485313074443</v>
+        <v>35.36549755008285</v>
       </c>
     </row>
     <row r="13">
@@ -937,7 +937,7 @@
         <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
-        <v>24.97566159603886</v>
+        <v>26.27647730416588</v>
       </c>
       <c r="D13" t="n">
         <v>32.26022956155019</v>
@@ -948,13 +948,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>2.151009220004762</v>
       </c>
       <c r="C14" t="n">
-        <v>23.04652735719387</v>
+        <v>23.96838845148163</v>
       </c>
       <c r="D14" t="n">
-        <v>30.42141611149592</v>
+        <v>30.72870314292517</v>
       </c>
     </row>
     <row r="15">
@@ -965,7 +965,7 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>20.78359889890498</v>
+        <v>22.21695054710532</v>
       </c>
       <c r="D15" t="n">
         <v>29.38370878810703</v>
@@ -979,10 +979,10 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>19.01252604044373</v>
+        <v>19.42584182393164</v>
       </c>
       <c r="D16" t="n">
-        <v>26.45221014322606</v>
+        <v>26.86552592671396</v>
       </c>
     </row>
     <row r="17">
@@ -993,7 +993,7 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>17.9443845382232</v>
+        <v>18.41660518396592</v>
       </c>
       <c r="D17" t="n">
         <v>24.55547357862122</v>
@@ -1010,7 +1010,7 @@
         <v>18.1917849596934</v>
       </c>
       <c r="D18" t="n">
-        <v>20.86704745376595</v>
+        <v>21.40209995258047</v>
       </c>
     </row>
     <row r="19">
@@ -1035,7 +1035,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>18.82992096745382</v>
+        <v>19.50241814486288</v>
       </c>
       <c r="D20" t="n">
         <v>10.75995483854504</v>
@@ -1046,13 +1046,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.661304743899239</v>
+        <v>7.726390975287</v>
       </c>
       <c r="C21" t="n">
-        <v>92.89332001977826</v>
+        <v>96.57988719108751</v>
       </c>
       <c r="D21" t="n">
-        <v>7.661304743899239</v>
+        <v>8.692189847197875</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.573782627636643</v>
+        <v>6.956664232292898</v>
       </c>
       <c r="C2" t="n">
-        <v>12.70774228377071</v>
+        <v>8.04542243630261</v>
       </c>
       <c r="D2" t="n">
-        <v>26.38054256081604</v>
+        <v>26.19891923553038</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.30468594568178</v>
+        <v>19.18825887950391</v>
       </c>
       <c r="C3" t="n">
-        <v>32.8100082759284</v>
+        <v>13.91627370769854</v>
       </c>
       <c r="D3" t="n">
-        <v>82.91350236216437</v>
+        <v>64.09339887175302</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>33.06820792214531</v>
+        <v>36.69282044622454</v>
       </c>
       <c r="C4" t="n">
-        <v>66.46824656832605</v>
+        <v>29.62227348023901</v>
       </c>
       <c r="D4" t="n">
-        <v>109.2233590882746</v>
+        <v>83.25122357242527</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>48.44924920458011</v>
+        <v>49.75006491270713</v>
       </c>
       <c r="C5" t="n">
-        <v>131.4069302134356</v>
+        <v>61.67829951930587</v>
       </c>
       <c r="D5" t="n">
-        <v>86.86012813323656</v>
+        <v>70.58765993534568</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>49.02651685467723</v>
+        <v>54.05797383894213</v>
       </c>
       <c r="C6" t="n">
-        <v>185.8821468266826</v>
+        <v>98.01278205348032</v>
       </c>
       <c r="D6" t="n">
-        <v>58.16364273810229</v>
+        <v>52.00513938936205</v>
       </c>
     </row>
     <row r="7">
@@ -1161,10 +1161,10 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>37.42913122440964</v>
+        <v>41.86074036137975</v>
       </c>
       <c r="C7" t="n">
-        <v>175.5875403999505</v>
+        <v>114.8625179014683</v>
       </c>
       <c r="D7" t="n">
         <v>43.95677170994669</v>
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>21.36283004441059</v>
+        <v>24.20008090968387</v>
       </c>
       <c r="C8" t="n">
-        <v>115.8265941470387</v>
+        <v>89.20650514638642</v>
       </c>
       <c r="D8" t="n">
-        <v>37.88564390688441</v>
+        <v>39.05392367493811</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>10.31718662392973</v>
+        <v>11.53749902030851</v>
       </c>
       <c r="C9" t="n">
-        <v>63.78905708343648</v>
+        <v>55.1359328182051</v>
       </c>
       <c r="D9" t="n">
-        <v>35.49999698556465</v>
+        <v>35.72187196672443</v>
       </c>
     </row>
     <row r="10">
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>5.978843518863076</v>
+        <v>6.405903770210439</v>
       </c>
       <c r="C10" t="n">
-        <v>38.29306920414684</v>
+        <v>36.86953503298896</v>
       </c>
       <c r="D10" t="n">
-        <v>35.3036474447153</v>
+        <v>36.58482819875739</v>
       </c>
     </row>
     <row r="11">
@@ -1217,13 +1217,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.620104696185489</v>
+        <v>5.153193699591506</v>
       </c>
       <c r="C11" t="n">
-        <v>32.16303653882975</v>
+        <v>32.51842920776709</v>
       </c>
       <c r="D11" t="n">
-        <v>36.25005223160922</v>
+        <v>35.89465956267188</v>
       </c>
     </row>
     <row r="12">
@@ -1231,13 +1231,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.905392367493811</v>
+        <v>4.122358610132356</v>
       </c>
       <c r="C12" t="n">
-        <v>29.94134148411922</v>
+        <v>31.46010518258904</v>
       </c>
       <c r="D12" t="n">
-        <v>35.36549755008285</v>
+        <v>36.01639627799849</v>
       </c>
     </row>
     <row r="13">
@@ -1245,13 +1245,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.861794557879452</v>
+        <v>3.121957699504857</v>
       </c>
       <c r="C13" t="n">
-        <v>27.3171298706675</v>
+        <v>28.87810872041993</v>
       </c>
       <c r="D13" t="n">
-        <v>33.04071898642641</v>
+        <v>32.780555844801</v>
       </c>
     </row>
     <row r="14">
@@ -1259,13 +1259,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>2.151009220004762</v>
       </c>
       <c r="C14" t="n">
-        <v>24.89024954576939</v>
+        <v>26.42668470291564</v>
       </c>
       <c r="D14" t="n">
-        <v>30.42141611149592</v>
+        <v>31.34327720578367</v>
       </c>
     </row>
     <row r="15">
@@ -1276,10 +1276,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>22.21695054710532</v>
+        <v>24.00864010735575</v>
       </c>
       <c r="D15" t="n">
-        <v>29.38370878810703</v>
+        <v>29.74204670015712</v>
       </c>
     </row>
     <row r="16">
@@ -1290,10 +1290,10 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>20.25247339090745</v>
+        <v>21.07910495788326</v>
       </c>
       <c r="D16" t="n">
-        <v>26.45221014322606</v>
+        <v>26.86552592671396</v>
       </c>
     </row>
     <row r="17">
@@ -1304,7 +1304,7 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>18.41660518396592</v>
+        <v>19.36104647545135</v>
       </c>
       <c r="D17" t="n">
         <v>24.55547357862122</v>
@@ -1321,7 +1321,7 @@
         <v>18.72683745850791</v>
       </c>
       <c r="D18" t="n">
-        <v>20.86704745376595</v>
+        <v>21.40209995258047</v>
       </c>
     </row>
     <row r="19">
@@ -1346,7 +1346,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>18.82992096745382</v>
+        <v>19.50241814486288</v>
       </c>
       <c r="D20" t="n">
         <v>10.75995483854504</v>
@@ -1357,13 +1357,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.833046536318016</v>
+        <v>7.92247379590694</v>
       </c>
       <c r="C21" t="n">
-        <v>100.8504741550944</v>
+        <v>105.9630870202553</v>
       </c>
       <c r="D21" t="n">
-        <v>8.812177353357768</v>
+        <v>9.903092244883675</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7.282604470102839</v>
+        <v>8.146542449840032</v>
       </c>
       <c r="C2" t="n">
-        <v>20.30548776693678</v>
+        <v>7.945284170469436</v>
       </c>
       <c r="D2" t="n">
-        <v>21.8075617544344</v>
+        <v>36.54654003829177</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>19.44351328260808</v>
+        <v>21.05357951757285</v>
       </c>
       <c r="C3" t="n">
-        <v>40.00131020953629</v>
+        <v>22.76672926148353</v>
       </c>
       <c r="D3" t="n">
-        <v>83.48291603062752</v>
+        <v>68.88432766847745</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>32.9022925601276</v>
+        <v>36.1823116400162</v>
       </c>
       <c r="C4" t="n">
-        <v>73.04104744825845</v>
+        <v>32.1492920709703</v>
       </c>
       <c r="D4" t="n">
-        <v>121.2075533140155</v>
+        <v>94.32926466714628</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>48.49833658979244</v>
+        <v>52.0817157102933</v>
       </c>
       <c r="C5" t="n">
-        <v>125.9582304548658</v>
+        <v>57.62859023928778</v>
       </c>
       <c r="D5" t="n">
-        <v>99.91737259971916</v>
+        <v>81.50960314509145</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>55.30577517103983</v>
+        <v>60.86050368166828</v>
       </c>
       <c r="C6" t="n">
-        <v>194.0934846250029</v>
+        <v>98.45555026809564</v>
       </c>
       <c r="D6" t="n">
-        <v>68.70957657712154</v>
+        <v>61.06176196103888</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>45.75337000871835</v>
+        <v>52.22112388429633</v>
       </c>
       <c r="C7" t="n">
-        <v>215.0528163629681</v>
+        <v>127.3189327729519</v>
       </c>
       <c r="D7" t="n">
-        <v>48.44826745687584</v>
+        <v>47.9691745772034</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>29.2069942013426</v>
+        <v>33.88011327355743</v>
       </c>
       <c r="C8" t="n">
-        <v>162.5577848691868</v>
+        <v>119.6652276706437</v>
       </c>
       <c r="D8" t="n">
-        <v>40.05530633326986</v>
+        <v>41.8911745402114</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>14.53281126596553</v>
+        <v>17.41718602104266</v>
       </c>
       <c r="C9" t="n">
-        <v>95.73905437044468</v>
+        <v>80.6515556515797</v>
       </c>
       <c r="D9" t="n">
-        <v>36.94218436310322</v>
+        <v>37.16405934426299</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>7.402377690020952</v>
+        <v>8.541205026947251</v>
       </c>
       <c r="C10" t="n">
-        <v>53.52488483553611</v>
+        <v>50.39310965898878</v>
       </c>
       <c r="D10" t="n">
-        <v>35.73070769606267</v>
+        <v>37.43894870145212</v>
       </c>
     </row>
     <row r="11">
@@ -1528,13 +1528,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.975497365122834</v>
+        <v>5.508586368528851</v>
       </c>
       <c r="C11" t="n">
-        <v>36.96083756948391</v>
+        <v>37.31623023842126</v>
       </c>
       <c r="D11" t="n">
-        <v>36.78314123501524</v>
+        <v>36.25005223160922</v>
       </c>
     </row>
     <row r="12">
@@ -1542,13 +1542,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.905392367493811</v>
+        <v>4.339324852770901</v>
       </c>
       <c r="C12" t="n">
-        <v>32.54493639578176</v>
+        <v>34.49763257952867</v>
       </c>
       <c r="D12" t="n">
-        <v>35.58246379272139</v>
+        <v>36.45032876327558</v>
       </c>
     </row>
     <row r="13">
@@ -1556,13 +1556,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.861794557879452</v>
+        <v>3.382120841130262</v>
       </c>
       <c r="C13" t="n">
-        <v>29.91876128692155</v>
+        <v>31.47974013667398</v>
       </c>
       <c r="D13" t="n">
-        <v>33.56104526967722</v>
+        <v>33.30088212805181</v>
       </c>
     </row>
     <row r="14">
@@ -1570,13 +1570,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>2.151009220004762</v>
       </c>
       <c r="C14" t="n">
-        <v>26.73397173434489</v>
+        <v>28.88498095434966</v>
       </c>
       <c r="D14" t="n">
-        <v>30.42141611149592</v>
+        <v>31.65056423721292</v>
       </c>
     </row>
     <row r="15">
@@ -1587,10 +1587,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>23.65030219530566</v>
+        <v>25.80032966760617</v>
       </c>
       <c r="D15" t="n">
-        <v>29.38370878810703</v>
+        <v>29.74204670015712</v>
       </c>
     </row>
     <row r="16">
@@ -1601,10 +1601,10 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>21.49242074137117</v>
+        <v>22.7323680918349</v>
       </c>
       <c r="D16" t="n">
-        <v>26.45221014322606</v>
+        <v>27.27884171020187</v>
       </c>
     </row>
     <row r="17">
@@ -1615,7 +1615,7 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>19.36104647545135</v>
+        <v>20.30548776693678</v>
       </c>
       <c r="D17" t="n">
         <v>24.55547357862122</v>
@@ -1629,10 +1629,10 @@
         <v>0.5350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>18.72683745850791</v>
+        <v>19.26188995732242</v>
       </c>
       <c r="D18" t="n">
-        <v>20.86704745376595</v>
+        <v>21.40209995258047</v>
       </c>
     </row>
     <row r="19">
@@ -1657,7 +1657,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>18.82992096745382</v>
+        <v>19.50241814486288</v>
       </c>
       <c r="D20" t="n">
         <v>10.75995483854504</v>
@@ -1668,13 +1668,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.988665366298864</v>
+        <v>8.10531604179492</v>
       </c>
       <c r="C21" t="n">
-        <v>107.8469824450347</v>
+        <v>114.4875890903532</v>
       </c>
       <c r="D21" t="n">
-        <v>9.985831707873581</v>
+        <v>11.14480955746801</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.727917017203391</v>
+        <v>7.317947387455725</v>
       </c>
       <c r="C2" t="n">
-        <v>14.13225820263284</v>
+        <v>5.148284961070273</v>
       </c>
       <c r="D2" t="n">
-        <v>18.24676283113122</v>
+        <v>29.04893282095887</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>22.87472150895069</v>
+        <v>25.84450831429728</v>
       </c>
       <c r="C3" t="n">
-        <v>61.09415963527901</v>
+        <v>32.40258297866598</v>
       </c>
       <c r="D3" t="n">
-        <v>90.45332473077987</v>
+        <v>77.51388998880691</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>23.29196428325558</v>
+        <v>25.01493150420873</v>
       </c>
       <c r="C4" t="n">
-        <v>101.4380997935974</v>
+        <v>47.89848874249763</v>
       </c>
       <c r="D4" t="n">
-        <v>115.0303967588945</v>
+        <v>91.86605967719103</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>31.14594591723007</v>
+        <v>34.28753857081986</v>
       </c>
       <c r="C5" t="n">
-        <v>115.9689475641545</v>
+        <v>58.83123117699012</v>
       </c>
       <c r="D5" t="n">
-        <v>67.91239744127311</v>
+        <v>59.96024103687396</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>28.37741739125406</v>
+        <v>32.40258297866598</v>
       </c>
       <c r="C6" t="n">
-        <v>141.6455770210256</v>
+        <v>83.84419918579036</v>
       </c>
       <c r="D6" t="n">
-        <v>31.87931145230244</v>
+        <v>31.55729820530948</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>19.3433750167749</v>
+        <v>22.45747873464579</v>
       </c>
       <c r="C7" t="n">
-        <v>114.3235384118368</v>
+        <v>84.14068699247288</v>
       </c>
       <c r="D7" t="n">
-        <v>28.14670668075605</v>
+        <v>29.40432548989622</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.09727513817844</v>
+        <v>12.10004045484194</v>
       </c>
       <c r="C8" t="n">
-        <v>70.51402885752715</v>
+        <v>59.41537106101696</v>
       </c>
       <c r="D8" t="n">
-        <v>27.20422888467911</v>
+        <v>27.37112599440107</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.324999547834698</v>
+        <v>6.101561981893925</v>
       </c>
       <c r="C9" t="n">
-        <v>40.82499653339935</v>
+        <v>38.38437174064178</v>
       </c>
       <c r="D9" t="n">
-        <v>27.17968519207294</v>
+        <v>28.51093507903161</v>
       </c>
     </row>
     <row r="10">
@@ -1825,13 +1825,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>3.558835427894688</v>
+        <v>3.98589567924205</v>
       </c>
       <c r="C10" t="n">
-        <v>28.89774367450487</v>
+        <v>29.18245050873644</v>
       </c>
       <c r="D10" t="n">
-        <v>28.75539025738908</v>
+        <v>28.32833000604172</v>
       </c>
     </row>
     <row r="11">
@@ -1839,13 +1839,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>2.843141351498762</v>
+        <v>3.198534020436107</v>
       </c>
       <c r="C11" t="n">
-        <v>26.12136116689488</v>
+        <v>27.54293184264426</v>
       </c>
       <c r="D11" t="n">
-        <v>28.43141351498762</v>
+        <v>29.14219885286231</v>
       </c>
     </row>
     <row r="12">
@@ -1853,13 +1853,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2.169662426385451</v>
+        <v>2.603594911662541</v>
       </c>
       <c r="C12" t="n">
-        <v>24.30021917551705</v>
+        <v>25.60201663134832</v>
       </c>
       <c r="D12" t="n">
-        <v>27.33774657245668</v>
+        <v>27.12078032981814</v>
       </c>
     </row>
     <row r="13">
@@ -1867,13 +1867,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>1.300815708127024</v>
+        <v>1.560978849752429</v>
       </c>
       <c r="C13" t="n">
-        <v>22.11386703815941</v>
+        <v>23.93500902953724</v>
       </c>
       <c r="D13" t="n">
-        <v>25.23582473766426</v>
+        <v>26.01631416254048</v>
       </c>
     </row>
     <row r="14">
@@ -1884,10 +1884,10 @@
         <v>0.921861094287755</v>
       </c>
       <c r="C14" t="n">
-        <v>19.66637001147211</v>
+        <v>21.51009220004762</v>
       </c>
       <c r="D14" t="n">
-        <v>24.58296251434014</v>
+        <v>24.89024954576939</v>
       </c>
     </row>
     <row r="15">
@@ -1898,10 +1898,10 @@
         <v>0.7166758241001715</v>
       </c>
       <c r="C15" t="n">
-        <v>17.91689560250429</v>
+        <v>18.99190933865455</v>
       </c>
       <c r="D15" t="n">
-        <v>22.21695054710532</v>
+        <v>22.93362637120549</v>
       </c>
     </row>
     <row r="16">
@@ -1912,7 +1912,7 @@
         <v>0.4133157834879072</v>
       </c>
       <c r="C16" t="n">
-        <v>16.53263133951629</v>
+        <v>17.3592629064921</v>
       </c>
       <c r="D16" t="n">
         <v>20.66578917439536</v>
@@ -1926,10 +1926,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>16.05550195525234</v>
+        <v>16.52772260099505</v>
       </c>
       <c r="D17" t="n">
-        <v>17.9443845382232</v>
+        <v>18.41660518396592</v>
       </c>
     </row>
     <row r="18">
@@ -1954,7 +1954,7 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>16.24890625298896</v>
+        <v>16.85071759569225</v>
       </c>
       <c r="D19" t="n">
         <v>9.027170140549421</v>
@@ -1968,10 +1968,10 @@
         <v>5.37997741927252</v>
       </c>
       <c r="C20" t="n">
-        <v>72.62969516017901</v>
+        <v>75.31968386981528</v>
       </c>
       <c r="D20" t="n">
-        <v>6.724971774090649</v>
+        <v>7.397468951499714</v>
       </c>
     </row>
     <row r="21">
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.101741908343174</v>
+        <v>4.518002934943821</v>
       </c>
       <c r="C2" t="n">
-        <v>6.760314691443536</v>
+        <v>2.492657421082652</v>
       </c>
       <c r="D2" t="n">
-        <v>13.14952875068178</v>
+        <v>21.27152750791564</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>23.55212742488098</v>
+        <v>26.45810062945154</v>
       </c>
       <c r="C3" t="n">
-        <v>59.34664872171968</v>
+        <v>26.25684235008094</v>
       </c>
       <c r="D3" t="n">
-        <v>86.21708338695488</v>
+        <v>82.67788291314514</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>31.79193590662446</v>
+        <v>36.52690508420682</v>
       </c>
       <c r="C4" t="n">
-        <v>129.1204398102448</v>
+        <v>66.87665361329272</v>
       </c>
       <c r="D4" t="n">
-        <v>131.034847833526</v>
+        <v>108.7256130022215</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>34.48388811166922</v>
+        <v>38.06726723217008</v>
       </c>
       <c r="C5" t="n">
-        <v>150.2564861349744</v>
+        <v>75.12824306748718</v>
       </c>
       <c r="D5" t="n">
-        <v>84.79845795431825</v>
+        <v>74.95643721924398</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>33.2881194078966</v>
+        <v>39.20511282139213</v>
       </c>
       <c r="C6" t="n">
-        <v>164.7902791486441</v>
+        <v>92.78006678984484</v>
       </c>
       <c r="D6" t="n">
-        <v>39.28561613314037</v>
+        <v>39.1246095096439</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>18.02586959767568</v>
+        <v>21.79872602509618</v>
       </c>
       <c r="C7" t="n">
-        <v>148.8781123582118</v>
+        <v>103.8433816690021</v>
       </c>
       <c r="D7" t="n">
-        <v>30.66194429903638</v>
+        <v>31.9794497181356</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.428304040958867</v>
+        <v>10.18072369303942</v>
       </c>
       <c r="C8" t="n">
-        <v>93.79617566374026</v>
+        <v>79.10923000820797</v>
       </c>
       <c r="D8" t="n">
-        <v>27.95526587842792</v>
+        <v>29.12354564648163</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4.326562132615692</v>
+        <v>4.992187076095029</v>
       </c>
       <c r="C9" t="n">
-        <v>44.5968712131156</v>
+        <v>46.14999608123405</v>
       </c>
       <c r="D9" t="n">
-        <v>28.39999758845172</v>
+        <v>29.39843500367073</v>
       </c>
     </row>
     <row r="10">
@@ -2136,13 +2136,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.992947839621025</v>
+        <v>2.420008090968388</v>
       </c>
       <c r="C10" t="n">
-        <v>31.46010518258904</v>
+        <v>32.31422568528377</v>
       </c>
       <c r="D10" t="n">
-        <v>29.60951076008381</v>
+        <v>29.89421759431538</v>
       </c>
     </row>
     <row r="11">
@@ -2150,13 +2150,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>1.599267010218054</v>
+        <v>1.954659679155399</v>
       </c>
       <c r="C11" t="n">
-        <v>28.96450251839364</v>
+        <v>30.91916219754903</v>
       </c>
       <c r="D11" t="n">
-        <v>29.67528785626833</v>
+        <v>30.03068052520567</v>
       </c>
     </row>
     <row r="12">
@@ -2164,13 +2164,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>0.8678649705541803</v>
+        <v>1.084831213192725</v>
       </c>
       <c r="C12" t="n">
-        <v>20.17786056538469</v>
+        <v>22.56448923440869</v>
       </c>
       <c r="D12" t="n">
-        <v>28.20561154301086</v>
+        <v>28.8565102709265</v>
       </c>
     </row>
     <row r="13">
@@ -2181,10 +2181,10 @@
         <v>0.5203262832508095</v>
       </c>
       <c r="C13" t="n">
-        <v>16.1301147807751</v>
+        <v>17.69109363052753</v>
       </c>
       <c r="D13" t="n">
-        <v>25.75615102091507</v>
+        <v>26.27647730416588</v>
       </c>
     </row>
     <row r="14">
@@ -2195,10 +2195,10 @@
         <v>0.3072870314292517</v>
       </c>
       <c r="C14" t="n">
-        <v>15.05706454003333</v>
+        <v>15.67163860289184</v>
       </c>
       <c r="D14" t="n">
-        <v>18.4372218857551</v>
+        <v>19.0517959486136</v>
       </c>
     </row>
     <row r="15">
@@ -2209,7 +2209,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>13.97517856995334</v>
+        <v>14.69185439405351</v>
       </c>
       <c r="D15" t="n">
         <v>17.5585576904542</v>
@@ -2223,10 +2223,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>13.63942085510094</v>
+        <v>14.05273663858884</v>
       </c>
       <c r="D16" t="n">
-        <v>15.29268398905256</v>
+        <v>15.70599977254047</v>
       </c>
     </row>
     <row r="17">
@@ -2251,7 +2251,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>13.9113649691773</v>
+        <v>14.44641746799181</v>
       </c>
       <c r="D18" t="n">
         <v>7.490734983403163</v>
@@ -2265,10 +2265,10 @@
         <v>4.212679398923063</v>
       </c>
       <c r="C19" t="n">
-        <v>63.19019098384595</v>
+        <v>65.59743635465912</v>
       </c>
       <c r="D19" t="n">
-        <v>5.416302084329653</v>
+        <v>6.018113427032947</v>
       </c>
     </row>
     <row r="20">
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.084070449666731</v>
+        <v>4.603414985213294</v>
       </c>
       <c r="C2" t="n">
-        <v>15.11891464540088</v>
+        <v>8.463646958311752</v>
       </c>
       <c r="D2" t="n">
-        <v>11.80846138668064</v>
+        <v>20.03354365286041</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.76610736667778</v>
+        <v>20.70996782108647</v>
       </c>
       <c r="C3" t="n">
-        <v>42.57348919466293</v>
+        <v>16.92533042121501</v>
       </c>
       <c r="D3" t="n">
-        <v>77.63660845183777</v>
+        <v>81.24944000346602</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>37.93080430127976</v>
+        <v>44.4142661401257</v>
       </c>
       <c r="C4" t="n">
-        <v>138.2713101615293</v>
+        <v>66.21299216522188</v>
       </c>
       <c r="D4" t="n">
-        <v>142.2405161297991</v>
+        <v>122.7263170124853</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>40.30074325933157</v>
+        <v>46.58392856651115</v>
       </c>
       <c r="C5" t="n">
-        <v>191.3671712503095</v>
+        <v>101.488168926514</v>
       </c>
       <c r="D5" t="n">
-        <v>107.8940726967245</v>
+        <v>95.84311962709488</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>38.96360288614742</v>
+        <v>46.00764266411829</v>
       </c>
       <c r="C6" t="n">
-        <v>200.0909813502467</v>
+        <v>107.3109145604019</v>
       </c>
       <c r="D6" t="n">
-        <v>53.13218575383738</v>
+        <v>52.24664932460676</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>26.29022177202533</v>
+        <v>32.5184292077671</v>
       </c>
       <c r="C7" t="n">
-        <v>188.4032749311884</v>
+        <v>119.5336734782746</v>
       </c>
       <c r="D7" t="n">
-        <v>34.13536767666159</v>
+        <v>36.05173919535137</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>12.18348900970292</v>
+        <v>15.77177686872501</v>
       </c>
       <c r="C8" t="n">
-        <v>139.1921895081128</v>
+        <v>108.7334669838555</v>
       </c>
       <c r="D8" t="n">
-        <v>29.79113408536946</v>
+        <v>30.87596529856218</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.657812019574366</v>
+        <v>6.878124415953151</v>
       </c>
       <c r="C9" t="n">
-        <v>74.43905617910588</v>
+        <v>71.22186895228909</v>
       </c>
       <c r="D9" t="n">
-        <v>28.95468504135117</v>
+        <v>30.17499743772996</v>
       </c>
     </row>
     <row r="10">
@@ -2447,13 +2447,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2.420008090968388</v>
+        <v>3.131775176547325</v>
       </c>
       <c r="C10" t="n">
-        <v>40.00131020953629</v>
+        <v>42.84837855185204</v>
       </c>
       <c r="D10" t="n">
-        <v>30.17892442854695</v>
+        <v>30.7483380970101</v>
       </c>
     </row>
     <row r="11">
@@ -2461,13 +2461,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>1.599267010218054</v>
+        <v>1.954659679155399</v>
       </c>
       <c r="C11" t="n">
-        <v>32.51842920776709</v>
+        <v>34.65078522139116</v>
       </c>
       <c r="D11" t="n">
-        <v>29.852984190737</v>
+        <v>30.56376952861169</v>
       </c>
     </row>
     <row r="12">
@@ -2475,13 +2475,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>0.8678649705541803</v>
+        <v>1.084831213192725</v>
       </c>
       <c r="C12" t="n">
-        <v>24.5171854181556</v>
+        <v>27.55471281509523</v>
       </c>
       <c r="D12" t="n">
-        <v>28.8565102709265</v>
+        <v>29.29044275620359</v>
       </c>
     </row>
     <row r="13">
@@ -2492,10 +2492,10 @@
         <v>0.2601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>18.21141991377833</v>
+        <v>20.55288818840698</v>
       </c>
       <c r="D13" t="n">
-        <v>26.01631416254048</v>
+        <v>26.79680358741669</v>
       </c>
     </row>
     <row r="14">
@@ -2506,10 +2506,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>15.97892563432109</v>
+        <v>17.20807376003809</v>
       </c>
       <c r="D14" t="n">
-        <v>19.0517959486136</v>
+        <v>19.97365704290136</v>
       </c>
     </row>
     <row r="15">
@@ -2520,10 +2520,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>15.76686813020377</v>
+        <v>16.12520604225386</v>
       </c>
       <c r="D15" t="n">
-        <v>17.20021977840412</v>
+        <v>17.5585576904542</v>
       </c>
     </row>
     <row r="16">
@@ -2534,10 +2534,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>14.46605242207675</v>
+        <v>15.70599977254047</v>
       </c>
       <c r="D16" t="n">
-        <v>14.87936820556466</v>
+        <v>15.29268398905256</v>
       </c>
     </row>
     <row r="17">
@@ -2562,7 +2562,7 @@
         <v>3.21031499288707</v>
       </c>
       <c r="C18" t="n">
-        <v>34.77841242294325</v>
+        <v>34.24335992412875</v>
       </c>
       <c r="D18" t="n">
         <v>6.955682484588652</v>
@@ -2576,10 +2576,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>33.09962384868121</v>
+        <v>36.71049190490098</v>
       </c>
       <c r="D19" t="n">
-        <v>3.610868056219768</v>
+        <v>4.212679398923063</v>
       </c>
     </row>
     <row r="20">
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.473022466997715</v>
+        <v>2.66839026014283</v>
       </c>
       <c r="C2" t="n">
-        <v>7.305184667300516</v>
+        <v>3.698243601897735</v>
       </c>
       <c r="D2" t="n">
-        <v>8.255516445011429</v>
+        <v>13.68850824031328</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.47649179392497</v>
+        <v>20.53325323432204</v>
       </c>
       <c r="C3" t="n">
-        <v>51.97863220134738</v>
+        <v>25.64325003492669</v>
       </c>
       <c r="D3" t="n">
-        <v>73.95996329943345</v>
+        <v>81.43597206727293</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>41.555416825359</v>
+        <v>49.44277788127786</v>
       </c>
       <c r="C4" t="n">
-        <v>140.1857181848106</v>
+        <v>63.08612572719579</v>
       </c>
       <c r="D4" t="n">
-        <v>150.9702167159618</v>
+        <v>134.2255278723281</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>41.77336481570179</v>
+        <v>49.45554060143309</v>
       </c>
       <c r="C5" t="n">
-        <v>238.8101290580367</v>
+        <v>121.7121716339983</v>
       </c>
       <c r="D5" t="n">
-        <v>113.1709666070511</v>
+        <v>106.4459948329604</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>31.43654323768712</v>
+        <v>40.17115256237099</v>
       </c>
       <c r="C6" t="n">
-        <v>231.608027899682</v>
+        <v>140.2367690654314</v>
       </c>
       <c r="D6" t="n">
-        <v>51.44161620712438</v>
+        <v>51.52211951887262</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>8.024805734513427</v>
+        <v>10.42027013287564</v>
       </c>
       <c r="C7" t="n">
-        <v>191.3377188191821</v>
+        <v>132.8285008891849</v>
       </c>
       <c r="D7" t="n">
-        <v>34.2551408965797</v>
+        <v>36.53083207502382</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>3.922082078466008</v>
+        <v>4.756567627075796</v>
       </c>
       <c r="C8" t="n">
-        <v>94.38031554776711</v>
+        <v>89.79064503041327</v>
       </c>
       <c r="D8" t="n">
-        <v>31.2097595180061</v>
+        <v>32.54493639578176</v>
       </c>
     </row>
     <row r="9">
@@ -2744,13 +2744,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.664062358698343</v>
+        <v>2.218749811597791</v>
       </c>
       <c r="C9" t="n">
-        <v>30.50780990946962</v>
+        <v>32.61562223048752</v>
       </c>
       <c r="D9" t="n">
-        <v>31.50624732468863</v>
+        <v>32.61562223048752</v>
       </c>
     </row>
     <row r="10">
@@ -2758,13 +2758,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.1388273369263</v>
+        <v>1.423534171157875</v>
       </c>
       <c r="C10" t="n">
-        <v>25.48126166372597</v>
+        <v>27.18950266911542</v>
       </c>
       <c r="D10" t="n">
-        <v>23.34596040698915</v>
+        <v>23.91537407545231</v>
       </c>
     </row>
     <row r="11">
@@ -2772,13 +2772,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>0.5330890034060179</v>
+        <v>0.7107853378746906</v>
       </c>
       <c r="C11" t="n">
-        <v>19.54659679155399</v>
+        <v>22.0343454741154</v>
       </c>
       <c r="D11" t="n">
-        <v>23.10052348092744</v>
+        <v>23.45591614986479</v>
       </c>
     </row>
     <row r="12">
@@ -2789,10 +2789,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>14.75370449942107</v>
+        <v>16.70640068316797</v>
       </c>
       <c r="D12" t="n">
-        <v>21.26269177857742</v>
+        <v>21.69662426385451</v>
       </c>
     </row>
     <row r="13">
@@ -2803,10 +2803,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>13.00815708127024</v>
+        <v>14.04880964777186</v>
       </c>
       <c r="D13" t="n">
-        <v>15.60978849752428</v>
+        <v>16.3902779224005</v>
       </c>
     </row>
     <row r="14">
@@ -2817,10 +2817,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>13.21334235145782</v>
+        <v>13.52062938288707</v>
       </c>
       <c r="D14" t="n">
-        <v>14.44249047717483</v>
+        <v>14.74977750860408</v>
       </c>
     </row>
     <row r="15">
@@ -2831,10 +2831,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>12.18348900970292</v>
+        <v>13.25850274585317</v>
       </c>
       <c r="D15" t="n">
-        <v>12.541826921753</v>
+        <v>12.90016483380309</v>
       </c>
     </row>
     <row r="16">
@@ -2859,7 +2859,7 @@
         <v>2.361103228713579</v>
       </c>
       <c r="C17" t="n">
-        <v>29.7499006817911</v>
+        <v>29.27768003604838</v>
       </c>
       <c r="D17" t="n">
         <v>5.66664774891259</v>
@@ -2873,10 +2873,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>28.35778243716912</v>
+        <v>31.56809743005619</v>
       </c>
       <c r="D18" t="n">
-        <v>2.675262494072558</v>
+        <v>3.21031499288707</v>
       </c>
     </row>
     <row r="19">
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.68998870963626</v>
+        <v>4.226423866782518</v>
       </c>
       <c r="C2" t="n">
-        <v>11.0191362324662</v>
+        <v>7.220754364735291</v>
       </c>
       <c r="D2" t="n">
-        <v>6.983171420307562</v>
+        <v>12.80297181108265</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>13.77392029058275</v>
+        <v>14.83911654969054</v>
       </c>
       <c r="C3" t="n">
-        <v>40.47254910757476</v>
+        <v>19.55641426859646</v>
       </c>
       <c r="D3" t="n">
-        <v>64.92297568184158</v>
+        <v>73.95996329943345</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>38.50512670826415</v>
+        <v>44.79714774478195</v>
       </c>
       <c r="C4" t="n">
-        <v>136.3313766979376</v>
+        <v>64.19648238069892</v>
       </c>
       <c r="D4" t="n">
-        <v>152.7187093772253</v>
+        <v>143.5295508654752</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>50.16730768701202</v>
+        <v>61.28560043760715</v>
       </c>
       <c r="C5" t="n">
-        <v>249.1184799526282</v>
+        <v>120.1413753072034</v>
       </c>
       <c r="D5" t="n">
-        <v>136.3156687346697</v>
+        <v>128.9771046454247</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>40.77492740048278</v>
+        <v>52.20639766873265</v>
       </c>
       <c r="C6" t="n">
-        <v>294.8433792779234</v>
+        <v>167.0041202217207</v>
       </c>
       <c r="D6" t="n">
-        <v>67.50202690089796</v>
+        <v>68.54856995362505</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>16.70836417857646</v>
+        <v>23.83487076370406</v>
       </c>
       <c r="C7" t="n">
-        <v>250.2062564089336</v>
+        <v>168.0418275451095</v>
       </c>
       <c r="D7" t="n">
-        <v>39.16584291322225</v>
+        <v>41.98051358129786</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5.17381040138069</v>
+        <v>6.759332943739289</v>
       </c>
       <c r="C8" t="n">
-        <v>155.2143120414207</v>
+        <v>128.8445687053514</v>
       </c>
       <c r="D8" t="n">
-        <v>32.46148784092078</v>
+        <v>34.63115026730623</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.996874830438012</v>
+        <v>2.884374755077128</v>
       </c>
       <c r="C9" t="n">
-        <v>60.23905738488002</v>
+        <v>64.12186955517615</v>
       </c>
       <c r="D9" t="n">
-        <v>32.61562223048752</v>
+        <v>33.61405964570653</v>
       </c>
     </row>
     <row r="10">
@@ -3069,13 +3069,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.1388273369263</v>
+        <v>1.565887588273662</v>
       </c>
       <c r="C10" t="n">
-        <v>29.89421759431538</v>
+        <v>32.59893251951534</v>
       </c>
       <c r="D10" t="n">
-        <v>24.20008090968388</v>
+        <v>25.19655482949439</v>
       </c>
     </row>
     <row r="11">
@@ -3083,13 +3083,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>0.3553926689373453</v>
+        <v>0.5330890034060179</v>
       </c>
       <c r="C11" t="n">
-        <v>22.7451308119901</v>
+        <v>25.9436648324262</v>
       </c>
       <c r="D11" t="n">
-        <v>23.98900515327081</v>
+        <v>24.34439782220815</v>
       </c>
     </row>
     <row r="12">
@@ -3100,10 +3100,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>16.92336692580652</v>
+        <v>19.30999559483051</v>
       </c>
       <c r="D12" t="n">
-        <v>21.26269177857742</v>
+        <v>22.34752299177014</v>
       </c>
     </row>
     <row r="13">
@@ -3114,10 +3114,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>14.82929907264807</v>
+        <v>16.65044106402591</v>
       </c>
       <c r="D13" t="n">
-        <v>15.60978849752428</v>
+        <v>16.3902779224005</v>
       </c>
     </row>
     <row r="14">
@@ -3128,10 +3128,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>13.82791641431633</v>
+        <v>14.44249047717483</v>
       </c>
       <c r="D14" t="n">
-        <v>14.13520344574558</v>
+        <v>14.74977750860408</v>
       </c>
     </row>
     <row r="15">
@@ -3142,10 +3142,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>13.25850274585317</v>
+        <v>13.97517856995334</v>
       </c>
       <c r="D15" t="n">
-        <v>11.82515109765283</v>
+        <v>12.18348900970292</v>
       </c>
     </row>
     <row r="16">
@@ -3156,7 +3156,7 @@
         <v>1.653263133951629</v>
       </c>
       <c r="C16" t="n">
-        <v>23.97231544229862</v>
+        <v>23.1456838753228</v>
       </c>
       <c r="D16" t="n">
         <v>8.266315669758143</v>
@@ -3170,10 +3170,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>33.0554452019901</v>
+        <v>35.41654843070368</v>
       </c>
       <c r="D17" t="n">
-        <v>4.249985811684442</v>
+        <v>4.722206457427158</v>
       </c>
     </row>
     <row r="18">
@@ -3184,7 +3184,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>0.5350524988145117</v>
+        <v>1.605157496443535</v>
       </c>
       <c r="D18" t="n">
         <v>1.070104997629023</v>
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1.936988220478957</v>
+        <v>3.021819433671682</v>
       </c>
       <c r="C2" t="n">
-        <v>5.936628367580462</v>
+        <v>4.643666641087413</v>
       </c>
       <c r="D2" t="n">
-        <v>6.231152678854506</v>
+        <v>9.156760837509999</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>11.99695694589602</v>
+        <v>14.93729132011522</v>
       </c>
       <c r="C3" t="n">
-        <v>42.21024254409161</v>
+        <v>24.28843820306609</v>
       </c>
       <c r="D3" t="n">
-        <v>58.13419030697487</v>
+        <v>68.54071597199106</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>34.77841242294325</v>
+        <v>39.41127983928396</v>
       </c>
       <c r="C4" t="n">
-        <v>124.4620469535936</v>
+        <v>58.19800390775092</v>
       </c>
       <c r="D4" t="n">
-        <v>151.5445391229461</v>
+        <v>147.5625704345211</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>54.3151917374548</v>
+        <v>66.63612542575227</v>
       </c>
       <c r="C5" t="n">
-        <v>257.880578213031</v>
+        <v>123.5774922720673</v>
       </c>
       <c r="D5" t="n">
-        <v>151.3854959948582</v>
+        <v>145.8631651584699</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>46.28940425523712</v>
+        <v>61.90704673439538</v>
       </c>
       <c r="C6" t="n">
-        <v>339.0799490835804</v>
+        <v>184.2720805917178</v>
       </c>
       <c r="D6" t="n">
-        <v>79.98004022187492</v>
+        <v>82.75740447718914</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>14.85187926984575</v>
+        <v>24.852943133008</v>
       </c>
       <c r="C7" t="n">
-        <v>307.877061799504</v>
+        <v>202.3568550516483</v>
       </c>
       <c r="D7" t="n">
-        <v>44.19631814978291</v>
+        <v>47.78951474732623</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.088979188187965</v>
+        <v>5.674501730546564</v>
       </c>
       <c r="C8" t="n">
-        <v>196.5213466976053</v>
+        <v>162.4743363143259</v>
       </c>
       <c r="D8" t="n">
-        <v>32.87873061522568</v>
+        <v>36.38356991938679</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.553124868118454</v>
+        <v>2.218749811597791</v>
       </c>
       <c r="C9" t="n">
-        <v>64.34374453633593</v>
+        <v>80.31874317984003</v>
       </c>
       <c r="D9" t="n">
-        <v>32.17187226816797</v>
+        <v>33.50312215512664</v>
       </c>
     </row>
     <row r="10">
@@ -3380,13 +3380,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.4270602513473625</v>
+        <v>0.5694136684631501</v>
       </c>
       <c r="C10" t="n">
-        <v>30.60598467989432</v>
+        <v>34.16482010778901</v>
       </c>
       <c r="D10" t="n">
-        <v>24.76949457814703</v>
+        <v>25.76596849795754</v>
       </c>
     </row>
     <row r="11">
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>22.0343454741154</v>
+        <v>25.9436648324262</v>
       </c>
       <c r="D11" t="n">
-        <v>23.98900515327081</v>
+        <v>24.87748682561417</v>
       </c>
     </row>
     <row r="12">
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>16.05550195525234</v>
+        <v>19.09302935219197</v>
       </c>
       <c r="D12" t="n">
-        <v>19.7439280801076</v>
+        <v>20.82875929330033</v>
       </c>
     </row>
     <row r="13">
@@ -3425,10 +3425,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>11.44717823151781</v>
+        <v>11.96750451476862</v>
       </c>
       <c r="D13" t="n">
-        <v>15.86995163914969</v>
+        <v>16.91060420565131</v>
       </c>
     </row>
     <row r="14">
@@ -3439,10 +3439,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>11.06233313145306</v>
+        <v>11.67690719431156</v>
       </c>
       <c r="D14" t="n">
-        <v>11.06233313145306</v>
+        <v>11.67690719431156</v>
       </c>
     </row>
     <row r="15">
@@ -3453,7 +3453,7 @@
         <v>1.075013736150257</v>
       </c>
       <c r="C15" t="n">
-        <v>20.0669230748048</v>
+        <v>19.35024725070463</v>
       </c>
       <c r="D15" t="n">
         <v>6.808420328951629</v>
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>28.10547327717769</v>
+        <v>30.17205219461722</v>
       </c>
       <c r="D16" t="n">
-        <v>3.306526267903257</v>
+        <v>3.719842051391165</v>
       </c>
     </row>
     <row r="17">
@@ -3481,7 +3481,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>0</v>
+        <v>0.9444412914854317</v>
       </c>
       <c r="D17" t="n">
         <v>0.4722206457427158</v>
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.381719930502762</v>
+        <v>4.746750150033328</v>
       </c>
       <c r="C2" t="n">
-        <v>6.409830761027425</v>
+        <v>3.749294482518569</v>
       </c>
       <c r="D2" t="n">
-        <v>6.88205140677014</v>
+        <v>13.37336722725005</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>9.478774084502955</v>
+        <v>12.59582304548658</v>
       </c>
       <c r="C3" t="n">
-        <v>33.63958508601696</v>
+        <v>21.22538536581604</v>
       </c>
       <c r="D3" t="n">
-        <v>51.48284961070274</v>
+        <v>61.12852080492765</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>29.21386643527233</v>
+        <v>34.05093737409637</v>
       </c>
       <c r="C4" t="n">
-        <v>116.0769398116216</v>
+        <v>59.25730968063323</v>
       </c>
       <c r="D4" t="n">
-        <v>146.8733835461398</v>
+        <v>147.7795366771596</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>53.77523050011905</v>
+        <v>64.52536786162162</v>
       </c>
       <c r="C5" t="n">
-        <v>245.5596445247335</v>
+        <v>115.8462291011237</v>
       </c>
       <c r="D5" t="n">
-        <v>164.2463909204914</v>
+        <v>159.8776136365931</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>54.66174867705392</v>
+        <v>73.78128521726055</v>
       </c>
       <c r="C6" t="n">
-        <v>366.2095651427368</v>
+        <v>190.3098289728357</v>
       </c>
       <c r="D6" t="n">
-        <v>98.33479530047329</v>
+        <v>104.1712854022206</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>27.06874770149305</v>
+        <v>42.87881273068369</v>
       </c>
       <c r="C7" t="n">
-        <v>375.1896113934823</v>
+        <v>233.7973252801524</v>
       </c>
       <c r="D7" t="n">
-        <v>51.3228247349105</v>
+        <v>57.61091878061132</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>7.42692138262712</v>
+        <v>12.93452600345173</v>
       </c>
       <c r="C8" t="n">
-        <v>273.5443628342888</v>
+        <v>208.0372472684203</v>
       </c>
       <c r="D8" t="n">
-        <v>35.63253292563798</v>
+        <v>39.80496066868692</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.107812321017901</v>
+        <v>3.217187226816797</v>
       </c>
       <c r="C9" t="n">
-        <v>122.1421771284584</v>
+        <v>130.2406139407903</v>
       </c>
       <c r="D9" t="n">
-        <v>33.28124717396686</v>
+        <v>35.16718451382499</v>
       </c>
     </row>
     <row r="10">
@@ -3691,13 +3691,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.5694136684631501</v>
+        <v>0.8541205026947251</v>
       </c>
       <c r="C10" t="n">
-        <v>45.12603322570465</v>
+        <v>57.65313393189394</v>
       </c>
       <c r="D10" t="n">
-        <v>25.76596849795754</v>
+        <v>27.18950266911542</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>26.29905750136355</v>
+        <v>31.09685853201771</v>
       </c>
       <c r="D11" t="n">
-        <v>24.34439782220815</v>
+        <v>25.41057582902019</v>
       </c>
     </row>
     <row r="12">
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>18.44213062427633</v>
+        <v>22.78145547704723</v>
       </c>
       <c r="D12" t="n">
-        <v>19.96089432274615</v>
+        <v>21.26269177857742</v>
       </c>
     </row>
     <row r="13">
@@ -3736,10 +3736,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>12.74799393964483</v>
+        <v>14.56913593102267</v>
       </c>
       <c r="D13" t="n">
-        <v>16.1301147807751</v>
+        <v>17.43093048890212</v>
       </c>
     </row>
     <row r="14">
@@ -3750,10 +3750,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>11.67690719431156</v>
+        <v>12.29148125717007</v>
       </c>
       <c r="D14" t="n">
-        <v>11.06233313145306</v>
+        <v>11.98419422574081</v>
       </c>
     </row>
     <row r="15">
@@ -3764,10 +3764,10 @@
         <v>0.7166758241001715</v>
       </c>
       <c r="C15" t="n">
-        <v>21.50027472300514</v>
+        <v>19.35024725070463</v>
       </c>
       <c r="D15" t="n">
-        <v>6.450082416901544</v>
+        <v>6.808420328951629</v>
       </c>
     </row>
     <row r="16">
@@ -3778,10 +3778,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>26.03889435973815</v>
+        <v>30.58536797810513</v>
       </c>
       <c r="D16" t="n">
-        <v>2.89321048441535</v>
+        <v>3.306526267903257</v>
       </c>
     </row>
     <row r="17">
@@ -3792,7 +3792,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>0</v>
+        <v>0.4722206457427158</v>
       </c>
       <c r="D17" t="n">
         <v>0</v>
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.827253461781567</v>
+        <v>4.397247967321463</v>
       </c>
       <c r="C2" t="n">
-        <v>6.824128292219578</v>
+        <v>3.91815508764902</v>
       </c>
       <c r="D2" t="n">
-        <v>8.138688468206057</v>
+        <v>9.683959354690538</v>
       </c>
     </row>
     <row r="3">
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1.760273633714531</v>
+        <v>3.285909566114074</v>
       </c>
       <c r="C2" t="n">
-        <v>3.845505757534756</v>
+        <v>2.008655802888974</v>
       </c>
       <c r="D2" t="n">
-        <v>5.174792149084937</v>
+        <v>9.735991983015619</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>12.66454538478385</v>
+        <v>17.18058482431918</v>
       </c>
       <c r="C3" t="n">
-        <v>37.29659528433633</v>
+        <v>22.26603793231766</v>
       </c>
       <c r="D3" t="n">
-        <v>55.40984042768997</v>
+        <v>66.76866136582558</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>40.76412817573606</v>
+        <v>48.28137034715389</v>
       </c>
       <c r="C4" t="n">
-        <v>159.2021712160713</v>
+        <v>81.59206995224817</v>
       </c>
       <c r="D4" t="n">
-        <v>151.0340303167378</v>
+        <v>151.7104544849638</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>30.77779052813751</v>
+        <v>45.13585070274711</v>
       </c>
       <c r="C5" t="n">
-        <v>332.4934037357885</v>
+        <v>165.3754007803752</v>
       </c>
       <c r="D5" t="n">
-        <v>146.6485633218673</v>
+        <v>148.6611461155733</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>16.78494049950772</v>
+        <v>26.60634453279281</v>
       </c>
       <c r="C6" t="n">
-        <v>308.1264257163827</v>
+        <v>198.7224250505267</v>
       </c>
       <c r="D6" t="n">
-        <v>76.96116603131597</v>
+        <v>84.68948395914687</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>4.910702016642545</v>
+        <v>8.563785224144926</v>
       </c>
       <c r="C7" t="n">
-        <v>192.3557911884861</v>
+        <v>146.3029881299724</v>
       </c>
       <c r="D7" t="n">
-        <v>31.08115056874977</v>
+        <v>35.87207936547421</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.418625432636641</v>
+        <v>2.169662426385451</v>
       </c>
       <c r="C8" t="n">
-        <v>89.95754214013523</v>
+        <v>95.9658380901257</v>
       </c>
       <c r="D8" t="n">
-        <v>24.53387512912779</v>
+        <v>25.86905200690345</v>
       </c>
     </row>
     <row r="9">
@@ -4299,13 +4299,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>0.3328124717396686</v>
+        <v>0.5546874528994477</v>
       </c>
       <c r="C9" t="n">
-        <v>34.39062207976576</v>
+        <v>43.93124626963626</v>
       </c>
       <c r="D9" t="n">
-        <v>19.63593583264045</v>
+        <v>20.74531073843935</v>
       </c>
     </row>
     <row r="10">
@@ -4316,10 +4316,10 @@
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>20.64124548178919</v>
+        <v>24.34243432679967</v>
       </c>
       <c r="D10" t="n">
-        <v>19.07535789351553</v>
+        <v>19.92947839621025</v>
       </c>
     </row>
     <row r="11">
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>14.74879576089983</v>
+        <v>18.12502611580461</v>
       </c>
       <c r="D11" t="n">
-        <v>15.99267010218054</v>
+        <v>17.05884810899257</v>
       </c>
     </row>
     <row r="12">
@@ -4344,10 +4344,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>10.41437964665016</v>
+        <v>11.71617710248143</v>
       </c>
       <c r="D12" t="n">
-        <v>13.0179745583127</v>
+        <v>14.10280577150543</v>
       </c>
     </row>
     <row r="13">
@@ -4358,10 +4358,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>9.626036240139976</v>
+        <v>10.14636252339079</v>
       </c>
       <c r="D13" t="n">
-        <v>9.105709956889166</v>
+        <v>9.886199381765381</v>
       </c>
     </row>
     <row r="14">
@@ -4372,10 +4372,10 @@
         <v>0.3072870314292517</v>
       </c>
       <c r="C14" t="n">
-        <v>17.8226478228966</v>
+        <v>15.97892563432109</v>
       </c>
       <c r="D14" t="n">
-        <v>5.223879534297279</v>
+        <v>5.53116656572653</v>
       </c>
     </row>
     <row r="15">
@@ -4386,10 +4386,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>21.85861263505523</v>
+        <v>25.80032966760617</v>
       </c>
       <c r="D15" t="n">
-        <v>2.150027472300515</v>
+        <v>2.5083653843506</v>
       </c>
     </row>
     <row r="16">
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7.390596717569988</v>
+        <v>7.107853378746906</v>
       </c>
       <c r="C2" t="n">
-        <v>7.062692984351554</v>
+        <v>5.684319207589032</v>
       </c>
       <c r="D2" t="n">
-        <v>28.7622624913188</v>
+        <v>14.7124710958427</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>10.25926350937917</v>
+        <v>9.346238144429634</v>
       </c>
       <c r="C3" t="n">
-        <v>17.19531103988288</v>
+        <v>10.02855279888117</v>
       </c>
       <c r="D3" t="n">
-        <v>9.974556675147594</v>
+        <v>11.27046364475338</v>
       </c>
     </row>
     <row r="4">
@@ -4778,13 +4778,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>13.3986048872793</v>
+        <v>13.39891285973927</v>
       </c>
       <c r="C21" t="n">
-        <v>70.14563735105048</v>
+        <v>70.14724967745852</v>
       </c>
       <c r="D21" t="n">
-        <v>1.576306457326977</v>
+        <v>1.57634268938109</v>
       </c>
     </row>
   </sheetData>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.1865731215359</v>
+        <v>5.869869523691679</v>
       </c>
       <c r="C2" t="n">
-        <v>7.638978886744431</v>
+        <v>4.691772278595507</v>
       </c>
       <c r="D2" t="n">
-        <v>23.87806766269092</v>
+        <v>17.31213901668826</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>19.35515598922587</v>
+        <v>18.39795197758523</v>
       </c>
       <c r="C3" t="n">
-        <v>23.6699371493906</v>
+        <v>17.75490723130357</v>
       </c>
       <c r="D3" t="n">
-        <v>31.72026832421444</v>
+        <v>20.9014086234146</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>12.02248238620644</v>
+        <v>10.97593933347934</v>
       </c>
       <c r="C4" t="n">
-        <v>26.75066144531709</v>
+        <v>16.06826467540754</v>
       </c>
       <c r="D4" t="n">
-        <v>20.29272504678157</v>
+        <v>20.98191193516283</v>
       </c>
     </row>
     <row r="5">
@@ -4865,13 +4865,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>3.043417883165113</v>
+        <v>3.067961575771283</v>
       </c>
       <c r="C5" t="n">
-        <v>5.473243451175969</v>
+        <v>5.399612373357458</v>
       </c>
       <c r="D5" t="n">
-        <v>29.40334374219198</v>
+        <v>29.10881943091793</v>
       </c>
     </row>
     <row r="6">
@@ -4879,13 +4879,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>7.446556336712058</v>
+        <v>7.366053024963819</v>
       </c>
       <c r="C6" t="n">
-        <v>16.42267559664065</v>
+        <v>16.54343056426301</v>
       </c>
       <c r="D6" t="n">
-        <v>34.3346624606237</v>
+        <v>34.77743067523902</v>
       </c>
     </row>
     <row r="7">
@@ -4893,7 +4893,7 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.521970983489814</v>
+        <v>9.641744203407924</v>
       </c>
       <c r="C7" t="n">
         <v>24.49362347325367</v>
@@ -4921,10 +4921,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>9.429686699290611</v>
+        <v>9.318749208710722</v>
       </c>
       <c r="C9" t="n">
-        <v>25.73749781453438</v>
+        <v>25.5156228333746</v>
       </c>
       <c r="D9" t="n">
         <v>40.27030908049991</v>
@@ -4935,7 +4935,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8.825911861178826</v>
+        <v>8.968265278294615</v>
       </c>
       <c r="C10" t="n">
         <v>27.3318560862312</v>
@@ -4949,10 +4949,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>7.640942382152923</v>
+        <v>7.463246047684251</v>
       </c>
       <c r="C11" t="n">
-        <v>29.14219885286231</v>
+        <v>29.49759152179966</v>
       </c>
       <c r="D11" t="n">
         <v>47.97801030654161</v>
@@ -4983,7 +4983,7 @@
         <v>26.79680358741669</v>
       </c>
       <c r="D13" t="n">
-        <v>44.74806035956962</v>
+        <v>44.22773407631881</v>
       </c>
     </row>
     <row r="14">
@@ -4997,7 +4997,7 @@
         <v>25.50482360862789</v>
       </c>
       <c r="D14" t="n">
-        <v>44.86390658867074</v>
+        <v>45.47848065152925</v>
       </c>
     </row>
     <row r="15">
@@ -5005,7 +5005,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4.658392856651115</v>
+        <v>5.0167307687012</v>
       </c>
       <c r="C15" t="n">
         <v>26.51700549170635</v>
@@ -5025,7 +5025,7 @@
         <v>29.34542062764141</v>
       </c>
       <c r="D16" t="n">
-        <v>40.91826256530281</v>
+        <v>40.5049467818149</v>
       </c>
     </row>
     <row r="17">
@@ -5036,10 +5036,10 @@
         <v>5.66664774891259</v>
       </c>
       <c r="C17" t="n">
-        <v>31.63878326476196</v>
+        <v>32.11100391050468</v>
       </c>
       <c r="D17" t="n">
-        <v>36.36098972218912</v>
+        <v>36.83321036793183</v>
       </c>
     </row>
     <row r="18">
@@ -5089,13 +5089,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>15.43955356290963</v>
+        <v>15.44418801559227</v>
       </c>
       <c r="C21" t="n">
-        <v>86.13645671939058</v>
+        <v>86.16231208698845</v>
       </c>
       <c r="D21" t="n">
-        <v>3.250432329033607</v>
+        <v>3.251408003282583</v>
       </c>
     </row>
   </sheetData>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.269039928692631</v>
+        <v>5.178719139901924</v>
       </c>
       <c r="C2" t="n">
-        <v>12.95121571442392</v>
+        <v>6.14672237628928</v>
       </c>
       <c r="D2" t="n">
-        <v>19.68698671326129</v>
+        <v>16.19000139073415</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.57466656434965</v>
+        <v>19.49750940634166</v>
       </c>
       <c r="C3" t="n">
-        <v>27.34167356327367</v>
+        <v>18.05924901962008</v>
       </c>
       <c r="D3" t="n">
-        <v>43.4619708670063</v>
+        <v>29.89912633283661</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>26.43159344143688</v>
+        <v>24.8234907018806</v>
       </c>
       <c r="C4" t="n">
-        <v>45.89474167812989</v>
+        <v>32.62151271671301</v>
       </c>
       <c r="D4" t="n">
-        <v>31.61325782445154</v>
+        <v>26.73789872516188</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>10.77468105410875</v>
+        <v>10.16108873895449</v>
       </c>
       <c r="C5" t="n">
-        <v>30.50780990946964</v>
+        <v>19.46314823669302</v>
       </c>
       <c r="D5" t="n">
-        <v>29.96784867213389</v>
+        <v>29.99239236474006</v>
       </c>
     </row>
     <row r="6">
@@ -5190,13 +5190,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>5.957245069369646</v>
+        <v>5.876741757621407</v>
       </c>
       <c r="C6" t="n">
-        <v>12.27675504160637</v>
+        <v>12.19625172985813</v>
       </c>
       <c r="D6" t="n">
-        <v>36.34724525432967</v>
+        <v>36.6290068454485</v>
       </c>
     </row>
     <row r="7">
@@ -5204,13 +5204,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.462084373530759</v>
+        <v>9.581857593448868</v>
       </c>
       <c r="C7" t="n">
-        <v>24.19419042345839</v>
+        <v>24.49362347325367</v>
       </c>
       <c r="D7" t="n">
-        <v>37.66867766424586</v>
+        <v>37.42913122440964</v>
       </c>
     </row>
     <row r="8">
@@ -5224,7 +5224,7 @@
         <v>29.87458264023044</v>
       </c>
       <c r="D8" t="n">
-        <v>38.05254101660637</v>
+        <v>38.55323234577224</v>
       </c>
     </row>
     <row r="9">
@@ -5232,10 +5232,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>9.984374152190059</v>
+        <v>10.09531164276995</v>
       </c>
       <c r="C9" t="n">
-        <v>29.7312474754104</v>
+        <v>29.39843500367073</v>
       </c>
       <c r="D9" t="n">
         <v>41.26874649571891</v>
@@ -5260,10 +5260,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>8.174031385558941</v>
+        <v>8.351727720027615</v>
       </c>
       <c r="C11" t="n">
-        <v>30.91916219754903</v>
+        <v>31.45225120095506</v>
       </c>
       <c r="D11" t="n">
         <v>49.75497365122833</v>
@@ -5274,13 +5274,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>6.725953521794898</v>
+        <v>6.508987279156352</v>
       </c>
       <c r="C12" t="n">
-        <v>31.89403766786613</v>
+        <v>32.11100391050467</v>
       </c>
       <c r="D12" t="n">
-        <v>46.2138096820101</v>
+        <v>45.77987719673301</v>
       </c>
     </row>
     <row r="13">
@@ -5291,7 +5291,7 @@
         <v>5.463425974133501</v>
       </c>
       <c r="C13" t="n">
-        <v>30.17892442854696</v>
+        <v>29.91876128692155</v>
       </c>
       <c r="D13" t="n">
         <v>45.00822350119503</v>
@@ -5308,7 +5308,7 @@
         <v>27.9631198600619</v>
       </c>
       <c r="D14" t="n">
-        <v>45.47848065152925</v>
+        <v>45.7857676829585</v>
       </c>
     </row>
     <row r="15">
@@ -5316,13 +5316,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4.30005494460103</v>
+        <v>4.658392856651115</v>
       </c>
       <c r="C15" t="n">
-        <v>27.23368131580652</v>
+        <v>27.5920192278566</v>
       </c>
       <c r="D15" t="n">
-        <v>43.00054944601029</v>
+        <v>43.35888735806038</v>
       </c>
     </row>
     <row r="16">
@@ -5336,7 +5336,7 @@
         <v>29.75873641112932</v>
       </c>
       <c r="D16" t="n">
-        <v>41.33157834879071</v>
+        <v>40.91826256530281</v>
       </c>
     </row>
     <row r="17">
@@ -5350,7 +5350,7 @@
         <v>32.11100391050468</v>
       </c>
       <c r="D17" t="n">
-        <v>36.83321036793183</v>
+        <v>37.30543101367455</v>
       </c>
     </row>
     <row r="18">
@@ -5361,7 +5361,7 @@
         <v>5.350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>34.77841242294325</v>
+        <v>35.31346492175777</v>
       </c>
       <c r="D18" t="n">
         <v>31.56809743005619</v>
@@ -5375,7 +5375,7 @@
         <v>6.018113427032947</v>
       </c>
       <c r="C19" t="n">
-        <v>36.71049190490098</v>
+        <v>37.31230324760427</v>
       </c>
       <c r="D19" t="n">
         <v>24.67426505083508</v>
@@ -5400,13 +5400,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>16.73005519265283</v>
+        <v>16.74221042850644</v>
       </c>
       <c r="C21" t="n">
-        <v>102.0533366751823</v>
+        <v>102.1274836138893</v>
       </c>
       <c r="D21" t="n">
-        <v>4.182513798163207</v>
+        <v>5.022663128551931</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.339725763398402</v>
+        <v>5.450663253978291</v>
       </c>
       <c r="C2" t="n">
-        <v>9.087056750508477</v>
+        <v>3.131775176547325</v>
       </c>
       <c r="D2" t="n">
-        <v>18.83090271515807</v>
+        <v>14.38162211951153</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.2359636063845</v>
+        <v>18.53539665617978</v>
       </c>
       <c r="C3" t="n">
-        <v>40.55599766243574</v>
+        <v>21.46591355335651</v>
       </c>
       <c r="D3" t="n">
-        <v>48.7535909928966</v>
+        <v>35.549084370777</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>31.30695254072654</v>
+        <v>31.71535958569321</v>
       </c>
       <c r="C4" t="n">
-        <v>58.47878375116551</v>
+        <v>39.781398723785</v>
       </c>
       <c r="D4" t="n">
-        <v>45.48633463316322</v>
+        <v>34.96985322527139</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>25.15728492132452</v>
+        <v>23.95464398362218</v>
       </c>
       <c r="C5" t="n">
-        <v>59.78843518863076</v>
+        <v>41.89608327873264</v>
       </c>
       <c r="D5" t="n">
-        <v>34.09118902997049</v>
+        <v>32.98672286269284</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>10.18366893615217</v>
+        <v>9.861655689159212</v>
       </c>
       <c r="C6" t="n">
-        <v>30.83276839957533</v>
+        <v>21.9774041072691</v>
       </c>
       <c r="D6" t="n">
-        <v>38.03781480104267</v>
+        <v>37.91705983342032</v>
       </c>
     </row>
     <row r="7">
@@ -5521,7 +5521,7 @@
         <v>21.19985992550562</v>
       </c>
       <c r="D7" t="n">
-        <v>39.64493579289469</v>
+        <v>40.00425545264903</v>
       </c>
     </row>
     <row r="8">
@@ -5529,13 +5529,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.6814150222053</v>
+        <v>10.76486357706628</v>
       </c>
       <c r="C8" t="n">
-        <v>31.62700229231099</v>
+        <v>31.87734795689393</v>
       </c>
       <c r="D8" t="n">
-        <v>40.05530633326986</v>
+        <v>40.38910055271378</v>
       </c>
     </row>
     <row r="9">
@@ -5543,13 +5543,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>10.6499990956694</v>
+        <v>10.87187407682917</v>
       </c>
       <c r="C9" t="n">
         <v>33.9468721174462</v>
       </c>
       <c r="D9" t="n">
-        <v>42.26718391093791</v>
+        <v>41.93437143919824</v>
       </c>
     </row>
     <row r="10">
@@ -5560,10 +5560,10 @@
         <v>9.964739198105127</v>
       </c>
       <c r="C10" t="n">
-        <v>33.59540643932586</v>
+        <v>33.45305302221006</v>
       </c>
       <c r="D10" t="n">
-        <v>48.68486865359933</v>
+        <v>49.25428232206248</v>
       </c>
     </row>
     <row r="11">
@@ -5571,13 +5571,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>8.707120388964958</v>
+        <v>8.884816723433632</v>
       </c>
       <c r="C11" t="n">
-        <v>33.58460721457913</v>
+        <v>33.93999988351647</v>
       </c>
       <c r="D11" t="n">
-        <v>50.82115165804038</v>
+        <v>50.46575898910303</v>
       </c>
     </row>
     <row r="12">
@@ -5585,13 +5585,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>7.376852249710534</v>
+        <v>7.159886007071988</v>
       </c>
       <c r="C12" t="n">
-        <v>33.84673385161303</v>
+        <v>34.28066633689012</v>
       </c>
       <c r="D12" t="n">
-        <v>47.08167465256428</v>
+        <v>47.29864089520282</v>
       </c>
     </row>
     <row r="13">
@@ -5619,7 +5619,7 @@
         <v>30.72870314292517</v>
       </c>
       <c r="D14" t="n">
-        <v>45.47848065152925</v>
+        <v>45.7857676829585</v>
       </c>
     </row>
     <row r="15">
@@ -5630,10 +5630,10 @@
         <v>4.30005494460103</v>
       </c>
       <c r="C15" t="n">
-        <v>28.66703296400686</v>
+        <v>29.38370878810703</v>
       </c>
       <c r="D15" t="n">
-        <v>43.71722527011046</v>
+        <v>44.07556318216055</v>
       </c>
     </row>
     <row r="16">
@@ -5647,7 +5647,7 @@
         <v>30.17205219461722</v>
       </c>
       <c r="D16" t="n">
-        <v>41.74489413227862</v>
+        <v>40.91826256530281</v>
       </c>
     </row>
     <row r="17">
@@ -5661,7 +5661,7 @@
         <v>32.58322455624739</v>
       </c>
       <c r="D17" t="n">
-        <v>36.83321036793183</v>
+        <v>37.77765165941727</v>
       </c>
     </row>
     <row r="18">
@@ -5672,7 +5672,7 @@
         <v>4.815472489330605</v>
       </c>
       <c r="C18" t="n">
-        <v>34.77841242294325</v>
+        <v>35.31346492175777</v>
       </c>
       <c r="D18" t="n">
         <v>32.1031499288707</v>
@@ -5700,7 +5700,7 @@
         <v>4.707480241863455</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>39.67733346713483</v>
       </c>
       <c r="D20" t="n">
         <v>16.13993225781756</v>
@@ -5711,13 +5711,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>18.05072163444165</v>
+        <v>18.07585335480817</v>
       </c>
       <c r="C21" t="n">
-        <v>117.759469710405</v>
+        <v>117.9234242670819</v>
       </c>
       <c r="D21" t="n">
-        <v>6.016907211480549</v>
+        <v>6.886039373260256</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.317546476828225</v>
+        <v>5.8787052530299</v>
       </c>
       <c r="C2" t="n">
-        <v>7.823547455142832</v>
+        <v>2.610467145592269</v>
       </c>
       <c r="D2" t="n">
-        <v>29.39450801285375</v>
+        <v>16.79770321966293</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.25283324380595</v>
+        <v>16.64553232550467</v>
       </c>
       <c r="C3" t="n">
-        <v>35.24965132098173</v>
+        <v>15.09437095279471</v>
       </c>
       <c r="D3" t="n">
-        <v>49.13156385903162</v>
+        <v>36.29030388748335</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>24.44060909722434</v>
+        <v>24.78520254141498</v>
       </c>
       <c r="C4" t="n">
-        <v>68.21673922958962</v>
+        <v>39.70482240285375</v>
       </c>
       <c r="D4" t="n">
-        <v>51.39547406502477</v>
+        <v>38.41578766717769</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>21.94206118991621</v>
+        <v>22.2856728864026</v>
       </c>
       <c r="C5" t="n">
-        <v>63.64179492779949</v>
+        <v>44.27682146153116</v>
       </c>
       <c r="D5" t="n">
-        <v>33.96847056693964</v>
+        <v>30.99868376159304</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>12.07549676223577</v>
+        <v>11.63272854762046</v>
       </c>
       <c r="C6" t="n">
-        <v>42.9082651618111</v>
+        <v>30.99377502307181</v>
       </c>
       <c r="D6" t="n">
-        <v>31.23528495831652</v>
+        <v>30.67176177607885</v>
       </c>
     </row>
     <row r="7">
@@ -5829,10 +5829,10 @@
         <v>5.210135066437822</v>
       </c>
       <c r="C7" t="n">
-        <v>21.25974653546468</v>
+        <v>17.12757044828985</v>
       </c>
       <c r="D7" t="n">
-        <v>30.78171751895449</v>
+        <v>31.4404702285041</v>
       </c>
     </row>
     <row r="8">
@@ -5840,10 +5840,10 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.756567627075796</v>
+        <v>4.840016181936775</v>
       </c>
       <c r="C8" t="n">
-        <v>18.69247628885927</v>
+        <v>18.77592484372025</v>
       </c>
       <c r="D8" t="n">
         <v>30.12492830481337</v>
@@ -5857,10 +5857,10 @@
         <v>4.881249585515139</v>
       </c>
       <c r="C9" t="n">
-        <v>21.74374815365835</v>
+        <v>22.18749811597791</v>
       </c>
       <c r="D9" t="n">
-        <v>30.06405994715006</v>
+        <v>30.28593492830985</v>
       </c>
     </row>
     <row r="10">
@@ -5868,13 +5868,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.270602513473626</v>
+        <v>4.412955930589413</v>
       </c>
       <c r="C10" t="n">
-        <v>21.49536598448391</v>
+        <v>21.35301256736813</v>
       </c>
       <c r="D10" t="n">
-        <v>33.45305302221006</v>
+        <v>33.73775985644164</v>
       </c>
     </row>
     <row r="11">
@@ -5885,10 +5885,10 @@
         <v>3.731623023842126</v>
       </c>
       <c r="C11" t="n">
-        <v>20.25738212942868</v>
+        <v>20.61277479836603</v>
       </c>
       <c r="D11" t="n">
-        <v>34.65078522139116</v>
+        <v>34.29539255245382</v>
       </c>
     </row>
     <row r="12">
@@ -5899,10 +5899,10 @@
         <v>3.037527396939631</v>
       </c>
       <c r="C12" t="n">
-        <v>19.7439280801076</v>
+        <v>19.96089432274615</v>
       </c>
       <c r="D12" t="n">
-        <v>31.89403766786613</v>
+        <v>32.32797015314322</v>
       </c>
     </row>
     <row r="13">
@@ -5913,10 +5913,10 @@
         <v>2.341468274628643</v>
       </c>
       <c r="C13" t="n">
-        <v>18.99190933865455</v>
+        <v>19.25207248027995</v>
       </c>
       <c r="D13" t="n">
-        <v>30.43908757017236</v>
+        <v>30.17892442854696</v>
       </c>
     </row>
     <row r="14">
@@ -5927,10 +5927,10 @@
         <v>1.536435157146258</v>
       </c>
       <c r="C14" t="n">
-        <v>17.51536079146734</v>
+        <v>17.8226478228966</v>
       </c>
       <c r="D14" t="n">
-        <v>29.49955501720816</v>
+        <v>29.80684204863741</v>
       </c>
     </row>
     <row r="15">
@@ -5972,7 +5972,7 @@
         <v>16.52772260099505</v>
       </c>
       <c r="D17" t="n">
-        <v>23.61103228713579</v>
+        <v>24.0832529328785</v>
       </c>
     </row>
     <row r="18">
@@ -5983,7 +5983,7 @@
         <v>1.070104997629023</v>
       </c>
       <c r="C18" t="n">
-        <v>17.12167996206437</v>
+        <v>17.65673246087889</v>
       </c>
       <c r="D18" t="n">
         <v>20.33199495495144</v>
@@ -6011,7 +6011,7 @@
         <v>1.34499435481813</v>
       </c>
       <c r="C20" t="n">
-        <v>18.82992096745382</v>
+        <v>19.50241814486288</v>
       </c>
       <c r="D20" t="n">
         <v>10.08745766113597</v>
@@ -6022,13 +6022,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.052159761423134</v>
+        <v>7.069077266871918</v>
       </c>
       <c r="C21" t="n">
-        <v>66.11399776334189</v>
+        <v>67.15623403528321</v>
       </c>
       <c r="D21" t="n">
-        <v>4.407599850889459</v>
+        <v>5.301807950153938</v>
       </c>
     </row>
   </sheetData>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.424156065963627</v>
+        <v>5.159084185816988</v>
       </c>
       <c r="C2" t="n">
-        <v>4.07523472032851</v>
+        <v>3.422372497004381</v>
       </c>
       <c r="D2" t="n">
-        <v>31.71830482880595</v>
+        <v>25.94955531865169</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>19.78712497909446</v>
+        <v>19.21771131063132</v>
       </c>
       <c r="C3" t="n">
-        <v>32.26022956155019</v>
+        <v>11.85460352878024</v>
       </c>
       <c r="D3" t="n">
-        <v>61.94828013797374</v>
+        <v>41.95498814098744</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>29.12452739418588</v>
+        <v>29.82647700272235</v>
       </c>
       <c r="C4" t="n">
-        <v>80.73696770184918</v>
+        <v>38.5817030291954</v>
       </c>
       <c r="D4" t="n">
-        <v>65.21749999311561</v>
+        <v>49.05989627662161</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>30.36054775383262</v>
+        <v>31.6122760767473</v>
       </c>
       <c r="C5" t="n">
-        <v>100.6045959926919</v>
+        <v>62.73367830137119</v>
       </c>
       <c r="D5" t="n">
-        <v>45.0622196249286</v>
+        <v>38.38633523605029</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>22.1786623866397</v>
+        <v>22.70193391300324</v>
       </c>
       <c r="C6" t="n">
-        <v>77.16242431068657</v>
+        <v>54.94351026817275</v>
       </c>
       <c r="D6" t="n">
-        <v>35.46170882509904</v>
+        <v>34.29441080474959</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>10.42027013287564</v>
+        <v>10.30049691295753</v>
       </c>
       <c r="C7" t="n">
-        <v>45.03473068920969</v>
+        <v>33.83593462686632</v>
       </c>
       <c r="D7" t="n">
-        <v>33.0574086973986</v>
+        <v>33.89582123682538</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5.424156065963627</v>
+        <v>5.591053175685585</v>
       </c>
       <c r="C8" t="n">
-        <v>24.53387512912779</v>
+        <v>21.52972715413255</v>
       </c>
       <c r="D8" t="n">
-        <v>32.12769362147687</v>
+        <v>32.04424506661589</v>
       </c>
     </row>
     <row r="9">
@@ -6165,13 +6165,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.103124566674919</v>
+        <v>5.214062057254808</v>
       </c>
       <c r="C9" t="n">
-        <v>23.2968730217768</v>
+        <v>23.40781051235669</v>
       </c>
       <c r="D9" t="n">
-        <v>31.50624732468863</v>
+        <v>31.72812230584841</v>
       </c>
     </row>
     <row r="10">
@@ -6179,13 +6179,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.697662764820988</v>
+        <v>4.840016181936776</v>
       </c>
       <c r="C10" t="n">
-        <v>24.62714116103124</v>
+        <v>25.0542014123786</v>
       </c>
       <c r="D10" t="n">
-        <v>33.59540643932586</v>
+        <v>34.16482010778901</v>
       </c>
     </row>
     <row r="11">
@@ -6196,10 +6196,10 @@
         <v>4.08701569277947</v>
       </c>
       <c r="C11" t="n">
-        <v>23.27821981539612</v>
+        <v>23.63361248433346</v>
       </c>
       <c r="D11" t="n">
-        <v>35.36157055926586</v>
+        <v>34.82848155585983</v>
       </c>
     </row>
     <row r="12">
@@ -6210,10 +6210,10 @@
         <v>3.254493639578176</v>
       </c>
       <c r="C12" t="n">
-        <v>21.69662426385451</v>
+        <v>22.34752299177014</v>
       </c>
       <c r="D12" t="n">
-        <v>33.1958351236974</v>
+        <v>33.41280136633594</v>
       </c>
     </row>
     <row r="13">
@@ -6224,7 +6224,7 @@
         <v>2.601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>21.07321447165778</v>
+        <v>21.33337761328319</v>
       </c>
       <c r="D13" t="n">
         <v>30.95941385342317</v>
@@ -6238,10 +6238,10 @@
         <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>19.35908298004286</v>
+        <v>19.97365704290136</v>
       </c>
       <c r="D14" t="n">
-        <v>30.11412908006666</v>
+        <v>29.80684204863741</v>
       </c>
     </row>
     <row r="15">
@@ -6252,7 +6252,7 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>17.5585576904542</v>
+        <v>17.91689560250429</v>
       </c>
       <c r="D15" t="n">
         <v>28.66703296400686</v>
@@ -6269,7 +6269,7 @@
         <v>16.53263133951629</v>
       </c>
       <c r="D16" t="n">
-        <v>26.45221014322606</v>
+        <v>26.86552592671396</v>
       </c>
     </row>
     <row r="17">
@@ -6311,7 +6311,7 @@
         <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
-        <v>15.64709491028566</v>
+        <v>16.24890625298896</v>
       </c>
     </row>
     <row r="20">
@@ -6322,10 +6322,10 @@
         <v>0.672497177409065</v>
       </c>
       <c r="C20" t="n">
-        <v>18.82992096745382</v>
+        <v>19.50241814486288</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>10.08745766113597</v>
       </c>
     </row>
     <row r="21">
@@ -6333,13 +6333,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.270016425584893</v>
+        <v>7.29877672404931</v>
       </c>
       <c r="C21" t="n">
-        <v>75.42642041544327</v>
+        <v>77.54950269302391</v>
       </c>
       <c r="D21" t="n">
-        <v>5.45251231918867</v>
+        <v>6.386429633543146</v>
       </c>
     </row>
   </sheetData>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.11843161931537</v>
+        <v>5.849252821902496</v>
       </c>
       <c r="C2" t="n">
-        <v>7.835328427593794</v>
+        <v>2.495602664195392</v>
       </c>
       <c r="D2" t="n">
-        <v>30.83571364268807</v>
+        <v>23.40290177383547</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>19.17844140246144</v>
+        <v>18.54521413322225</v>
       </c>
       <c r="C3" t="n">
-        <v>22.60474089028281</v>
+        <v>12.78726384781471</v>
       </c>
       <c r="D3" t="n">
-        <v>72.27626598665017</v>
+        <v>53.61324212891832</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>34.43381897875263</v>
+        <v>34.66354794154638</v>
       </c>
       <c r="C4" t="n">
-        <v>79.9967299328471</v>
+        <v>33.23412328416303</v>
       </c>
       <c r="D4" t="n">
-        <v>80.08606897393356</v>
+        <v>59.6657167255999</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>37.38004383919731</v>
+        <v>39.1226460142354</v>
       </c>
       <c r="C5" t="n">
-        <v>127.8726384781471</v>
+        <v>67.29880512611886</v>
       </c>
       <c r="D5" t="n">
-        <v>58.34035732486672</v>
+        <v>47.95837535245669</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>32.36233132279187</v>
+        <v>34.29441080474959</v>
       </c>
       <c r="C6" t="n">
-        <v>121.8015106750848</v>
+        <v>80.94607996285377</v>
       </c>
       <c r="D6" t="n">
-        <v>41.25794727097221</v>
+        <v>38.68184129502858</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>18.68462230722529</v>
+        <v>19.58292145661112</v>
       </c>
       <c r="C7" t="n">
-        <v>80.12828412521617</v>
+        <v>60.06626978893259</v>
       </c>
       <c r="D7" t="n">
-        <v>36.17151241526948</v>
+        <v>36.71049190490098</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.595201150680824</v>
+        <v>8.845546815263761</v>
       </c>
       <c r="C8" t="n">
-        <v>43.56014563743097</v>
+        <v>35.04839304161113</v>
       </c>
       <c r="D8" t="n">
-        <v>33.79666471869644</v>
+        <v>34.04701038327938</v>
       </c>
     </row>
     <row r="9">
@@ -6476,13 +6476,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.435937038414587</v>
+        <v>5.657812019574366</v>
       </c>
       <c r="C9" t="n">
-        <v>27.73437264497238</v>
+        <v>25.95937279569415</v>
       </c>
       <c r="D9" t="n">
-        <v>32.9484347022272</v>
+        <v>33.28124717396686</v>
       </c>
     </row>
     <row r="10">
@@ -6490,13 +6490,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.982369599052563</v>
+        <v>5.267076433284139</v>
       </c>
       <c r="C10" t="n">
-        <v>26.90479583488384</v>
+        <v>27.47420950334699</v>
       </c>
       <c r="D10" t="n">
-        <v>34.30717352490479</v>
+        <v>34.87658719336794</v>
       </c>
     </row>
     <row r="11">
@@ -6504,13 +6504,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.264712027248144</v>
+        <v>4.442408361716816</v>
       </c>
       <c r="C11" t="n">
-        <v>26.29905750136355</v>
+        <v>26.83214650476957</v>
       </c>
       <c r="D11" t="n">
-        <v>35.53926689373453</v>
+        <v>35.18387422479719</v>
       </c>
     </row>
     <row r="12">
@@ -6521,10 +6521,10 @@
         <v>3.471459882216721</v>
       </c>
       <c r="C12" t="n">
-        <v>24.5171854181556</v>
+        <v>25.16808414607123</v>
       </c>
       <c r="D12" t="n">
-        <v>34.28066633689012</v>
+        <v>34.49763257952867</v>
       </c>
     </row>
     <row r="13">
@@ -6532,13 +6532,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.601631416254048</v>
+        <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
-        <v>22.89435646303562</v>
+        <v>23.67484588791184</v>
       </c>
       <c r="D13" t="n">
-        <v>31.47974013667398</v>
+        <v>31.73990327829938</v>
       </c>
     </row>
     <row r="14">
@@ -6549,10 +6549,10 @@
         <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>21.20280516861837</v>
+        <v>22.12466626290612</v>
       </c>
       <c r="D14" t="n">
-        <v>30.42141611149592</v>
+        <v>30.11412908006666</v>
       </c>
     </row>
     <row r="15">
@@ -6563,7 +6563,7 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>19.35024725070463</v>
+        <v>20.0669230748048</v>
       </c>
       <c r="D15" t="n">
         <v>29.02537087605695</v>
@@ -6580,7 +6580,7 @@
         <v>17.77257868998001</v>
       </c>
       <c r="D16" t="n">
-        <v>26.45221014322606</v>
+        <v>26.86552592671396</v>
       </c>
     </row>
     <row r="17">
@@ -6605,10 +6605,10 @@
         <v>0.5350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>17.65673246087889</v>
+        <v>18.1917849596934</v>
       </c>
       <c r="D18" t="n">
-        <v>20.86704745376595</v>
+        <v>21.40209995258047</v>
       </c>
     </row>
     <row r="19">
@@ -6622,7 +6622,7 @@
         <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
-        <v>15.64709491028566</v>
+        <v>16.24890625298896</v>
       </c>
     </row>
     <row r="20">
@@ -6633,7 +6633,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>18.82992096745382</v>
+        <v>19.50241814486288</v>
       </c>
       <c r="D20" t="n">
         <v>10.75995483854504</v>
@@ -6644,13 +6644,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.473356541019864</v>
+        <v>7.518216181043014</v>
       </c>
       <c r="C21" t="n">
-        <v>84.07526108647347</v>
+        <v>87.39926310462504</v>
       </c>
       <c r="D21" t="n">
-        <v>6.539186973392382</v>
+        <v>7.518216181043014</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_surface_area_iteration_94_growth_param_0.5.xlsx
+++ b/output/yearly_surface_area_iteration_94_growth_param_0.5.xlsx
@@ -735,10 +735,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>10.84497646883049</v>
+        <v>10.84497652914982</v>
       </c>
       <c r="C21" t="n">
-        <v>37.78907241794284</v>
+        <v>37.78907262812417</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.59890715731956</v>
+        <v>7.063674732055801</v>
       </c>
       <c r="C2" t="n">
-        <v>4.202861921880595</v>
+        <v>9.354092126063609</v>
       </c>
       <c r="D2" t="n">
-        <v>23.99882263031328</v>
+        <v>40.50887377263189</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>19.44351328260808</v>
+        <v>21.99114857512855</v>
       </c>
       <c r="C3" t="n">
-        <v>10.96612185643687</v>
+        <v>21.73098543350315</v>
       </c>
       <c r="D3" t="n">
-        <v>59.47427592327178</v>
+        <v>83.49273350766998</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>35.65904011365264</v>
+        <v>44.43979158043612</v>
       </c>
       <c r="C4" t="n">
-        <v>32.22586839190155</v>
+        <v>44.75885958431633</v>
       </c>
       <c r="D4" t="n">
-        <v>71.81582631335841</v>
+        <v>114.328447150358</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>45.99487994396307</v>
+        <v>51.93445355465628</v>
       </c>
       <c r="C5" t="n">
-        <v>64.05903770210439</v>
+        <v>55.02695882303374</v>
       </c>
       <c r="D5" t="n">
-        <v>58.65942532874693</v>
+        <v>88.82362354173019</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>44.71958967614647</v>
+        <v>46.57116584635595</v>
       </c>
       <c r="C6" t="n">
-        <v>95.27566945404023</v>
+        <v>69.15234479173684</v>
       </c>
       <c r="D6" t="n">
-        <v>44.63908636439822</v>
+        <v>56.79508643838223</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>30.72183090899544</v>
+        <v>31.91956310817654</v>
       </c>
       <c r="C7" t="n">
-        <v>90.18923459833748</v>
+        <v>62.34196096737671</v>
       </c>
       <c r="D7" t="n">
-        <v>40.00425545264903</v>
+        <v>41.56130731158447</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>15.43798264928109</v>
+        <v>17.02350519163969</v>
       </c>
       <c r="C8" t="n">
-        <v>59.33192250615598</v>
+        <v>42.55876297909923</v>
       </c>
       <c r="D8" t="n">
-        <v>36.46701847424777</v>
+        <v>37.05115835827462</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>7.432811868852599</v>
+        <v>8.098436812331936</v>
       </c>
       <c r="C9" t="n">
-        <v>35.83280945730432</v>
+        <v>30.84062238120929</v>
       </c>
       <c r="D9" t="n">
-        <v>34.39062207976576</v>
+        <v>33.72499713628642</v>
       </c>
     </row>
     <row r="10">
@@ -895,10 +895,10 @@
         <v>5.551783267515713</v>
       </c>
       <c r="C10" t="n">
-        <v>30.03657101143117</v>
+        <v>29.46715734296802</v>
       </c>
       <c r="D10" t="n">
-        <v>35.73070769606267</v>
+        <v>35.3036474447153</v>
       </c>
     </row>
     <row r="11">
@@ -909,10 +909,10 @@
         <v>4.797801030654161</v>
       </c>
       <c r="C11" t="n">
-        <v>29.67528785626833</v>
+        <v>29.852984190737</v>
       </c>
       <c r="D11" t="n">
-        <v>35.53926689373453</v>
+        <v>36.60544490054656</v>
       </c>
     </row>
     <row r="12">
@@ -920,13 +920,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.905392367493811</v>
+        <v>3.688426124855267</v>
       </c>
       <c r="C12" t="n">
         <v>28.42257778564941</v>
       </c>
       <c r="D12" t="n">
-        <v>35.36549755008285</v>
+        <v>34.28066633689012</v>
       </c>
     </row>
     <row r="13">
@@ -940,7 +940,7 @@
         <v>26.27647730416588</v>
       </c>
       <c r="D13" t="n">
-        <v>32.26022956155019</v>
+        <v>32.5203927031756</v>
       </c>
     </row>
     <row r="14">
@@ -948,13 +948,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>2.151009220004762</v>
+        <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>23.96838845148163</v>
+        <v>23.66110142005238</v>
       </c>
       <c r="D14" t="n">
-        <v>30.72870314292517</v>
+        <v>30.42141611149592</v>
       </c>
     </row>
     <row r="15">
@@ -965,10 +965,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>22.21695054710532</v>
+        <v>21.50027472300514</v>
       </c>
       <c r="D15" t="n">
-        <v>29.38370878810703</v>
+        <v>29.02537087605695</v>
       </c>
     </row>
     <row r="16">
@@ -979,10 +979,10 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>19.42584182393164</v>
+        <v>19.01252604044373</v>
       </c>
       <c r="D16" t="n">
-        <v>26.86552592671396</v>
+        <v>27.27884171020187</v>
       </c>
     </row>
     <row r="17">
@@ -993,10 +993,10 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>18.41660518396592</v>
+        <v>17.9443845382232</v>
       </c>
       <c r="D17" t="n">
-        <v>24.55547357862122</v>
+        <v>24.0832529328785</v>
       </c>
     </row>
     <row r="18">
@@ -1010,7 +1010,7 @@
         <v>18.1917849596934</v>
       </c>
       <c r="D18" t="n">
-        <v>21.40209995258047</v>
+        <v>20.86704745376595</v>
       </c>
     </row>
     <row r="19">
@@ -1046,13 +1046,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.726390975287</v>
+        <v>7.705141195158252</v>
       </c>
       <c r="C21" t="n">
-        <v>96.57988719108751</v>
+        <v>95.35112229008337</v>
       </c>
       <c r="D21" t="n">
-        <v>8.692189847197875</v>
+        <v>8.668283844553033</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.956664232292898</v>
+        <v>8.212319546024569</v>
       </c>
       <c r="C2" t="n">
-        <v>8.04542243630261</v>
+        <v>10.27300797723862</v>
       </c>
       <c r="D2" t="n">
-        <v>26.19891923553038</v>
+        <v>47.46651975262904</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>19.18825887950391</v>
+        <v>22.82563412373834</v>
       </c>
       <c r="C3" t="n">
-        <v>13.91627370769854</v>
+        <v>29.46715734296801</v>
       </c>
       <c r="D3" t="n">
-        <v>64.09339887175302</v>
+        <v>94.89082435397546</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>36.69282044622454</v>
+        <v>42.89550244165589</v>
       </c>
       <c r="C4" t="n">
-        <v>29.62227348023901</v>
+        <v>49.68526956422683</v>
       </c>
       <c r="D4" t="n">
-        <v>83.25122357242527</v>
+        <v>128.5971682838812</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>49.75006491270713</v>
+        <v>59.37119241432587</v>
       </c>
       <c r="C5" t="n">
-        <v>61.67829951930587</v>
+        <v>68.25600913775951</v>
       </c>
       <c r="D5" t="n">
-        <v>70.58765993534568</v>
+        <v>106.6423443738098</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>54.05797383894213</v>
+        <v>57.72087452348698</v>
       </c>
       <c r="C6" t="n">
-        <v>98.01278205348032</v>
+        <v>78.32972233103602</v>
       </c>
       <c r="D6" t="n">
-        <v>52.00513938936205</v>
+        <v>70.52090109145691</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>41.86074036137975</v>
+        <v>43.23813239043802</v>
       </c>
       <c r="C7" t="n">
-        <v>114.8625179014683</v>
+        <v>80.36783056505237</v>
       </c>
       <c r="D7" t="n">
-        <v>43.95677170994669</v>
+        <v>47.84940135728529</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>24.20008090968387</v>
+        <v>25.61870634232051</v>
       </c>
       <c r="C8" t="n">
-        <v>89.20650514638642</v>
+        <v>62.50296759087318</v>
       </c>
       <c r="D8" t="n">
-        <v>39.05392367493811</v>
+        <v>39.30426933952106</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>11.53749902030851</v>
+        <v>12.31406145436774</v>
       </c>
       <c r="C9" t="n">
-        <v>55.1359328182051</v>
+        <v>41.82343394861835</v>
       </c>
       <c r="D9" t="n">
-        <v>35.72187196672443</v>
+        <v>35.61093447614454</v>
       </c>
     </row>
     <row r="10">
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>6.405903770210439</v>
+        <v>6.690610604442014</v>
       </c>
       <c r="C10" t="n">
-        <v>36.86953503298896</v>
+        <v>33.31069960509428</v>
       </c>
       <c r="D10" t="n">
-        <v>36.58482819875739</v>
+        <v>35.58835427894688</v>
       </c>
     </row>
     <row r="11">
@@ -1223,7 +1223,7 @@
         <v>32.51842920776709</v>
       </c>
       <c r="D11" t="n">
-        <v>35.89465956267188</v>
+        <v>37.13853390395258</v>
       </c>
     </row>
     <row r="12">
@@ -1231,13 +1231,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>4.122358610132356</v>
+        <v>3.905392367493811</v>
       </c>
       <c r="C12" t="n">
-        <v>31.46010518258904</v>
+        <v>31.02617269731195</v>
       </c>
       <c r="D12" t="n">
-        <v>36.01639627799849</v>
+        <v>34.71459882216721</v>
       </c>
     </row>
     <row r="13">
@@ -1245,13 +1245,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>3.121957699504857</v>
+        <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
-        <v>28.87810872041993</v>
+        <v>29.13827186204534</v>
       </c>
       <c r="D13" t="n">
-        <v>32.780555844801</v>
+        <v>33.04071898642641</v>
       </c>
     </row>
     <row r="14">
@@ -1262,10 +1262,10 @@
         <v>2.151009220004762</v>
       </c>
       <c r="C14" t="n">
-        <v>26.42668470291564</v>
+        <v>25.81211064005714</v>
       </c>
       <c r="D14" t="n">
-        <v>31.34327720578367</v>
+        <v>30.72870314292517</v>
       </c>
     </row>
     <row r="15">
@@ -1276,10 +1276,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>24.00864010735575</v>
+        <v>23.29196428325557</v>
       </c>
       <c r="D15" t="n">
-        <v>29.74204670015712</v>
+        <v>29.38370878810703</v>
       </c>
     </row>
     <row r="16">
@@ -1290,10 +1290,10 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>21.07910495788326</v>
+        <v>20.66578917439536</v>
       </c>
       <c r="D16" t="n">
-        <v>26.86552592671396</v>
+        <v>27.27884171020187</v>
       </c>
     </row>
     <row r="17">
@@ -1304,7 +1304,7 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>19.36104647545135</v>
+        <v>18.88882582970863</v>
       </c>
       <c r="D17" t="n">
         <v>24.55547357862122</v>
@@ -1321,7 +1321,7 @@
         <v>18.72683745850791</v>
       </c>
       <c r="D18" t="n">
-        <v>21.40209995258047</v>
+        <v>20.86704745376595</v>
       </c>
     </row>
     <row r="19">
@@ -1357,13 +1357,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.92247379590694</v>
+        <v>7.893566869812262</v>
       </c>
       <c r="C21" t="n">
-        <v>105.9630870202553</v>
+        <v>104.5897610250125</v>
       </c>
       <c r="D21" t="n">
-        <v>9.903092244883675</v>
+        <v>9.866958587265328</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8.146542449840032</v>
+        <v>9.547496423800231</v>
       </c>
       <c r="C2" t="n">
-        <v>7.945284170469436</v>
+        <v>5.883613991551134</v>
       </c>
       <c r="D2" t="n">
-        <v>36.54654003829177</v>
+        <v>37.474291618805</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>21.05357951757285</v>
+        <v>25.00020528864503</v>
       </c>
       <c r="C3" t="n">
-        <v>22.76672926148353</v>
+        <v>34.30226478638355</v>
       </c>
       <c r="D3" t="n">
-        <v>68.88432766847745</v>
+        <v>106.897598776914</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>36.1823116400162</v>
+        <v>42.37223091529233</v>
       </c>
       <c r="C4" t="n">
-        <v>32.1492920709703</v>
+        <v>60.31661545351554</v>
       </c>
       <c r="D4" t="n">
-        <v>94.32926466714628</v>
+        <v>141.5896174018835</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>52.0817157102933</v>
+        <v>61.26105674500098</v>
       </c>
       <c r="C5" t="n">
-        <v>57.62859023928778</v>
+        <v>78.22074833586463</v>
       </c>
       <c r="D5" t="n">
-        <v>81.50960314509145</v>
+        <v>125.0010264432252</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>60.86050368166828</v>
+        <v>67.42152358914971</v>
       </c>
       <c r="C6" t="n">
-        <v>98.45555026809564</v>
+        <v>92.0957886399848</v>
       </c>
       <c r="D6" t="n">
-        <v>61.06176196103888</v>
+        <v>83.9247024975386</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>52.22112388429633</v>
+        <v>54.91602133245383</v>
       </c>
       <c r="C7" t="n">
-        <v>127.3189327729519</v>
+        <v>94.74061695522569</v>
       </c>
       <c r="D7" t="n">
-        <v>47.9691745772034</v>
+        <v>55.69454726192155</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>33.88011327355743</v>
+        <v>34.71459882216722</v>
       </c>
       <c r="C8" t="n">
-        <v>119.6652276706437</v>
+        <v>82.78096642209104</v>
       </c>
       <c r="D8" t="n">
-        <v>41.8911745402114</v>
+        <v>42.22496875965531</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>17.41718602104266</v>
+        <v>18.08281096452199</v>
       </c>
       <c r="C9" t="n">
-        <v>80.6515556515797</v>
+        <v>57.46562012038278</v>
       </c>
       <c r="D9" t="n">
-        <v>37.16405934426299</v>
+        <v>37.49687181600267</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8.541205026947251</v>
+        <v>8.825911861178826</v>
       </c>
       <c r="C10" t="n">
-        <v>50.39310965898878</v>
+        <v>40.9977841293468</v>
       </c>
       <c r="D10" t="n">
-        <v>37.43894870145212</v>
+        <v>36.15776794741003</v>
       </c>
     </row>
     <row r="11">
@@ -1528,13 +1528,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>5.508586368528851</v>
+        <v>5.686282702997524</v>
       </c>
       <c r="C11" t="n">
-        <v>37.31623023842126</v>
+        <v>35.36157055926586</v>
       </c>
       <c r="D11" t="n">
-        <v>36.25005223160922</v>
+        <v>37.6716229073586</v>
       </c>
     </row>
     <row r="12">
@@ -1542,13 +1542,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>4.339324852770901</v>
+        <v>4.122358610132356</v>
       </c>
       <c r="C12" t="n">
-        <v>34.49763257952867</v>
+        <v>33.62976760897449</v>
       </c>
       <c r="D12" t="n">
-        <v>36.45032876327558</v>
+        <v>35.1485313074443</v>
       </c>
     </row>
     <row r="13">
@@ -1556,13 +1556,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>3.382120841130262</v>
+        <v>3.121957699504857</v>
       </c>
       <c r="C13" t="n">
-        <v>31.47974013667398</v>
+        <v>31.73990327829938</v>
       </c>
       <c r="D13" t="n">
-        <v>33.30088212805181</v>
+        <v>33.56104526967722</v>
       </c>
     </row>
     <row r="14">
@@ -1573,10 +1573,10 @@
         <v>2.151009220004762</v>
       </c>
       <c r="C14" t="n">
-        <v>28.88498095434966</v>
+        <v>28.27040689149115</v>
       </c>
       <c r="D14" t="n">
-        <v>31.65056423721292</v>
+        <v>30.72870314292517</v>
       </c>
     </row>
     <row r="15">
@@ -1587,7 +1587,7 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>25.80032966760617</v>
+        <v>25.083653843506</v>
       </c>
       <c r="D15" t="n">
         <v>29.74204670015712</v>
@@ -1601,7 +1601,7 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>22.7323680918349</v>
+        <v>21.90573652485908</v>
       </c>
       <c r="D16" t="n">
         <v>27.27884171020187</v>
@@ -1615,7 +1615,7 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>20.30548776693678</v>
+        <v>19.83326712119407</v>
       </c>
       <c r="D17" t="n">
         <v>24.55547357862122</v>
@@ -1629,10 +1629,10 @@
         <v>0.5350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>19.26188995732242</v>
+        <v>18.72683745850791</v>
       </c>
       <c r="D18" t="n">
-        <v>21.40209995258047</v>
+        <v>20.86704745376595</v>
       </c>
     </row>
     <row r="19">
@@ -1643,7 +1643,7 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>19.25796296650543</v>
       </c>
       <c r="D19" t="n">
         <v>16.24890625298896</v>
@@ -1668,13 +1668,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8.10531604179492</v>
+        <v>8.066190094776502</v>
       </c>
       <c r="C21" t="n">
-        <v>114.4875890903532</v>
+        <v>112.926661326871</v>
       </c>
       <c r="D21" t="n">
-        <v>11.14480955746801</v>
+        <v>11.09101138031769</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7.317947387455725</v>
+        <v>8.672759219316323</v>
       </c>
       <c r="C2" t="n">
-        <v>5.148284961070273</v>
+        <v>3.906374115198058</v>
       </c>
       <c r="D2" t="n">
-        <v>29.04893282095887</v>
+        <v>30.49995592783566</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>25.84450831429728</v>
+        <v>30.0709321810798</v>
       </c>
       <c r="C3" t="n">
-        <v>32.40258297866598</v>
+        <v>46.05869354473911</v>
       </c>
       <c r="D3" t="n">
-        <v>77.51388998880691</v>
+        <v>116.2192932287374</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>25.01493150420873</v>
+        <v>29.43083267791088</v>
       </c>
       <c r="C4" t="n">
-        <v>47.89848874249763</v>
+        <v>73.20696281027615</v>
       </c>
       <c r="D4" t="n">
-        <v>91.86605967719103</v>
+        <v>138.0926320793563</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>34.28753857081986</v>
+        <v>37.9690924617454</v>
       </c>
       <c r="C5" t="n">
-        <v>58.83123117699012</v>
+        <v>55.02695882303374</v>
       </c>
       <c r="D5" t="n">
-        <v>59.96024103687396</v>
+        <v>84.94572010995527</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>32.40258297866598</v>
+        <v>34.09315252537899</v>
       </c>
       <c r="C6" t="n">
-        <v>83.84419918579036</v>
+        <v>62.39006660488482</v>
       </c>
       <c r="D6" t="n">
-        <v>31.55729820530948</v>
+        <v>36.66925850132262</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>22.45747873464579</v>
+        <v>22.99645822427728</v>
       </c>
       <c r="C7" t="n">
-        <v>84.14068699247288</v>
+        <v>58.20978488020188</v>
       </c>
       <c r="D7" t="n">
-        <v>29.40432548989622</v>
+        <v>29.64387192973244</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>12.10004045484194</v>
+        <v>12.51728322914683</v>
       </c>
       <c r="C8" t="n">
-        <v>59.41537106101696</v>
+        <v>42.30841731451629</v>
       </c>
       <c r="D8" t="n">
-        <v>27.37112599440107</v>
+        <v>27.62147165898401</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>6.101561981893925</v>
+        <v>6.323436963053704</v>
       </c>
       <c r="C9" t="n">
-        <v>38.38437174064178</v>
+        <v>31.28437234352885</v>
       </c>
       <c r="D9" t="n">
-        <v>28.51093507903161</v>
+        <v>27.5124976638126</v>
       </c>
     </row>
     <row r="10">
@@ -1825,13 +1825,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>3.98589567924205</v>
+        <v>4.128249096357838</v>
       </c>
       <c r="C10" t="n">
-        <v>29.18245050873644</v>
+        <v>27.75891633757857</v>
       </c>
       <c r="D10" t="n">
-        <v>28.32833000604172</v>
+        <v>29.46715734296802</v>
       </c>
     </row>
     <row r="11">
@@ -1839,13 +1839,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>3.198534020436107</v>
+        <v>3.020837685967435</v>
       </c>
       <c r="C11" t="n">
-        <v>27.54293184264426</v>
+        <v>26.83214650476957</v>
       </c>
       <c r="D11" t="n">
-        <v>29.14219885286231</v>
+        <v>28.07602084605028</v>
       </c>
     </row>
     <row r="12">
@@ -1853,13 +1853,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2.603594911662541</v>
+        <v>2.386628669023996</v>
       </c>
       <c r="C12" t="n">
-        <v>25.60201663134832</v>
+        <v>25.81898287398687</v>
       </c>
       <c r="D12" t="n">
-        <v>27.12078032981814</v>
+        <v>27.33774657245668</v>
       </c>
     </row>
     <row r="13">
@@ -1870,10 +1870,10 @@
         <v>1.560978849752429</v>
       </c>
       <c r="C13" t="n">
-        <v>23.93500902953724</v>
+        <v>23.41468274628643</v>
       </c>
       <c r="D13" t="n">
-        <v>26.01631416254048</v>
+        <v>25.49598787928967</v>
       </c>
     </row>
     <row r="14">
@@ -1884,7 +1884,7 @@
         <v>0.921861094287755</v>
       </c>
       <c r="C14" t="n">
-        <v>21.51009220004762</v>
+        <v>20.89551813718911</v>
       </c>
       <c r="D14" t="n">
         <v>24.89024954576939</v>
@@ -1898,7 +1898,7 @@
         <v>0.7166758241001715</v>
       </c>
       <c r="C15" t="n">
-        <v>18.99190933865455</v>
+        <v>18.27523351455437</v>
       </c>
       <c r="D15" t="n">
         <v>22.93362637120549</v>
@@ -1912,7 +1912,7 @@
         <v>0.4133157834879072</v>
       </c>
       <c r="C16" t="n">
-        <v>17.3592629064921</v>
+        <v>16.94594712300419</v>
       </c>
       <c r="D16" t="n">
         <v>20.66578917439536</v>
@@ -1926,10 +1926,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>16.52772260099505</v>
+        <v>16.05550195525234</v>
       </c>
       <c r="D17" t="n">
-        <v>18.41660518396592</v>
+        <v>17.9443845382232</v>
       </c>
     </row>
     <row r="18">
@@ -1940,7 +1940,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>16.05157496443535</v>
+        <v>16.58662746324986</v>
       </c>
       <c r="D18" t="n">
         <v>13.9113649691773</v>
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.518002934943821</v>
+        <v>5.322054304721958</v>
       </c>
       <c r="C2" t="n">
-        <v>2.492657421082652</v>
+        <v>2.057743188101315</v>
       </c>
       <c r="D2" t="n">
-        <v>21.27152750791564</v>
+        <v>21.39522771865074</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>26.45810062945154</v>
+        <v>30.87596529856219</v>
       </c>
       <c r="C3" t="n">
-        <v>26.25684235008094</v>
+        <v>30.38509144643878</v>
       </c>
       <c r="D3" t="n">
-        <v>82.67788291314514</v>
+        <v>115.6744232528804</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>36.52690508420682</v>
+        <v>41.86172210908399</v>
       </c>
       <c r="C4" t="n">
-        <v>66.87665361329272</v>
+        <v>96.83075781756715</v>
       </c>
       <c r="D4" t="n">
-        <v>108.7256130022215</v>
+        <v>161.7419525269578</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>38.06726723217008</v>
+        <v>42.3378697456437</v>
       </c>
       <c r="C5" t="n">
-        <v>75.12824306748718</v>
+        <v>92.72607066611126</v>
       </c>
       <c r="D5" t="n">
-        <v>74.95643721924398</v>
+        <v>106.519625910779</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>39.20511282139213</v>
+        <v>41.53970886209105</v>
       </c>
       <c r="C6" t="n">
-        <v>92.78006678984484</v>
+        <v>75.43160310809944</v>
       </c>
       <c r="D6" t="n">
-        <v>39.1246095096439</v>
+        <v>47.13468902859362</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>21.79872602509618</v>
+        <v>21.85861263505523</v>
       </c>
       <c r="C7" t="n">
-        <v>103.8433816690021</v>
+        <v>73.12155076000668</v>
       </c>
       <c r="D7" t="n">
-        <v>31.9794497181356</v>
+        <v>32.5184292077671</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.18072369303942</v>
+        <v>10.43106935762236</v>
       </c>
       <c r="C8" t="n">
-        <v>79.10923000820797</v>
+        <v>55.07604620824605</v>
       </c>
       <c r="D8" t="n">
-        <v>29.12354564648163</v>
+        <v>28.87319998189869</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4.992187076095029</v>
+        <v>5.103124566674919</v>
       </c>
       <c r="C9" t="n">
-        <v>46.14999608123405</v>
+        <v>37.27499683484289</v>
       </c>
       <c r="D9" t="n">
-        <v>29.39843500367073</v>
+        <v>28.84374755077128</v>
       </c>
     </row>
     <row r="10">
@@ -2136,13 +2136,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2.420008090968388</v>
+        <v>2.135301256736813</v>
       </c>
       <c r="C10" t="n">
-        <v>32.31422568528377</v>
+        <v>31.17539834835747</v>
       </c>
       <c r="D10" t="n">
-        <v>29.89421759431538</v>
+        <v>30.17892442854695</v>
       </c>
     </row>
     <row r="11">
@@ -2150,13 +2150,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>1.954659679155399</v>
+        <v>1.776963344686726</v>
       </c>
       <c r="C11" t="n">
-        <v>30.91916219754903</v>
+        <v>30.38607319414302</v>
       </c>
       <c r="D11" t="n">
-        <v>30.03068052520567</v>
+        <v>29.67528785626833</v>
       </c>
     </row>
     <row r="12">
@@ -2167,10 +2167,10 @@
         <v>1.084831213192725</v>
       </c>
       <c r="C12" t="n">
-        <v>22.56448923440869</v>
+        <v>21.91359050649305</v>
       </c>
       <c r="D12" t="n">
-        <v>28.8565102709265</v>
+        <v>28.20561154301086</v>
       </c>
     </row>
     <row r="13">
@@ -2181,7 +2181,7 @@
         <v>0.5203262832508095</v>
       </c>
       <c r="C13" t="n">
-        <v>17.69109363052753</v>
+        <v>17.17076734727672</v>
       </c>
       <c r="D13" t="n">
         <v>26.27647730416588</v>
@@ -2195,7 +2195,7 @@
         <v>0.3072870314292517</v>
       </c>
       <c r="C14" t="n">
-        <v>15.67163860289184</v>
+        <v>15.05706454003333</v>
       </c>
       <c r="D14" t="n">
         <v>19.0517959486136</v>
@@ -2209,7 +2209,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>14.69185439405351</v>
+        <v>14.33351648200343</v>
       </c>
       <c r="D15" t="n">
         <v>17.5585576904542</v>
@@ -2223,10 +2223,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>14.05273663858884</v>
+        <v>13.63942085510094</v>
       </c>
       <c r="D16" t="n">
-        <v>15.70599977254047</v>
+        <v>15.29268398905256</v>
       </c>
     </row>
     <row r="17">
@@ -2237,7 +2237,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>13.69439872653876</v>
+        <v>14.16661937228147</v>
       </c>
       <c r="D17" t="n">
         <v>11.8055161435679</v>
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.603414985213294</v>
+        <v>6.750497214401069</v>
       </c>
       <c r="C2" t="n">
-        <v>8.463646958311752</v>
+        <v>5.412375093512666</v>
       </c>
       <c r="D2" t="n">
-        <v>20.03354365286041</v>
+        <v>21.71429572253095</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>20.70996782108647</v>
+        <v>24.35716054236337</v>
       </c>
       <c r="C3" t="n">
-        <v>16.92533042121501</v>
+        <v>18.06906649666254</v>
       </c>
       <c r="D3" t="n">
-        <v>81.24944000346602</v>
+        <v>106.4607210485241</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>44.4142661401257</v>
+        <v>50.80838893788518</v>
       </c>
       <c r="C4" t="n">
-        <v>66.21299216522188</v>
+        <v>86.67163257402116</v>
       </c>
       <c r="D4" t="n">
-        <v>122.7263170124853</v>
+        <v>180.8349818791497</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>46.58392856651115</v>
+        <v>52.05717201768713</v>
       </c>
       <c r="C5" t="n">
-        <v>101.488168926514</v>
+        <v>135.6529890343031</v>
       </c>
       <c r="D5" t="n">
-        <v>95.84311962709488</v>
+        <v>136.659280431156</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>46.00764266411829</v>
+        <v>49.06676851055134</v>
       </c>
       <c r="C6" t="n">
-        <v>107.3109145604019</v>
+        <v>110.6920536538279</v>
       </c>
       <c r="D6" t="n">
-        <v>52.24664932460676</v>
+        <v>66.09321894530378</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>32.5184292077671</v>
+        <v>33.53650157707104</v>
       </c>
       <c r="C7" t="n">
-        <v>119.5336734782746</v>
+        <v>90.30900781825558</v>
       </c>
       <c r="D7" t="n">
-        <v>36.05173919535137</v>
+        <v>37.66867766424586</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>15.77177686872501</v>
+        <v>15.52143120414207</v>
       </c>
       <c r="C8" t="n">
-        <v>108.7334669838555</v>
+        <v>75.27059648460295</v>
       </c>
       <c r="D8" t="n">
-        <v>30.87596529856218</v>
+        <v>31.04286240828414</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>6.878124415953151</v>
+        <v>6.989061906533041</v>
       </c>
       <c r="C9" t="n">
-        <v>71.22186895228909</v>
+        <v>52.02968308196819</v>
       </c>
       <c r="D9" t="n">
-        <v>30.17499743772996</v>
+        <v>29.62030998483051</v>
       </c>
     </row>
     <row r="10">
@@ -2447,13 +2447,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>3.131775176547325</v>
+        <v>2.847068342315751</v>
       </c>
       <c r="C10" t="n">
-        <v>42.84837855185204</v>
+        <v>37.5813021185679</v>
       </c>
       <c r="D10" t="n">
-        <v>30.7483380970101</v>
+        <v>30.89069151412589</v>
       </c>
     </row>
     <row r="11">
@@ -2461,13 +2461,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>1.954659679155399</v>
+        <v>1.776963344686726</v>
       </c>
       <c r="C11" t="n">
-        <v>34.65078522139116</v>
+        <v>33.58460721457913</v>
       </c>
       <c r="D11" t="n">
-        <v>30.56376952861169</v>
+        <v>30.20837685967435</v>
       </c>
     </row>
     <row r="12">
@@ -2478,10 +2478,10 @@
         <v>1.084831213192725</v>
       </c>
       <c r="C12" t="n">
-        <v>27.55471281509523</v>
+        <v>26.68684784454105</v>
       </c>
       <c r="D12" t="n">
-        <v>29.29044275620359</v>
+        <v>28.63954402828795</v>
       </c>
     </row>
     <row r="13">
@@ -2492,10 +2492,10 @@
         <v>0.2601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>20.55288818840698</v>
+        <v>19.51223562190536</v>
       </c>
       <c r="D13" t="n">
-        <v>26.79680358741669</v>
+        <v>26.53664044579129</v>
       </c>
     </row>
     <row r="14">
@@ -2506,7 +2506,7 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>17.20807376003809</v>
+        <v>16.59349969717959</v>
       </c>
       <c r="D14" t="n">
         <v>19.97365704290136</v>
@@ -2520,10 +2520,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>16.12520604225386</v>
+        <v>15.76686813020377</v>
       </c>
       <c r="D15" t="n">
-        <v>17.5585576904542</v>
+        <v>17.20021977840412</v>
       </c>
     </row>
     <row r="16">
@@ -2534,10 +2534,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>15.70599977254047</v>
+        <v>15.29268398905256</v>
       </c>
       <c r="D16" t="n">
-        <v>15.29268398905256</v>
+        <v>14.87936820556466</v>
       </c>
     </row>
     <row r="17">
@@ -2548,10 +2548,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>14.63884001802419</v>
+        <v>15.11106066376691</v>
       </c>
       <c r="D17" t="n">
-        <v>10.86107485208246</v>
+        <v>11.33329549782518</v>
       </c>
     </row>
     <row r="18">
@@ -2562,7 +2562,7 @@
         <v>3.21031499288707</v>
       </c>
       <c r="C18" t="n">
-        <v>34.24335992412875</v>
+        <v>35.31346492175777</v>
       </c>
       <c r="D18" t="n">
         <v>6.955682484588652</v>
@@ -2576,7 +2576,7 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>36.71049190490098</v>
+        <v>35.50686921949439</v>
       </c>
       <c r="D19" t="n">
         <v>4.212679398923063</v>
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.66839026014283</v>
+        <v>3.956443248114646</v>
       </c>
       <c r="C2" t="n">
-        <v>3.698243601897735</v>
+        <v>2.444551783574558</v>
       </c>
       <c r="D2" t="n">
-        <v>13.68850824031328</v>
+        <v>14.99619618237003</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>20.53325323432204</v>
+        <v>25.73651606683013</v>
       </c>
       <c r="C3" t="n">
-        <v>25.64325003492669</v>
+        <v>20.62651926622549</v>
       </c>
       <c r="D3" t="n">
-        <v>81.43597206727293</v>
+        <v>104.1388877279804</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>49.44277788127786</v>
+        <v>56.13044324260714</v>
       </c>
       <c r="C4" t="n">
-        <v>63.08612572719579</v>
+        <v>79.46069568632835</v>
       </c>
       <c r="D4" t="n">
-        <v>134.2255278723281</v>
+        <v>193.2275831498572</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>49.45554060143309</v>
+        <v>54.14338588921161</v>
       </c>
       <c r="C5" t="n">
-        <v>121.7121716339983</v>
+        <v>162.1356333563608</v>
       </c>
       <c r="D5" t="n">
-        <v>106.4459948329604</v>
+        <v>148.4893402673301</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>40.17115256237099</v>
+        <v>41.21769561509809</v>
       </c>
       <c r="C6" t="n">
-        <v>140.2367690654314</v>
+        <v>137.4996564659913</v>
       </c>
       <c r="D6" t="n">
-        <v>51.52211951887262</v>
+        <v>64.24164277509429</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>10.42027013287564</v>
+        <v>10.24061030299848</v>
       </c>
       <c r="C7" t="n">
-        <v>132.8285008891849</v>
+        <v>96.47732864403831</v>
       </c>
       <c r="D7" t="n">
-        <v>36.53083207502382</v>
+        <v>37.42913122440964</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.756567627075796</v>
+        <v>4.840016181936775</v>
       </c>
       <c r="C8" t="n">
-        <v>89.79064503041327</v>
+        <v>62.66986470059513</v>
       </c>
       <c r="D8" t="n">
-        <v>32.54493639578176</v>
+        <v>32.3780392860598</v>
       </c>
     </row>
     <row r="9">
@@ -2744,13 +2744,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.218749811597791</v>
+        <v>1.996874830438012</v>
       </c>
       <c r="C9" t="n">
-        <v>32.61562223048752</v>
+        <v>28.6218725696115</v>
       </c>
       <c r="D9" t="n">
-        <v>32.61562223048752</v>
+        <v>32.50468473990763</v>
       </c>
     </row>
     <row r="10">
@@ -2758,13 +2758,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.423534171157875</v>
+        <v>1.281180754042088</v>
       </c>
       <c r="C10" t="n">
-        <v>27.18950266911542</v>
+        <v>26.33538216642069</v>
       </c>
       <c r="D10" t="n">
-        <v>23.91537407545231</v>
+        <v>23.63066724122073</v>
       </c>
     </row>
     <row r="11">
@@ -2775,10 +2775,10 @@
         <v>0.7107853378746906</v>
       </c>
       <c r="C11" t="n">
-        <v>22.0343454741154</v>
+        <v>21.32356013624072</v>
       </c>
       <c r="D11" t="n">
-        <v>23.45591614986479</v>
+        <v>22.92282714645877</v>
       </c>
     </row>
     <row r="12">
@@ -2789,10 +2789,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>16.70640068316797</v>
+        <v>15.83853571261379</v>
       </c>
       <c r="D12" t="n">
-        <v>21.69662426385451</v>
+        <v>21.47965802121596</v>
       </c>
     </row>
     <row r="13">
@@ -2803,7 +2803,7 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>14.04880964777186</v>
+        <v>13.52848336452105</v>
       </c>
       <c r="D13" t="n">
         <v>16.3902779224005</v>
@@ -2817,10 +2817,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>13.52062938288707</v>
+        <v>13.21334235145782</v>
       </c>
       <c r="D14" t="n">
-        <v>14.74977750860408</v>
+        <v>14.44249047717483</v>
       </c>
     </row>
     <row r="15">
@@ -2831,10 +2831,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>13.25850274585317</v>
+        <v>12.90016483380309</v>
       </c>
       <c r="D15" t="n">
-        <v>12.90016483380309</v>
+        <v>12.541826921753</v>
       </c>
     </row>
     <row r="16">
@@ -2845,10 +2845,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>12.39947350463721</v>
+        <v>12.81278928812512</v>
       </c>
       <c r="D16" t="n">
-        <v>9.092947236733956</v>
+        <v>9.506263020221864</v>
       </c>
     </row>
     <row r="17">
@@ -2859,7 +2859,7 @@
         <v>2.361103228713579</v>
       </c>
       <c r="C17" t="n">
-        <v>29.27768003604838</v>
+        <v>30.22212132753381</v>
       </c>
       <c r="D17" t="n">
         <v>5.66664774891259</v>
@@ -2873,7 +2873,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>31.56809743005619</v>
+        <v>30.49799243242716</v>
       </c>
       <c r="D18" t="n">
         <v>3.21031499288707</v>
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.226423866782518</v>
+        <v>4.742823159216341</v>
       </c>
       <c r="C2" t="n">
-        <v>7.220754364735291</v>
+        <v>2.344413517741383</v>
       </c>
       <c r="D2" t="n">
-        <v>12.80297181108265</v>
+        <v>15.43503740616835</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>14.83911654969054</v>
+        <v>19.80185119465817</v>
       </c>
       <c r="C3" t="n">
-        <v>19.55641426859646</v>
+        <v>14.68694565553228</v>
       </c>
       <c r="D3" t="n">
-        <v>73.95996329943345</v>
+        <v>93.17276587154355</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>44.79714774478195</v>
+        <v>52.9270004836498</v>
       </c>
       <c r="C4" t="n">
-        <v>64.19648238069892</v>
+        <v>65.91944960165209</v>
       </c>
       <c r="D4" t="n">
-        <v>143.5295508654752</v>
+        <v>200.004587552273</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>61.28560043760715</v>
+        <v>67.54424205218056</v>
       </c>
       <c r="C5" t="n">
-        <v>120.1413753072034</v>
+        <v>155.9997102048182</v>
       </c>
       <c r="D5" t="n">
-        <v>128.9771046454247</v>
+        <v>178.2362957060084</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>52.20639766873265</v>
+        <v>54.46049039768332</v>
       </c>
       <c r="C6" t="n">
-        <v>167.0041202217207</v>
+        <v>193.0066899164017</v>
       </c>
       <c r="D6" t="n">
-        <v>68.54856995362505</v>
+        <v>89.80144425516001</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>23.83487076370406</v>
+        <v>23.2360046641135</v>
       </c>
       <c r="C7" t="n">
-        <v>168.0418275451095</v>
+        <v>142.7696781423882</v>
       </c>
       <c r="D7" t="n">
-        <v>41.98051358129786</v>
+        <v>44.43586458961913</v>
       </c>
     </row>
     <row r="8">
@@ -3041,10 +3041,10 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>6.759332943739289</v>
+        <v>6.592435834017332</v>
       </c>
       <c r="C8" t="n">
-        <v>128.8445687053514</v>
+        <v>90.54168202416209</v>
       </c>
       <c r="D8" t="n">
         <v>34.63115026730623</v>
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.884374755077128</v>
+        <v>2.551562283337459</v>
       </c>
       <c r="C9" t="n">
-        <v>64.12186955517615</v>
+        <v>47.59218345877262</v>
       </c>
       <c r="D9" t="n">
-        <v>33.61405964570653</v>
+        <v>33.50312215512664</v>
       </c>
     </row>
     <row r="10">
@@ -3069,10 +3069,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.565887588273662</v>
+        <v>1.423534171157875</v>
       </c>
       <c r="C10" t="n">
-        <v>32.59893251951534</v>
+        <v>30.17892442854695</v>
       </c>
       <c r="D10" t="n">
         <v>25.19655482949439</v>
@@ -3086,10 +3086,10 @@
         <v>0.5330890034060179</v>
       </c>
       <c r="C11" t="n">
-        <v>25.9436648324262</v>
+        <v>24.87748682561417</v>
       </c>
       <c r="D11" t="n">
-        <v>24.34439782220815</v>
+        <v>23.63361248433346</v>
       </c>
     </row>
     <row r="12">
@@ -3100,10 +3100,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>19.30999559483051</v>
+        <v>18.22516438163779</v>
       </c>
       <c r="D12" t="n">
-        <v>22.34752299177014</v>
+        <v>21.91359050649305</v>
       </c>
     </row>
     <row r="13">
@@ -3114,7 +3114,7 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>16.65044106402591</v>
+        <v>15.86995163914969</v>
       </c>
       <c r="D13" t="n">
         <v>16.3902779224005</v>
@@ -3128,10 +3128,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
+        <v>14.13520344574558</v>
+      </c>
+      <c r="D14" t="n">
         <v>14.44249047717483</v>
-      </c>
-      <c r="D14" t="n">
-        <v>14.74977750860408</v>
       </c>
     </row>
     <row r="15">
@@ -3156,7 +3156,7 @@
         <v>1.653263133951629</v>
       </c>
       <c r="C16" t="n">
-        <v>23.1456838753228</v>
+        <v>24.38563122578652</v>
       </c>
       <c r="D16" t="n">
         <v>8.266315669758143</v>
@@ -3170,7 +3170,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>35.41654843070368</v>
+        <v>34.94432778496098</v>
       </c>
       <c r="D17" t="n">
         <v>4.722206457427158</v>
@@ -3184,7 +3184,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>1.605157496443535</v>
+        <v>1.070104997629023</v>
       </c>
       <c r="D18" t="n">
         <v>1.070104997629023</v>
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.021819433671682</v>
+        <v>3.407646281440679</v>
       </c>
       <c r="C2" t="n">
-        <v>4.643666641087413</v>
+        <v>1.687624303600267</v>
       </c>
       <c r="D2" t="n">
-        <v>9.156760837509999</v>
+        <v>12.85402269170349</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>14.93729132011522</v>
+        <v>18.4666743168825</v>
       </c>
       <c r="C3" t="n">
-        <v>24.28843820306609</v>
+        <v>12.20803270230909</v>
       </c>
       <c r="D3" t="n">
-        <v>68.54071597199106</v>
+        <v>86.18272221730625</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>39.41127983928396</v>
+        <v>47.86020058203201</v>
       </c>
       <c r="C4" t="n">
-        <v>58.19800390775092</v>
+        <v>54.7265440255342</v>
       </c>
       <c r="D4" t="n">
-        <v>147.5625704345211</v>
+        <v>201.5105885305876</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>66.63612542575227</v>
+        <v>74.46556336712058</v>
       </c>
       <c r="C5" t="n">
-        <v>123.5774922720673</v>
+        <v>147.7775731817512</v>
       </c>
       <c r="D5" t="n">
-        <v>145.8631651584699</v>
+        <v>200.0065510476815</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>61.90704673439538</v>
+        <v>64.64415933383549</v>
       </c>
       <c r="C6" t="n">
-        <v>184.2720805917178</v>
+        <v>220.9815907489146</v>
       </c>
       <c r="D6" t="n">
-        <v>82.75740447718914</v>
+        <v>107.9549410543878</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>24.852943133008</v>
+        <v>22.57725195456389</v>
       </c>
       <c r="C7" t="n">
-        <v>202.3568550516483</v>
+        <v>189.2416874706151</v>
       </c>
       <c r="D7" t="n">
-        <v>47.78951474732623</v>
+        <v>50.96350507515617</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5.674501730546564</v>
+        <v>5.340707511102648</v>
       </c>
       <c r="C8" t="n">
-        <v>162.4743363143259</v>
+        <v>117.5790137991192</v>
       </c>
       <c r="D8" t="n">
-        <v>36.38356991938679</v>
+        <v>36.63391558396972</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.218749811597791</v>
+        <v>1.996874830438012</v>
       </c>
       <c r="C9" t="n">
-        <v>80.31874317984003</v>
+        <v>57.13280764864312</v>
       </c>
       <c r="D9" t="n">
-        <v>33.50312215512664</v>
+        <v>33.05937219280708</v>
       </c>
     </row>
     <row r="10">
@@ -3383,7 +3383,7 @@
         <v>0.5694136684631501</v>
       </c>
       <c r="C10" t="n">
-        <v>34.16482010778901</v>
+        <v>31.74481201682062</v>
       </c>
       <c r="D10" t="n">
         <v>25.76596849795754</v>
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>25.9436648324262</v>
+        <v>24.34439782220815</v>
       </c>
       <c r="D11" t="n">
-        <v>24.87748682561417</v>
+        <v>24.16670148773948</v>
       </c>
     </row>
     <row r="12">
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>19.09302935219197</v>
+        <v>17.7912318963607</v>
       </c>
       <c r="D12" t="n">
-        <v>20.82875929330033</v>
+        <v>20.39482680802324</v>
       </c>
     </row>
     <row r="13">
@@ -3425,10 +3425,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>11.96750451476862</v>
+        <v>11.70734137314322</v>
       </c>
       <c r="D13" t="n">
-        <v>16.91060420565131</v>
+        <v>16.3902779224005</v>
       </c>
     </row>
     <row r="14">
@@ -3442,7 +3442,7 @@
         <v>11.67690719431156</v>
       </c>
       <c r="D14" t="n">
-        <v>11.67690719431156</v>
+        <v>11.36962016288231</v>
       </c>
     </row>
     <row r="15">
@@ -3453,7 +3453,7 @@
         <v>1.075013736150257</v>
       </c>
       <c r="C15" t="n">
-        <v>19.35024725070463</v>
+        <v>20.42526098685489</v>
       </c>
       <c r="D15" t="n">
         <v>6.808420328951629</v>
@@ -3467,7 +3467,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>30.17205219461722</v>
+        <v>29.75873641112932</v>
       </c>
       <c r="D16" t="n">
         <v>3.719842051391165</v>
@@ -3481,7 +3481,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>0.9444412914854317</v>
+        <v>0.4722206457427158</v>
       </c>
       <c r="D17" t="n">
         <v>0.4722206457427158</v>
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.746750150033328</v>
+        <v>5.424156065963627</v>
       </c>
       <c r="C2" t="n">
-        <v>3.749294482518569</v>
+        <v>4.856705892908971</v>
       </c>
       <c r="D2" t="n">
-        <v>13.37336722725005</v>
+        <v>15.53419392429728</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>12.59582304548658</v>
+        <v>15.08946221427348</v>
       </c>
       <c r="C3" t="n">
-        <v>21.22538536581604</v>
+        <v>9.429686699290613</v>
       </c>
       <c r="D3" t="n">
-        <v>61.12852080492765</v>
+        <v>78.54963381678731</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>34.05093737409637</v>
+        <v>41.63199314629023</v>
       </c>
       <c r="C4" t="n">
-        <v>59.25730968063323</v>
+        <v>43.43153668817465</v>
       </c>
       <c r="D4" t="n">
-        <v>147.7795366771596</v>
+        <v>196.6990430320739</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>64.52536786162162</v>
+        <v>74.22012644105888</v>
       </c>
       <c r="C5" t="n">
-        <v>115.8462291011237</v>
+        <v>126.7190849256571</v>
       </c>
       <c r="D5" t="n">
-        <v>159.8776136365931</v>
+        <v>220.9177771481386</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>73.78128521726055</v>
+        <v>78.49072895453251</v>
       </c>
       <c r="C6" t="n">
-        <v>190.3098289728357</v>
+        <v>227.6231139681443</v>
       </c>
       <c r="D6" t="n">
-        <v>104.1712854022206</v>
+        <v>136.0908485103971</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>42.87881273068369</v>
+        <v>41.20198765183014</v>
       </c>
       <c r="C7" t="n">
-        <v>233.7973252801524</v>
+        <v>245.7147606620044</v>
       </c>
       <c r="D7" t="n">
-        <v>57.61091878061132</v>
+        <v>64.37810570598458</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>12.93452600345173</v>
+        <v>11.34900346109313</v>
       </c>
       <c r="C8" t="n">
-        <v>208.0372472684203</v>
+        <v>170.4853975809798</v>
       </c>
       <c r="D8" t="n">
-        <v>39.80496066868692</v>
+        <v>40.22220344299182</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>3.217187226816797</v>
+        <v>2.995312245657018</v>
       </c>
       <c r="C9" t="n">
-        <v>130.2406139407903</v>
+        <v>91.63436721898876</v>
       </c>
       <c r="D9" t="n">
-        <v>35.16718451382499</v>
+        <v>34.39062207976576</v>
       </c>
     </row>
     <row r="10">
@@ -3694,10 +3694,10 @@
         <v>0.8541205026947251</v>
       </c>
       <c r="C10" t="n">
-        <v>57.65313393189394</v>
+        <v>44.98367980858886</v>
       </c>
       <c r="D10" t="n">
-        <v>27.18950266911542</v>
+        <v>27.3318560862312</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>31.09685853201771</v>
+        <v>29.14219885286231</v>
       </c>
       <c r="D11" t="n">
-        <v>25.41057582902019</v>
+        <v>24.52209415667683</v>
       </c>
     </row>
     <row r="12">
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>22.78145547704723</v>
+        <v>21.04572553593887</v>
       </c>
       <c r="D12" t="n">
-        <v>21.26269177857742</v>
+        <v>20.82875929330033</v>
       </c>
     </row>
     <row r="13">
@@ -3736,10 +3736,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>14.56913593102267</v>
+        <v>13.78864650614645</v>
       </c>
       <c r="D13" t="n">
-        <v>17.43093048890212</v>
+        <v>16.65044106402591</v>
       </c>
     </row>
     <row r="14">
@@ -3753,7 +3753,7 @@
         <v>12.29148125717007</v>
       </c>
       <c r="D14" t="n">
-        <v>11.98419422574081</v>
+        <v>11.67690719431156</v>
       </c>
     </row>
     <row r="15">
@@ -3764,10 +3764,10 @@
         <v>0.7166758241001715</v>
       </c>
       <c r="C15" t="n">
-        <v>19.35024725070463</v>
+        <v>21.14193681095506</v>
       </c>
       <c r="D15" t="n">
-        <v>6.808420328951629</v>
+        <v>6.450082416901544</v>
       </c>
     </row>
     <row r="16">
@@ -3778,7 +3778,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>30.58536797810513</v>
+        <v>29.34542062764141</v>
       </c>
       <c r="D16" t="n">
         <v>3.306526267903257</v>
@@ -3792,7 +3792,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>0.4722206457427158</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
         <v>0</v>
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.397247967321463</v>
+        <v>6.427502219703868</v>
       </c>
       <c r="C2" t="n">
-        <v>3.91815508764902</v>
+        <v>3.421390749300134</v>
       </c>
       <c r="D2" t="n">
-        <v>9.683959354690538</v>
+        <v>14.35707842690536</v>
       </c>
     </row>
     <row r="3">
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.285909566114074</v>
+        <v>3.840597019013522</v>
       </c>
       <c r="C2" t="n">
-        <v>2.008655802888974</v>
+        <v>2.719441140763665</v>
       </c>
       <c r="D2" t="n">
-        <v>9.735991983015619</v>
+        <v>11.4344155113626</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.18058482431918</v>
+        <v>20.36635612460008</v>
       </c>
       <c r="C3" t="n">
-        <v>22.26603793231766</v>
+        <v>13.79355524466769</v>
       </c>
       <c r="D3" t="n">
-        <v>66.76866136582558</v>
+        <v>84.73464435354221</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>48.28137034715389</v>
+        <v>56.93449461238528</v>
       </c>
       <c r="C4" t="n">
-        <v>81.59206995224817</v>
+        <v>64.11990605976767</v>
       </c>
       <c r="D4" t="n">
-        <v>151.7104544849638</v>
+        <v>203.9610308003876</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>45.13585070274711</v>
+        <v>46.95208395560371</v>
       </c>
       <c r="C5" t="n">
-        <v>165.3754007803752</v>
+        <v>190.0172681569702</v>
       </c>
       <c r="D5" t="n">
-        <v>148.6611461155733</v>
+        <v>201.8227843005381</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>26.60634453279281</v>
+        <v>25.55980148006571</v>
       </c>
       <c r="C6" t="n">
-        <v>198.7224250505267</v>
+        <v>210.9186767803848</v>
       </c>
       <c r="D6" t="n">
-        <v>84.68948395914687</v>
+        <v>103.1247423494935</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>8.563785224144926</v>
+        <v>7.485826244881928</v>
       </c>
       <c r="C7" t="n">
-        <v>146.3029881299724</v>
+        <v>119.892993138029</v>
       </c>
       <c r="D7" t="n">
-        <v>35.87207936547421</v>
+        <v>37.06981156465531</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>2.169662426385451</v>
+        <v>2.002765316663493</v>
       </c>
       <c r="C8" t="n">
-        <v>95.9658380901257</v>
+        <v>67.5098808825319</v>
       </c>
       <c r="D8" t="n">
-        <v>25.86905200690345</v>
+        <v>25.2849121228766</v>
       </c>
     </row>
     <row r="9">
@@ -4302,10 +4302,10 @@
         <v>0.5546874528994477</v>
       </c>
       <c r="C9" t="n">
-        <v>43.93124626963626</v>
+        <v>34.27968458918587</v>
       </c>
       <c r="D9" t="n">
-        <v>20.74531073843935</v>
+        <v>20.85624822901923</v>
       </c>
     </row>
     <row r="10">
@@ -4316,10 +4316,10 @@
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>24.34243432679967</v>
+        <v>22.776546738526</v>
       </c>
       <c r="D10" t="n">
-        <v>19.92947839621025</v>
+        <v>19.21771131063132</v>
       </c>
     </row>
     <row r="11">
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>18.12502611580461</v>
+        <v>16.8811517745239</v>
       </c>
       <c r="D11" t="n">
-        <v>17.05884810899257</v>
+        <v>16.70345544005523</v>
       </c>
     </row>
     <row r="12">
@@ -4344,10 +4344,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>11.71617710248143</v>
+        <v>11.0652783745658</v>
       </c>
       <c r="D12" t="n">
-        <v>14.10280577150543</v>
+        <v>13.4519070435898</v>
       </c>
     </row>
     <row r="13">
@@ -4361,7 +4361,7 @@
         <v>10.14636252339079</v>
       </c>
       <c r="D13" t="n">
-        <v>9.886199381765381</v>
+        <v>9.626036240139976</v>
       </c>
     </row>
     <row r="14">
@@ -4372,10 +4372,10 @@
         <v>0.3072870314292517</v>
       </c>
       <c r="C14" t="n">
-        <v>15.97892563432109</v>
+        <v>17.51536079146734</v>
       </c>
       <c r="D14" t="n">
-        <v>5.53116656572653</v>
+        <v>5.223879534297279</v>
       </c>
     </row>
     <row r="15">
@@ -4386,7 +4386,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>25.80032966760617</v>
+        <v>24.72531593145592</v>
       </c>
       <c r="D15" t="n">
         <v>2.5083653843506</v>
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7.107853378746906</v>
+        <v>6.857507714163971</v>
       </c>
       <c r="C2" t="n">
-        <v>5.684319207589032</v>
+        <v>2.486766934857171</v>
       </c>
       <c r="D2" t="n">
-        <v>14.7124710958427</v>
+        <v>28.7622624913188</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>9.346238144429634</v>
+        <v>13.6512018275519</v>
       </c>
       <c r="C3" t="n">
-        <v>10.02855279888117</v>
+        <v>8.619744843286995</v>
       </c>
       <c r="D3" t="n">
-        <v>11.27046364475338</v>
+        <v>15.19745446174063</v>
       </c>
     </row>
     <row r="4">
@@ -4543,7 +4543,7 @@
         <v>1.008254892261474</v>
       </c>
       <c r="C4" t="n">
-        <v>1.454950097693773</v>
+        <v>1.493238258159399</v>
       </c>
       <c r="D4" t="n">
         <v>19.62906359871073</v>
@@ -4554,10 +4554,10 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>4.68784528777852</v>
+        <v>4.736932672990861</v>
       </c>
       <c r="C5" t="n">
-        <v>9.424777960769381</v>
+        <v>9.35114688295087</v>
       </c>
       <c r="D5" t="n">
         <v>28.49522711576368</v>
@@ -4568,13 +4568,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>8.130834486572086</v>
+        <v>8.050331174823848</v>
       </c>
       <c r="C6" t="n">
         <v>18.47551004622073</v>
       </c>
       <c r="D6" t="n">
-        <v>32.52333794628834</v>
+        <v>32.8453511932813</v>
       </c>
     </row>
     <row r="7">
@@ -4588,7 +4588,7 @@
         <v>20.9603134856694</v>
       </c>
       <c r="D7" t="n">
-        <v>32.69808903764427</v>
+        <v>32.21899615797182</v>
       </c>
     </row>
     <row r="8">
@@ -4778,13 +4778,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>13.39891285973927</v>
+        <v>13.39784643691723</v>
       </c>
       <c r="C21" t="n">
-        <v>70.14724967745852</v>
+        <v>70.14166664033138</v>
       </c>
       <c r="D21" t="n">
-        <v>1.57634268938109</v>
+        <v>1.576217227872615</v>
       </c>
     </row>
   </sheetData>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.869869523691679</v>
+        <v>4.532729150507524</v>
       </c>
       <c r="C2" t="n">
-        <v>4.691772278595507</v>
+        <v>4.82921695719006</v>
       </c>
       <c r="D2" t="n">
-        <v>17.31213901668826</v>
+        <v>28.90756115154733</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.39795197758523</v>
+        <v>19.68404147014855</v>
       </c>
       <c r="C3" t="n">
-        <v>17.75490723130357</v>
+        <v>9.29224202069606</v>
       </c>
       <c r="D3" t="n">
-        <v>20.9014086234146</v>
+        <v>35.68162031085032</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>10.97593933347934</v>
+        <v>15.851298432769</v>
       </c>
       <c r="C4" t="n">
-        <v>16.06826467540754</v>
+        <v>13.70716144669397</v>
       </c>
       <c r="D4" t="n">
-        <v>20.98191193516283</v>
+        <v>23.03670988015141</v>
       </c>
     </row>
     <row r="5">
@@ -4868,10 +4868,10 @@
         <v>3.067961575771283</v>
       </c>
       <c r="C5" t="n">
-        <v>5.399612373357458</v>
+        <v>5.375068680751288</v>
       </c>
       <c r="D5" t="n">
-        <v>29.10881943091793</v>
+        <v>29.40334374219198</v>
       </c>
     </row>
     <row r="6">
@@ -4879,13 +4879,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>7.366053024963819</v>
+        <v>7.446556336712058</v>
       </c>
       <c r="C6" t="n">
-        <v>16.54343056426301</v>
+        <v>16.50317890838889</v>
       </c>
       <c r="D6" t="n">
-        <v>34.77743067523902</v>
+        <v>34.57617239586842</v>
       </c>
     </row>
     <row r="7">
@@ -4893,13 +4893,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.641744203407924</v>
+        <v>9.462084373530759</v>
       </c>
       <c r="C7" t="n">
         <v>24.49362347325367</v>
       </c>
       <c r="D7" t="n">
-        <v>35.27321326588365</v>
+        <v>34.97378021608837</v>
       </c>
     </row>
     <row r="8">
@@ -4913,7 +4913,7 @@
         <v>25.61870634232051</v>
       </c>
       <c r="D8" t="n">
-        <v>36.80081269369168</v>
+        <v>36.63391558396972</v>
       </c>
     </row>
     <row r="9">
@@ -4921,10 +4921,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>9.318749208710722</v>
+        <v>9.429686699290611</v>
       </c>
       <c r="C9" t="n">
-        <v>25.5156228333746</v>
+        <v>25.73749781453438</v>
       </c>
       <c r="D9" t="n">
         <v>40.27030908049991</v>
@@ -4935,7 +4935,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8.968265278294615</v>
+        <v>8.825911861178826</v>
       </c>
       <c r="C10" t="n">
         <v>27.3318560862312</v>
@@ -4949,10 +4949,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>7.463246047684251</v>
+        <v>7.640942382152923</v>
       </c>
       <c r="C11" t="n">
-        <v>29.49759152179966</v>
+        <v>29.14219885286231</v>
       </c>
       <c r="D11" t="n">
         <v>47.97801030654161</v>
@@ -4983,7 +4983,7 @@
         <v>26.79680358741669</v>
       </c>
       <c r="D13" t="n">
-        <v>44.22773407631881</v>
+        <v>44.74806035956962</v>
       </c>
     </row>
     <row r="14">
@@ -4997,7 +4997,7 @@
         <v>25.50482360862789</v>
       </c>
       <c r="D14" t="n">
-        <v>45.47848065152925</v>
+        <v>44.86390658867074</v>
       </c>
     </row>
     <row r="15">
@@ -5036,7 +5036,7 @@
         <v>5.66664774891259</v>
       </c>
       <c r="C17" t="n">
-        <v>32.11100391050468</v>
+        <v>31.63878326476196</v>
       </c>
       <c r="D17" t="n">
         <v>36.83321036793183</v>
@@ -5089,13 +5089,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>15.44418801559227</v>
+        <v>15.43968952312328</v>
       </c>
       <c r="C21" t="n">
-        <v>86.16231208698845</v>
+        <v>86.13721523426673</v>
       </c>
       <c r="D21" t="n">
-        <v>3.251408003282583</v>
+        <v>3.25046095223648</v>
       </c>
     </row>
   </sheetData>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.178719139901924</v>
+        <v>5.987679248201297</v>
       </c>
       <c r="C2" t="n">
-        <v>6.14672237628928</v>
+        <v>3.3703398686793</v>
       </c>
       <c r="D2" t="n">
-        <v>16.19000139073415</v>
+        <v>26.92835777978576</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>19.49750940634166</v>
+        <v>17.43583922742335</v>
       </c>
       <c r="C3" t="n">
-        <v>18.05924901962008</v>
+        <v>15.0501923061036</v>
       </c>
       <c r="D3" t="n">
-        <v>29.89912633283661</v>
+        <v>50.5256455990621</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>24.8234907018806</v>
+        <v>28.51191682673587</v>
       </c>
       <c r="C4" t="n">
-        <v>32.62151271671301</v>
+        <v>19.33552103514093</v>
       </c>
       <c r="D4" t="n">
-        <v>26.73789872516188</v>
+        <v>35.72285371442869</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>10.16108873895449</v>
+        <v>13.71992416684918</v>
       </c>
       <c r="C5" t="n">
-        <v>19.46314823669302</v>
+        <v>16.73879835740812</v>
       </c>
       <c r="D5" t="n">
-        <v>29.99239236474006</v>
+        <v>30.92505268377453</v>
       </c>
     </row>
     <row r="6">
@@ -5190,13 +5190,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>5.876741757621407</v>
+        <v>5.957245069369646</v>
       </c>
       <c r="C6" t="n">
-        <v>12.19625172985813</v>
+        <v>12.07549676223577</v>
       </c>
       <c r="D6" t="n">
-        <v>36.6290068454485</v>
+        <v>36.54850353370026</v>
       </c>
     </row>
     <row r="7">
@@ -5204,13 +5204,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.581857593448868</v>
+        <v>9.462084373530759</v>
       </c>
       <c r="C7" t="n">
         <v>24.49362347325367</v>
       </c>
       <c r="D7" t="n">
-        <v>37.42913122440964</v>
+        <v>37.12969817461437</v>
       </c>
     </row>
     <row r="8">
@@ -5224,7 +5224,7 @@
         <v>29.87458264023044</v>
       </c>
       <c r="D8" t="n">
-        <v>38.55323234577224</v>
+        <v>38.38633523605029</v>
       </c>
     </row>
     <row r="9">
@@ -5232,13 +5232,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>10.09531164276995</v>
+        <v>9.984374152190059</v>
       </c>
       <c r="C9" t="n">
-        <v>29.39843500367073</v>
+        <v>29.7312474754104</v>
       </c>
       <c r="D9" t="n">
-        <v>41.26874649571891</v>
+        <v>41.15780900513902</v>
       </c>
     </row>
     <row r="10">
@@ -5249,7 +5249,7 @@
         <v>9.395325529641976</v>
       </c>
       <c r="C10" t="n">
-        <v>29.89421759431538</v>
+        <v>29.60951076008381</v>
       </c>
       <c r="D10" t="n">
         <v>49.25428232206248</v>
@@ -5260,10 +5260,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>8.351727720027615</v>
+        <v>8.174031385558941</v>
       </c>
       <c r="C11" t="n">
-        <v>31.45225120095506</v>
+        <v>31.27455486648638</v>
       </c>
       <c r="D11" t="n">
         <v>49.75497365122833</v>
@@ -5274,13 +5274,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>6.508987279156352</v>
+        <v>6.725953521794898</v>
       </c>
       <c r="C12" t="n">
-        <v>32.11100391050467</v>
+        <v>31.89403766786613</v>
       </c>
       <c r="D12" t="n">
-        <v>45.77987719673301</v>
+        <v>46.2138096820101</v>
       </c>
     </row>
     <row r="13">
@@ -5291,7 +5291,7 @@
         <v>5.463425974133501</v>
       </c>
       <c r="C13" t="n">
-        <v>29.91876128692155</v>
+        <v>30.17892442854696</v>
       </c>
       <c r="D13" t="n">
         <v>45.00822350119503</v>
@@ -5305,10 +5305,10 @@
         <v>4.609305471438775</v>
       </c>
       <c r="C14" t="n">
-        <v>27.9631198600619</v>
+        <v>27.65583282863265</v>
       </c>
       <c r="D14" t="n">
-        <v>45.7857676829585</v>
+        <v>45.47848065152925</v>
       </c>
     </row>
     <row r="15">
@@ -5322,7 +5322,7 @@
         <v>27.5920192278566</v>
       </c>
       <c r="D15" t="n">
-        <v>43.35888735806038</v>
+        <v>43.00054944601029</v>
       </c>
     </row>
     <row r="16">
@@ -5361,7 +5361,7 @@
         <v>5.350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>35.31346492175777</v>
+        <v>34.77841242294325</v>
       </c>
       <c r="D18" t="n">
         <v>31.56809743005619</v>
@@ -5375,7 +5375,7 @@
         <v>6.018113427032947</v>
       </c>
       <c r="C19" t="n">
-        <v>37.31230324760427</v>
+        <v>36.71049190490098</v>
       </c>
       <c r="D19" t="n">
         <v>24.67426505083508</v>
@@ -5400,13 +5400,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>16.74221042850644</v>
+        <v>16.73312042259591</v>
       </c>
       <c r="C21" t="n">
-        <v>102.1274836138893</v>
+        <v>102.0720345778351</v>
       </c>
       <c r="D21" t="n">
-        <v>5.022663128551931</v>
+        <v>5.019936126778774</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.450663253978291</v>
+        <v>6.478553100324701</v>
       </c>
       <c r="C2" t="n">
-        <v>3.131775176547325</v>
+        <v>3.634430001121692</v>
       </c>
       <c r="D2" t="n">
-        <v>14.38162211951153</v>
+        <v>31.69081589308704</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.53539665617978</v>
+        <v>19.1293540172491</v>
       </c>
       <c r="C3" t="n">
-        <v>21.46591355335651</v>
+        <v>13.90645623065607</v>
       </c>
       <c r="D3" t="n">
-        <v>35.549084370777</v>
+        <v>59.75407401898212</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>31.71535958569321</v>
+        <v>31.51115606320987</v>
       </c>
       <c r="C4" t="n">
-        <v>39.781398723785</v>
+        <v>29.37978179729005</v>
       </c>
       <c r="D4" t="n">
-        <v>34.96985322527139</v>
+        <v>51.72730478906019</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>23.95464398362218</v>
+        <v>28.10252803406495</v>
       </c>
       <c r="C5" t="n">
-        <v>41.89608327873264</v>
+        <v>27.16986771503048</v>
       </c>
       <c r="D5" t="n">
-        <v>32.98672286269284</v>
+        <v>36.86462629446773</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>9.861655689159212</v>
+        <v>12.27675504160637</v>
       </c>
       <c r="C6" t="n">
-        <v>21.9774041072691</v>
+        <v>19.76356303419254</v>
       </c>
       <c r="D6" t="n">
-        <v>37.91705983342032</v>
+        <v>38.48058301565798</v>
       </c>
     </row>
     <row r="7">
@@ -5515,13 +5515,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>8.683558444063037</v>
+        <v>8.623671834103982</v>
       </c>
       <c r="C7" t="n">
-        <v>21.19985992550562</v>
+        <v>20.9603134856694</v>
       </c>
       <c r="D7" t="n">
-        <v>40.00425545264903</v>
+        <v>39.22572952318131</v>
       </c>
     </row>
     <row r="8">
@@ -5535,7 +5535,7 @@
         <v>31.87734795689393</v>
       </c>
       <c r="D8" t="n">
-        <v>40.38910055271378</v>
+        <v>40.13875488813084</v>
       </c>
     </row>
     <row r="9">
@@ -5543,13 +5543,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>10.87187407682917</v>
+        <v>10.76093658624928</v>
       </c>
       <c r="C9" t="n">
-        <v>33.9468721174462</v>
+        <v>34.39062207976576</v>
       </c>
       <c r="D9" t="n">
-        <v>41.93437143919824</v>
+        <v>41.82343394861835</v>
       </c>
     </row>
     <row r="10">
@@ -5560,7 +5560,7 @@
         <v>9.964739198105127</v>
       </c>
       <c r="C10" t="n">
-        <v>33.45305302221006</v>
+        <v>33.02599277086271</v>
       </c>
       <c r="D10" t="n">
         <v>49.25428232206248</v>
@@ -5574,10 +5574,10 @@
         <v>8.884816723433632</v>
       </c>
       <c r="C11" t="n">
-        <v>33.93999988351647</v>
+        <v>33.7623035490478</v>
       </c>
       <c r="D11" t="n">
-        <v>50.46575898910303</v>
+        <v>50.82115165804038</v>
       </c>
     </row>
     <row r="12">
@@ -5588,10 +5588,10 @@
         <v>7.159886007071988</v>
       </c>
       <c r="C12" t="n">
-        <v>34.28066633689012</v>
+        <v>34.49763257952867</v>
       </c>
       <c r="D12" t="n">
-        <v>47.29864089520282</v>
+        <v>47.08167465256428</v>
       </c>
     </row>
     <row r="13">
@@ -5602,7 +5602,7 @@
         <v>5.723589115758904</v>
       </c>
       <c r="C13" t="n">
-        <v>33.30088212805181</v>
+        <v>33.04071898642641</v>
       </c>
       <c r="D13" t="n">
         <v>45.78871292607123</v>
@@ -5619,7 +5619,7 @@
         <v>30.72870314292517</v>
       </c>
       <c r="D14" t="n">
-        <v>45.7857676829585</v>
+        <v>45.47848065152925</v>
       </c>
     </row>
     <row r="15">
@@ -5630,10 +5630,10 @@
         <v>4.30005494460103</v>
       </c>
       <c r="C15" t="n">
-        <v>29.38370878810703</v>
+        <v>29.02537087605695</v>
       </c>
       <c r="D15" t="n">
-        <v>44.07556318216055</v>
+        <v>43.71722527011046</v>
       </c>
     </row>
     <row r="16">
@@ -5647,7 +5647,7 @@
         <v>30.17205219461722</v>
       </c>
       <c r="D16" t="n">
-        <v>40.91826256530281</v>
+        <v>41.33157834879071</v>
       </c>
     </row>
     <row r="17">
@@ -5658,10 +5658,10 @@
         <v>4.722206457427158</v>
       </c>
       <c r="C17" t="n">
-        <v>32.58322455624739</v>
+        <v>32.11100391050468</v>
       </c>
       <c r="D17" t="n">
-        <v>37.77765165941727</v>
+        <v>37.30543101367455</v>
       </c>
     </row>
     <row r="18">
@@ -5672,7 +5672,7 @@
         <v>4.815472489330605</v>
       </c>
       <c r="C18" t="n">
-        <v>35.31346492175777</v>
+        <v>34.77841242294325</v>
       </c>
       <c r="D18" t="n">
         <v>32.1031499288707</v>
@@ -5700,7 +5700,7 @@
         <v>4.707480241863455</v>
       </c>
       <c r="C20" t="n">
-        <v>39.67733346713483</v>
+        <v>39.00483628972577</v>
       </c>
       <c r="D20" t="n">
         <v>16.13993225781756</v>
@@ -5711,13 +5711,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>18.07585335480817</v>
+        <v>18.06145476456269</v>
       </c>
       <c r="C21" t="n">
-        <v>117.9234242670819</v>
+        <v>117.829490606909</v>
       </c>
       <c r="D21" t="n">
-        <v>6.886039373260256</v>
+        <v>6.880554196023881</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.8787052530299</v>
+        <v>7.868707849538185</v>
       </c>
       <c r="C2" t="n">
-        <v>2.610467145592269</v>
+        <v>3.346777923777377</v>
       </c>
       <c r="D2" t="n">
-        <v>16.79770321966293</v>
+        <v>25.79934791990193</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.64553232550467</v>
+        <v>18.68756755033803</v>
       </c>
       <c r="C3" t="n">
-        <v>15.09437095279471</v>
+        <v>13.19959788359837</v>
       </c>
       <c r="D3" t="n">
-        <v>36.29030388748335</v>
+        <v>66.37105354560562</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>24.78520254141498</v>
+        <v>25.37228766855457</v>
       </c>
       <c r="C4" t="n">
-        <v>39.70482240285375</v>
+        <v>27.2101193709046</v>
       </c>
       <c r="D4" t="n">
-        <v>38.41578766717769</v>
+        <v>59.83163208761761</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>22.2856728864026</v>
+        <v>23.16924582022473</v>
       </c>
       <c r="C5" t="n">
-        <v>44.27682146153116</v>
+        <v>31.21957699504858</v>
       </c>
       <c r="D5" t="n">
-        <v>30.99868376159304</v>
+        <v>38.23907308041327</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>11.63272854762046</v>
+        <v>13.92707293244525</v>
       </c>
       <c r="C6" t="n">
-        <v>30.99377502307181</v>
+        <v>21.61513920440203</v>
       </c>
       <c r="D6" t="n">
-        <v>30.67176177607885</v>
+        <v>31.83905979642831</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>5.210135066437822</v>
+        <v>5.809001166028376</v>
       </c>
       <c r="C7" t="n">
-        <v>17.12757044828985</v>
+        <v>16.10949807898591</v>
       </c>
       <c r="D7" t="n">
-        <v>31.4404702285041</v>
+        <v>31.02126395879071</v>
       </c>
     </row>
     <row r="8">
@@ -5843,7 +5843,7 @@
         <v>4.840016181936775</v>
       </c>
       <c r="C8" t="n">
-        <v>18.77592484372025</v>
+        <v>18.44213062427633</v>
       </c>
       <c r="D8" t="n">
         <v>30.12492830481337</v>
@@ -5857,10 +5857,10 @@
         <v>4.881249585515139</v>
       </c>
       <c r="C9" t="n">
-        <v>22.18749811597791</v>
+        <v>22.2984356065578</v>
       </c>
       <c r="D9" t="n">
-        <v>30.28593492830985</v>
+        <v>29.84218496599028</v>
       </c>
     </row>
     <row r="10">
@@ -5868,10 +5868,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.412955930589413</v>
+        <v>4.270602513473626</v>
       </c>
       <c r="C10" t="n">
-        <v>21.35301256736813</v>
+        <v>21.49536598448391</v>
       </c>
       <c r="D10" t="n">
         <v>33.73775985644164</v>
@@ -5885,10 +5885,10 @@
         <v>3.731623023842126</v>
       </c>
       <c r="C11" t="n">
-        <v>20.61277479836603</v>
+        <v>20.25738212942868</v>
       </c>
       <c r="D11" t="n">
-        <v>34.29539255245382</v>
+        <v>34.47308888692249</v>
       </c>
     </row>
     <row r="12">
@@ -5899,10 +5899,10 @@
         <v>3.037527396939631</v>
       </c>
       <c r="C12" t="n">
-        <v>19.96089432274615</v>
+        <v>20.17786056538469</v>
       </c>
       <c r="D12" t="n">
-        <v>32.32797015314322</v>
+        <v>32.11100391050467</v>
       </c>
     </row>
     <row r="13">
@@ -5913,7 +5913,7 @@
         <v>2.341468274628643</v>
       </c>
       <c r="C13" t="n">
-        <v>19.25207248027995</v>
+        <v>18.99190933865455</v>
       </c>
       <c r="D13" t="n">
         <v>30.17892442854696</v>
@@ -5927,7 +5927,7 @@
         <v>1.536435157146258</v>
       </c>
       <c r="C14" t="n">
-        <v>17.8226478228966</v>
+        <v>17.51536079146734</v>
       </c>
       <c r="D14" t="n">
         <v>29.80684204863741</v>
@@ -5958,7 +5958,7 @@
         <v>15.70599977254047</v>
       </c>
       <c r="D16" t="n">
-        <v>26.45221014322606</v>
+        <v>26.03889435973815</v>
       </c>
     </row>
     <row r="17">
@@ -5972,7 +5972,7 @@
         <v>16.52772260099505</v>
       </c>
       <c r="D17" t="n">
-        <v>24.0832529328785</v>
+        <v>23.61103228713579</v>
       </c>
     </row>
     <row r="18">
@@ -5980,7 +5980,7 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1.070104997629023</v>
+        <v>1.605157496443535</v>
       </c>
       <c r="C18" t="n">
         <v>17.65673246087889</v>
@@ -6022,13 +6022,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.069077266871918</v>
+        <v>7.061060765604214</v>
       </c>
       <c r="C21" t="n">
-        <v>67.15623403528321</v>
+        <v>66.19744467753951</v>
       </c>
       <c r="D21" t="n">
-        <v>5.301807950153938</v>
+        <v>5.295795574203161</v>
       </c>
     </row>
   </sheetData>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.159084185816988</v>
+        <v>6.87616092054466</v>
       </c>
       <c r="C2" t="n">
-        <v>3.422372497004381</v>
+        <v>7.013605599139213</v>
       </c>
       <c r="D2" t="n">
-        <v>25.94955531865169</v>
+        <v>26.5032610238469</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>19.21771131063132</v>
+        <v>24.47497026687298</v>
       </c>
       <c r="C3" t="n">
-        <v>11.85460352878024</v>
+        <v>13.12596680577985</v>
       </c>
       <c r="D3" t="n">
-        <v>41.95498814098744</v>
+        <v>72.39898444968104</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>29.82647700272235</v>
+        <v>32.31520743298801</v>
       </c>
       <c r="C4" t="n">
-        <v>38.5817030291954</v>
+        <v>31.00064725700153</v>
       </c>
       <c r="D4" t="n">
-        <v>49.05989627662161</v>
+        <v>81.82179891504191</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>31.6122760767473</v>
+        <v>32.29949946972007</v>
       </c>
       <c r="C5" t="n">
-        <v>62.73367830137119</v>
+        <v>43.12326790904115</v>
       </c>
       <c r="D5" t="n">
-        <v>38.38633523605029</v>
+        <v>52.54804586981054</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>22.70193391300324</v>
+        <v>24.11074186859742</v>
       </c>
       <c r="C6" t="n">
-        <v>54.94351026817275</v>
+        <v>38.15856976866503</v>
       </c>
       <c r="D6" t="n">
-        <v>34.29441080474959</v>
+        <v>36.99127174831558</v>
       </c>
     </row>
     <row r="7">
@@ -6137,10 +6137,10 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>10.30049691295753</v>
+        <v>12.21686843164731</v>
       </c>
       <c r="C7" t="n">
-        <v>33.83593462686632</v>
+        <v>25.33203601268044</v>
       </c>
       <c r="D7" t="n">
         <v>33.89582123682538</v>
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5.591053175685585</v>
+        <v>5.9248473951295</v>
       </c>
       <c r="C8" t="n">
-        <v>21.52972715413255</v>
+        <v>20.61179305066178</v>
       </c>
       <c r="D8" t="n">
-        <v>32.04424506661589</v>
+        <v>32.21114217633784</v>
       </c>
     </row>
     <row r="9">
@@ -6165,13 +6165,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.214062057254808</v>
+        <v>5.103124566674919</v>
       </c>
       <c r="C9" t="n">
         <v>23.40781051235669</v>
       </c>
       <c r="D9" t="n">
-        <v>31.72812230584841</v>
+        <v>30.95155987178918</v>
       </c>
     </row>
     <row r="10">
@@ -6179,7 +6179,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.840016181936776</v>
+        <v>4.697662764820988</v>
       </c>
       <c r="C10" t="n">
         <v>25.0542014123786</v>
@@ -6196,10 +6196,10 @@
         <v>4.08701569277947</v>
       </c>
       <c r="C11" t="n">
-        <v>23.63361248433346</v>
+        <v>23.45591614986479</v>
       </c>
       <c r="D11" t="n">
-        <v>34.82848155585983</v>
+        <v>35.36157055926586</v>
       </c>
     </row>
     <row r="12">
@@ -6213,7 +6213,7 @@
         <v>22.34752299177014</v>
       </c>
       <c r="D12" t="n">
-        <v>33.41280136633594</v>
+        <v>32.97886888105885</v>
       </c>
     </row>
     <row r="13">
@@ -6238,10 +6238,10 @@
         <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>19.97365704290136</v>
+        <v>19.66637001147211</v>
       </c>
       <c r="D14" t="n">
-        <v>29.80684204863741</v>
+        <v>30.11412908006666</v>
       </c>
     </row>
     <row r="15">
@@ -6255,7 +6255,7 @@
         <v>17.91689560250429</v>
       </c>
       <c r="D15" t="n">
-        <v>28.66703296400686</v>
+        <v>28.30869505195678</v>
       </c>
     </row>
     <row r="16">
@@ -6269,7 +6269,7 @@
         <v>16.53263133951629</v>
       </c>
       <c r="D16" t="n">
-        <v>26.86552592671396</v>
+        <v>26.45221014322606</v>
       </c>
     </row>
     <row r="17">
@@ -6297,7 +6297,7 @@
         <v>17.65673246087889</v>
       </c>
       <c r="D18" t="n">
-        <v>20.86704745376595</v>
+        <v>20.33199495495144</v>
       </c>
     </row>
     <row r="19">
@@ -6305,7 +6305,7 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>0.6018113427032947</v>
+        <v>1.203622685406589</v>
       </c>
       <c r="C19" t="n">
         <v>18.65615162380213</v>
@@ -6325,7 +6325,7 @@
         <v>19.50241814486288</v>
       </c>
       <c r="D20" t="n">
-        <v>10.08745766113597</v>
+        <v>10.75995483854504</v>
       </c>
     </row>
     <row r="21">
@@ -6333,13 +6333,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.29877672404931</v>
+        <v>7.287092513710725</v>
       </c>
       <c r="C21" t="n">
-        <v>77.54950269302391</v>
+        <v>76.51447139396262</v>
       </c>
       <c r="D21" t="n">
-        <v>6.386429633543146</v>
+        <v>6.376205949496884</v>
       </c>
     </row>
   </sheetData>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.849252821902496</v>
+        <v>5.892449720889356</v>
       </c>
       <c r="C2" t="n">
-        <v>2.495602664195392</v>
+        <v>5.579272203234622</v>
       </c>
       <c r="D2" t="n">
-        <v>23.40290177383547</v>
+        <v>31.28437234352886</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.54521413322225</v>
+        <v>24.1755372170777</v>
       </c>
       <c r="C3" t="n">
-        <v>12.78726384781471</v>
+        <v>21.8684301120977</v>
       </c>
       <c r="D3" t="n">
-        <v>53.61324212891832</v>
+        <v>76.80212290322798</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>34.66354794154638</v>
+        <v>41.14700978039232</v>
       </c>
       <c r="C4" t="n">
-        <v>33.23412328416303</v>
+        <v>32.1492920709703</v>
       </c>
       <c r="D4" t="n">
-        <v>59.6657167255999</v>
+        <v>98.97489480364219</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>39.1226460142354</v>
+        <v>41.74882112309562</v>
       </c>
       <c r="C5" t="n">
-        <v>67.29880512611886</v>
+        <v>50.97724954301564</v>
       </c>
       <c r="D5" t="n">
-        <v>47.95837535245669</v>
+        <v>71.05399009486291</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>34.29441080474959</v>
+        <v>35.01894061048373</v>
       </c>
       <c r="C6" t="n">
-        <v>80.94607996285377</v>
+        <v>55.50703345041042</v>
       </c>
       <c r="D6" t="n">
-        <v>38.68184129502858</v>
+        <v>45.08185457901354</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>19.58292145661112</v>
+        <v>21.55917958525995</v>
       </c>
       <c r="C7" t="n">
-        <v>60.06626978893259</v>
+        <v>42.22006002113408</v>
       </c>
       <c r="D7" t="n">
-        <v>36.71049190490098</v>
+        <v>37.42913122440964</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.845546815263761</v>
+        <v>10.01382658331747</v>
       </c>
       <c r="C8" t="n">
-        <v>35.04839304161113</v>
+        <v>28.20561154301086</v>
       </c>
       <c r="D8" t="n">
-        <v>34.04701038327938</v>
+        <v>34.46425315758427</v>
       </c>
     </row>
     <row r="9">
@@ -6476,13 +6476,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.657812019574366</v>
+        <v>5.768749510154256</v>
       </c>
       <c r="C9" t="n">
-        <v>25.95937279569415</v>
+        <v>25.07187287105504</v>
       </c>
       <c r="D9" t="n">
-        <v>33.28124717396686</v>
+        <v>32.28280975874785</v>
       </c>
     </row>
     <row r="10">
@@ -6490,13 +6490,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>5.267076433284139</v>
+        <v>5.124723016168351</v>
       </c>
       <c r="C10" t="n">
         <v>27.47420950334699</v>
       </c>
       <c r="D10" t="n">
-        <v>34.87658719336794</v>
+        <v>34.73423377625215</v>
       </c>
     </row>
     <row r="11">
@@ -6507,10 +6507,10 @@
         <v>4.442408361716816</v>
       </c>
       <c r="C11" t="n">
-        <v>26.83214650476957</v>
+        <v>27.00984283923824</v>
       </c>
       <c r="D11" t="n">
-        <v>35.18387422479719</v>
+        <v>36.07235589714055</v>
       </c>
     </row>
     <row r="12">
@@ -6524,7 +6524,7 @@
         <v>25.16808414607123</v>
       </c>
       <c r="D12" t="n">
-        <v>34.49763257952867</v>
+        <v>33.62976760897449</v>
       </c>
     </row>
     <row r="13">
@@ -6532,7 +6532,7 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.861794557879452</v>
+        <v>2.601631416254048</v>
       </c>
       <c r="C13" t="n">
         <v>23.67484588791184</v>
@@ -6549,7 +6549,7 @@
         <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>22.12466626290612</v>
+        <v>21.81737923147687</v>
       </c>
       <c r="D14" t="n">
         <v>30.11412908006666</v>
@@ -6563,10 +6563,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>20.0669230748048</v>
+        <v>19.35024725070463</v>
       </c>
       <c r="D15" t="n">
-        <v>29.02537087605695</v>
+        <v>28.66703296400686</v>
       </c>
     </row>
     <row r="16">
@@ -6594,7 +6594,7 @@
         <v>17.47216389248049</v>
       </c>
       <c r="D17" t="n">
-        <v>24.55547357862122</v>
+        <v>24.0832529328785</v>
       </c>
     </row>
     <row r="18">
@@ -6608,7 +6608,7 @@
         <v>18.1917849596934</v>
       </c>
       <c r="D18" t="n">
-        <v>21.40209995258047</v>
+        <v>20.86704745376595</v>
       </c>
     </row>
     <row r="19">
@@ -6630,7 +6630,7 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>0</v>
+        <v>0.672497177409065</v>
       </c>
       <c r="C20" t="n">
         <v>19.50241814486288</v>
@@ -6644,13 +6644,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.518216181043014</v>
+        <v>7.50235094051005</v>
       </c>
       <c r="C21" t="n">
-        <v>87.39926310462504</v>
+        <v>86.27703581586557</v>
       </c>
       <c r="D21" t="n">
-        <v>7.518216181043014</v>
+        <v>7.50235094051005</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_surface_area_iteration_94_growth_param_0.5.xlsx
+++ b/output/yearly_surface_area_iteration_94_growth_param_0.5.xlsx
@@ -735,10 +735,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>10.84497652914982</v>
+        <v>10.84497638133586</v>
       </c>
       <c r="C21" t="n">
-        <v>37.78907262812417</v>
+        <v>37.7890721130698</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7.063674732055801</v>
+        <v>1.382300767579509</v>
       </c>
       <c r="C2" t="n">
-        <v>9.354092126063609</v>
+        <v>3.3703398686793</v>
       </c>
       <c r="D2" t="n">
-        <v>40.50887377263189</v>
+        <v>9.267698328089891</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>21.99114857512855</v>
+        <v>11.38336463074177</v>
       </c>
       <c r="C3" t="n">
-        <v>21.73098543350315</v>
+        <v>37.50767104074939</v>
       </c>
       <c r="D3" t="n">
-        <v>83.49273350766998</v>
+        <v>42.14152020479434</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>44.43979158043612</v>
+        <v>18.96540215063988</v>
       </c>
       <c r="C4" t="n">
-        <v>44.75885958431633</v>
+        <v>111.5844623169882</v>
       </c>
       <c r="D4" t="n">
-        <v>114.328447150358</v>
+        <v>52.32715263635499</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>51.93445355465628</v>
+        <v>17.45056544298706</v>
       </c>
       <c r="C5" t="n">
-        <v>55.02695882303374</v>
+        <v>158.135011461555</v>
       </c>
       <c r="D5" t="n">
-        <v>88.82362354173019</v>
+        <v>38.65631585471817</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>46.57116584635595</v>
+        <v>11.18996033300515</v>
       </c>
       <c r="C6" t="n">
-        <v>69.15234479173684</v>
+        <v>127.7990074003286</v>
       </c>
       <c r="D6" t="n">
-        <v>56.79508643838223</v>
+        <v>28.86043726174349</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>31.91956310817654</v>
+        <v>5.988660995905543</v>
       </c>
       <c r="C7" t="n">
-        <v>62.34196096737671</v>
+        <v>67.07300315414209</v>
       </c>
       <c r="D7" t="n">
-        <v>41.56130731158447</v>
+        <v>29.52409870981433</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>17.02350519163969</v>
+        <v>6.00829594999048</v>
       </c>
       <c r="C8" t="n">
-        <v>42.55876297909923</v>
+        <v>31.79389940203295</v>
       </c>
       <c r="D8" t="n">
-        <v>37.05115835827462</v>
+        <v>30.37527396939631</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>8.098436812331936</v>
+        <v>5.768749510154256</v>
       </c>
       <c r="C9" t="n">
-        <v>30.84062238120929</v>
+        <v>30.7296848906294</v>
       </c>
       <c r="D9" t="n">
-        <v>33.72499713628642</v>
+        <v>35.49999698556465</v>
       </c>
     </row>
     <row r="10">
@@ -892,13 +892,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>5.551783267515713</v>
+        <v>3.4164820107789</v>
       </c>
       <c r="C10" t="n">
-        <v>29.46715734296802</v>
+        <v>29.75186417719959</v>
       </c>
       <c r="D10" t="n">
-        <v>35.3036474447153</v>
+        <v>37.5813021185679</v>
       </c>
     </row>
     <row r="11">
@@ -906,13 +906,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.797801030654161</v>
+        <v>2.665445017030089</v>
       </c>
       <c r="C11" t="n">
-        <v>29.852984190737</v>
+        <v>30.56376952861169</v>
       </c>
       <c r="D11" t="n">
-        <v>36.60544490054656</v>
+        <v>37.31623023842126</v>
       </c>
     </row>
     <row r="12">
@@ -920,13 +920,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.688426124855267</v>
+        <v>2.169662426385451</v>
       </c>
       <c r="C12" t="n">
-        <v>28.42257778564941</v>
+        <v>23.43235420496287</v>
       </c>
       <c r="D12" t="n">
-        <v>34.28066633689012</v>
+        <v>37.75212621910684</v>
       </c>
     </row>
     <row r="13">
@@ -934,13 +934,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.861794557879452</v>
+        <v>1.821141991377834</v>
       </c>
       <c r="C13" t="n">
-        <v>26.27647730416588</v>
+        <v>20.03256190515617</v>
       </c>
       <c r="D13" t="n">
-        <v>32.5203927031756</v>
+        <v>35.90251354430586</v>
       </c>
     </row>
     <row r="14">
@@ -948,13 +948,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>1.536435157146258</v>
       </c>
       <c r="C14" t="n">
-        <v>23.66110142005238</v>
+        <v>19.97365704290136</v>
       </c>
       <c r="D14" t="n">
-        <v>30.42141611149592</v>
+        <v>27.3485457972034</v>
       </c>
     </row>
     <row r="15">
@@ -965,10 +965,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>21.50027472300514</v>
+        <v>20.78359889890498</v>
       </c>
       <c r="D15" t="n">
-        <v>29.02537087605695</v>
+        <v>25.44199175555609</v>
       </c>
     </row>
     <row r="16">
@@ -976,13 +976,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>1.653263133951629</v>
       </c>
       <c r="C16" t="n">
-        <v>19.01252604044373</v>
+        <v>22.7323680918349</v>
       </c>
       <c r="D16" t="n">
-        <v>27.27884171020187</v>
+        <v>22.31905230834699</v>
       </c>
     </row>
     <row r="17">
@@ -990,13 +990,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>1.416661937228147</v>
       </c>
       <c r="C17" t="n">
+        <v>24.55547357862122</v>
+      </c>
+      <c r="D17" t="n">
         <v>17.9443845382232</v>
-      </c>
-      <c r="D17" t="n">
-        <v>24.0832529328785</v>
       </c>
     </row>
     <row r="18">
@@ -1004,13 +1004,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>0.5350524988145117</v>
+        <v>1.605157496443535</v>
       </c>
       <c r="C18" t="n">
-        <v>18.1917849596934</v>
+        <v>26.21757244191107</v>
       </c>
       <c r="D18" t="n">
-        <v>20.86704745376595</v>
+        <v>11.77115497391926</v>
       </c>
     </row>
     <row r="19">
@@ -1018,13 +1018,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>0</v>
+        <v>10.83260416865931</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>84.25358797846125</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>3.009056713516474</v>
       </c>
     </row>
     <row r="20">
@@ -1035,10 +1035,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1046,13 +1046,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.705141195158252</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>95.35112229008337</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>8.668283844553033</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8.212319546024569</v>
+        <v>1.693514789825748</v>
       </c>
       <c r="C2" t="n">
-        <v>10.27300797723862</v>
+        <v>6.1094159635279</v>
       </c>
       <c r="D2" t="n">
-        <v>47.46651975262904</v>
+        <v>11.22923024117502</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>22.82563412373834</v>
+        <v>7.873616588059419</v>
       </c>
       <c r="C3" t="n">
-        <v>29.46715734296801</v>
+        <v>23.39013905368026</v>
       </c>
       <c r="D3" t="n">
-        <v>94.89082435397546</v>
+        <v>39.80986940720816</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>42.89550244165589</v>
+        <v>20.71389481190345</v>
       </c>
       <c r="C4" t="n">
-        <v>49.68526956422683</v>
+        <v>102.7654226897391</v>
       </c>
       <c r="D4" t="n">
-        <v>128.5971682838812</v>
+        <v>61.1717177039145</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>59.37119241432587</v>
+        <v>22.87472150895069</v>
       </c>
       <c r="C5" t="n">
-        <v>68.25600913775951</v>
+        <v>183.5622770015474</v>
       </c>
       <c r="D5" t="n">
-        <v>106.6423443738098</v>
+        <v>48.17926858591223</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>57.72087452348698</v>
+        <v>16.90569546713008</v>
       </c>
       <c r="C6" t="n">
-        <v>78.32972233103602</v>
+        <v>192.080901831297</v>
       </c>
       <c r="D6" t="n">
-        <v>70.52090109145691</v>
+        <v>34.09315252537899</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>43.23813239043802</v>
+        <v>9.282424543653592</v>
       </c>
       <c r="C7" t="n">
-        <v>80.36783056505237</v>
+        <v>125.5822210841392</v>
       </c>
       <c r="D7" t="n">
-        <v>47.84940135728529</v>
+        <v>31.56024344842221</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>25.61870634232051</v>
+        <v>6.508987279156353</v>
       </c>
       <c r="C8" t="n">
-        <v>62.50296759087318</v>
+        <v>59.58226817073891</v>
       </c>
       <c r="D8" t="n">
-        <v>39.30426933952106</v>
+        <v>31.46010518258904</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>12.31406145436774</v>
+        <v>6.101561981893925</v>
       </c>
       <c r="C9" t="n">
-        <v>41.82343394861835</v>
+        <v>35.61093447614454</v>
       </c>
       <c r="D9" t="n">
-        <v>35.61093447614454</v>
+        <v>36.0546844384641</v>
       </c>
     </row>
     <row r="10">
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>6.690610604442014</v>
+        <v>4.128249096357838</v>
       </c>
       <c r="C10" t="n">
-        <v>33.31069960509428</v>
+        <v>33.88011327355743</v>
       </c>
       <c r="D10" t="n">
-        <v>35.58835427894688</v>
+        <v>38.00836236991527</v>
       </c>
     </row>
     <row r="11">
@@ -1217,13 +1217,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>5.153193699591506</v>
+        <v>2.843141351498762</v>
       </c>
       <c r="C11" t="n">
-        <v>32.51842920776709</v>
+        <v>33.58460721457913</v>
       </c>
       <c r="D11" t="n">
-        <v>37.13853390395258</v>
+        <v>38.20471191076462</v>
       </c>
     </row>
     <row r="12">
@@ -1231,13 +1231,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.905392367493811</v>
+        <v>2.169662426385451</v>
       </c>
       <c r="C12" t="n">
-        <v>31.02617269731195</v>
+        <v>27.98864530037232</v>
       </c>
       <c r="D12" t="n">
-        <v>34.71459882216721</v>
+        <v>38.18605870438393</v>
       </c>
     </row>
     <row r="13">
@@ -1245,13 +1245,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.861794557879452</v>
+        <v>1.560978849752429</v>
       </c>
       <c r="C13" t="n">
-        <v>29.13827186204534</v>
+        <v>22.63419332141022</v>
       </c>
       <c r="D13" t="n">
-        <v>33.04071898642641</v>
+        <v>36.68300296918207</v>
       </c>
     </row>
     <row r="14">
@@ -1259,13 +1259,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>2.151009220004762</v>
+        <v>1.229148125717007</v>
       </c>
       <c r="C14" t="n">
-        <v>25.81211064005714</v>
+        <v>21.20280516861837</v>
       </c>
       <c r="D14" t="n">
-        <v>30.72870314292517</v>
+        <v>28.88498095434966</v>
       </c>
     </row>
     <row r="15">
@@ -1276,10 +1276,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>23.29196428325557</v>
+        <v>22.93362637120549</v>
       </c>
       <c r="D15" t="n">
-        <v>29.38370878810703</v>
+        <v>25.44199175555609</v>
       </c>
     </row>
     <row r="16">
@@ -1290,10 +1290,10 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>20.66578917439536</v>
+        <v>25.21226279276234</v>
       </c>
       <c r="D16" t="n">
-        <v>27.27884171020187</v>
+        <v>21.90573652485908</v>
       </c>
     </row>
     <row r="17">
@@ -1301,13 +1301,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>1.416661937228147</v>
       </c>
       <c r="C17" t="n">
-        <v>18.88882582970863</v>
+        <v>26.44435616159209</v>
       </c>
       <c r="D17" t="n">
-        <v>24.55547357862122</v>
+        <v>16.99994324673777</v>
       </c>
     </row>
     <row r="18">
@@ -1315,13 +1315,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>0.5350524988145117</v>
+        <v>8.560839981032187</v>
       </c>
       <c r="C18" t="n">
-        <v>18.72683745850791</v>
+        <v>50.2949348885641</v>
       </c>
       <c r="D18" t="n">
-        <v>20.86704745376595</v>
+        <v>9.63094497866121</v>
       </c>
     </row>
     <row r="19">
@@ -1332,10 +1332,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>45.7376620454504</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>1.805434028109884</v>
       </c>
     </row>
     <row r="20">
@@ -1346,10 +1346,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1357,13 +1357,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.893566869812262</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>104.5897610250125</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>9.866958587265328</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>9.547496423800231</v>
+        <v>0.9100801218367931</v>
       </c>
       <c r="C2" t="n">
-        <v>5.883613991551134</v>
+        <v>2.630102099677205</v>
       </c>
       <c r="D2" t="n">
-        <v>37.474291618805</v>
+        <v>7.675303551801563</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>25.00020528864503</v>
+        <v>7.736171909464865</v>
       </c>
       <c r="C3" t="n">
-        <v>34.30226478638355</v>
+        <v>25.18182861393069</v>
       </c>
       <c r="D3" t="n">
-        <v>106.897598776914</v>
+        <v>40.74743846476387</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>42.37223091529233</v>
+        <v>22.65382827549515</v>
       </c>
       <c r="C4" t="n">
-        <v>60.31661545351554</v>
+        <v>94.77595987257858</v>
       </c>
       <c r="D4" t="n">
-        <v>141.5896174018835</v>
+        <v>66.71073825127502</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>61.26105674500098</v>
+        <v>22.58019719767664</v>
       </c>
       <c r="C5" t="n">
-        <v>78.22074833586463</v>
+        <v>210.9530379500334</v>
       </c>
       <c r="D5" t="n">
-        <v>125.0010264432252</v>
+        <v>53.92249265575607</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>67.42152358914971</v>
+        <v>13.08178815908875</v>
       </c>
       <c r="C6" t="n">
-        <v>92.0957886399848</v>
+        <v>238.4105577424082</v>
       </c>
       <c r="D6" t="n">
-        <v>83.9247024975386</v>
+        <v>34.81768233111314</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>54.91602133245383</v>
+        <v>4.311835917051991</v>
       </c>
       <c r="C7" t="n">
-        <v>94.74061695522569</v>
+        <v>115.8207036608132</v>
       </c>
       <c r="D7" t="n">
-        <v>55.69454726192155</v>
+        <v>33.0574086973986</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>34.71459882216722</v>
+        <v>4.172427743048944</v>
       </c>
       <c r="C8" t="n">
-        <v>82.78096642209104</v>
+        <v>46.64774216728719</v>
       </c>
       <c r="D8" t="n">
-        <v>42.22496875965531</v>
+        <v>36.21667280966483</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>18.08281096452199</v>
+        <v>2.884374755077128</v>
       </c>
       <c r="C9" t="n">
-        <v>57.46562012038278</v>
+        <v>25.84843530511426</v>
       </c>
       <c r="D9" t="n">
-        <v>37.49687181600267</v>
+        <v>39.93749660876023</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8.825911861178826</v>
+        <v>1.992947839621025</v>
       </c>
       <c r="C10" t="n">
-        <v>40.9977841293468</v>
+        <v>26.33538216642069</v>
       </c>
       <c r="D10" t="n">
-        <v>36.15776794741003</v>
+        <v>29.89421759431538</v>
       </c>
     </row>
     <row r="11">
@@ -1528,13 +1528,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>5.686282702997524</v>
+        <v>1.599267010218054</v>
       </c>
       <c r="C11" t="n">
-        <v>35.36157055926586</v>
+        <v>22.38973814305275</v>
       </c>
       <c r="D11" t="n">
-        <v>37.6716229073586</v>
+        <v>30.56376952861169</v>
       </c>
     </row>
     <row r="12">
@@ -1542,13 +1542,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>4.122358610132356</v>
+        <v>1.084831213192725</v>
       </c>
       <c r="C12" t="n">
-        <v>33.62976760897449</v>
+        <v>18.44213062427633</v>
       </c>
       <c r="D12" t="n">
-        <v>35.1485313074443</v>
+        <v>29.94134148411922</v>
       </c>
     </row>
     <row r="13">
@@ -1556,13 +1556,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>3.121957699504857</v>
+        <v>0.7804894248762143</v>
       </c>
       <c r="C13" t="n">
-        <v>31.73990327829938</v>
+        <v>17.43093048890212</v>
       </c>
       <c r="D13" t="n">
-        <v>33.56104526967722</v>
+        <v>23.93500902953724</v>
       </c>
     </row>
     <row r="14">
@@ -1570,13 +1570,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>2.151009220004762</v>
+        <v>0.921861094287755</v>
       </c>
       <c r="C14" t="n">
-        <v>28.27040689149115</v>
+        <v>19.0517959486136</v>
       </c>
       <c r="D14" t="n">
-        <v>30.72870314292517</v>
+        <v>21.20280516861837</v>
       </c>
     </row>
     <row r="15">
@@ -1584,13 +1584,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.433351648200343</v>
+        <v>0.7166758241001715</v>
       </c>
       <c r="C15" t="n">
-        <v>25.083653843506</v>
+        <v>21.14193681095506</v>
       </c>
       <c r="D15" t="n">
-        <v>29.74204670015712</v>
+        <v>18.27523351455437</v>
       </c>
     </row>
     <row r="16">
@@ -1598,13 +1598,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>0.8266315669758143</v>
       </c>
       <c r="C16" t="n">
-        <v>21.90573652485908</v>
+        <v>22.31905230834699</v>
       </c>
       <c r="D16" t="n">
-        <v>27.27884171020187</v>
+        <v>14.46605242207675</v>
       </c>
     </row>
     <row r="17">
@@ -1612,13 +1612,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>6.611089040398022</v>
       </c>
       <c r="C17" t="n">
-        <v>19.83326712119407</v>
+        <v>43.44429940832985</v>
       </c>
       <c r="D17" t="n">
-        <v>24.55547357862122</v>
+        <v>8.02775097762617</v>
       </c>
     </row>
     <row r="18">
@@ -1626,13 +1626,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>0.5350524988145117</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>18.72683745850791</v>
+        <v>39.59388491227386</v>
       </c>
       <c r="D18" t="n">
-        <v>20.86704745376595</v>
+        <v>1.070104997629023</v>
       </c>
     </row>
     <row r="19">
@@ -1643,10 +1643,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>19.25796296650543</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1657,10 +1657,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1668,13 +1668,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8.066190094776502</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>112.926661326871</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>11.09101138031769</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8.672759219316323</v>
+        <v>0.8354672963140357</v>
       </c>
       <c r="C2" t="n">
-        <v>3.906374115198058</v>
+        <v>6.616979526623502</v>
       </c>
       <c r="D2" t="n">
-        <v>30.49995592783566</v>
+        <v>10.21312136727957</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>30.0709321810798</v>
+        <v>5.394703634836223</v>
       </c>
       <c r="C3" t="n">
-        <v>46.05869354473911</v>
+        <v>16.90569546713007</v>
       </c>
       <c r="D3" t="n">
-        <v>116.2192932287374</v>
+        <v>37.60093707265283</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>29.43083267791088</v>
+        <v>19.13131751265759</v>
       </c>
       <c r="C4" t="n">
-        <v>73.20696281027615</v>
+        <v>78.5162543948429</v>
       </c>
       <c r="D4" t="n">
-        <v>138.0926320793563</v>
+        <v>71.45847014901258</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>37.9690924617454</v>
+        <v>28.02889695624644</v>
       </c>
       <c r="C5" t="n">
-        <v>55.02695882303374</v>
+        <v>194.5333075965055</v>
       </c>
       <c r="D5" t="n">
-        <v>84.94572010995527</v>
+        <v>64.91806694332035</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>34.09315252537899</v>
+        <v>20.40758952817845</v>
       </c>
       <c r="C6" t="n">
-        <v>62.39006660488482</v>
+        <v>290.2546905082738</v>
       </c>
       <c r="D6" t="n">
-        <v>36.66925850132262</v>
+        <v>42.0629803884546</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>22.99645822427728</v>
+        <v>8.384125394267761</v>
       </c>
       <c r="C7" t="n">
-        <v>58.20978488020188</v>
+        <v>221.0414773588736</v>
       </c>
       <c r="D7" t="n">
-        <v>29.64387192973244</v>
+        <v>35.57264631567892</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>12.51728322914683</v>
+        <v>4.506221962492859</v>
       </c>
       <c r="C8" t="n">
-        <v>42.30841731451629</v>
+        <v>92.46099878596459</v>
       </c>
       <c r="D8" t="n">
-        <v>27.62147165898401</v>
+        <v>37.30150402285756</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>6.323436963053704</v>
+        <v>3.217187226816797</v>
       </c>
       <c r="C9" t="n">
-        <v>31.28437234352885</v>
+        <v>39.2718716652809</v>
       </c>
       <c r="D9" t="n">
-        <v>27.5124976638126</v>
+        <v>40.71405904281946</v>
       </c>
     </row>
     <row r="10">
@@ -1825,13 +1825,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.128249096357838</v>
+        <v>2.135301256736813</v>
       </c>
       <c r="C10" t="n">
-        <v>27.75891633757857</v>
+        <v>29.32480392585223</v>
       </c>
       <c r="D10" t="n">
-        <v>29.46715734296802</v>
+        <v>31.74481201682062</v>
       </c>
     </row>
     <row r="11">
@@ -1839,13 +1839,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>3.020837685967435</v>
+        <v>1.421570675749381</v>
       </c>
       <c r="C11" t="n">
-        <v>26.83214650476957</v>
+        <v>25.9436648324262</v>
       </c>
       <c r="D11" t="n">
-        <v>28.07602084605028</v>
+        <v>31.27455486648638</v>
       </c>
     </row>
     <row r="12">
@@ -1853,13 +1853,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2.386628669023996</v>
+        <v>0.8678649705541803</v>
       </c>
       <c r="C12" t="n">
-        <v>25.81898287398687</v>
+        <v>21.26269177857742</v>
       </c>
       <c r="D12" t="n">
-        <v>27.33774657245668</v>
+        <v>30.8092064546734</v>
       </c>
     </row>
     <row r="13">
@@ -1867,13 +1867,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>1.560978849752429</v>
+        <v>0.7804894248762143</v>
       </c>
       <c r="C13" t="n">
-        <v>23.41468274628643</v>
+        <v>20.55288818840698</v>
       </c>
       <c r="D13" t="n">
-        <v>25.49598787928967</v>
+        <v>23.93500902953724</v>
       </c>
     </row>
     <row r="14">
@@ -1881,13 +1881,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0.921861094287755</v>
+        <v>0.6145740628585034</v>
       </c>
       <c r="C14" t="n">
         <v>20.89551813718911</v>
       </c>
       <c r="D14" t="n">
-        <v>24.89024954576939</v>
+        <v>21.20280516861837</v>
       </c>
     </row>
     <row r="15">
@@ -1898,10 +1898,10 @@
         <v>0.7166758241001715</v>
       </c>
       <c r="C15" t="n">
-        <v>18.27523351455437</v>
+        <v>23.65030219530566</v>
       </c>
       <c r="D15" t="n">
-        <v>22.93362637120549</v>
+        <v>17.91689560250429</v>
       </c>
     </row>
     <row r="16">
@@ -1909,13 +1909,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>0.4133157834879072</v>
+        <v>4.959789401854886</v>
       </c>
       <c r="C16" t="n">
-        <v>16.94594712300419</v>
+        <v>37.19842051391164</v>
       </c>
       <c r="D16" t="n">
-        <v>20.66578917439536</v>
+        <v>12.81278928812512</v>
       </c>
     </row>
     <row r="17">
@@ -1926,10 +1926,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>16.05550195525234</v>
+        <v>46.74984392852887</v>
       </c>
       <c r="D17" t="n">
-        <v>17.9443845382232</v>
+        <v>5.194427103169874</v>
       </c>
     </row>
     <row r="18">
@@ -1940,10 +1940,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>16.58662746324986</v>
+        <v>1.070104997629023</v>
       </c>
       <c r="D18" t="n">
-        <v>13.9113649691773</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -1954,10 +1954,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>16.85071759569225</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>9.027170140549421</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1965,13 +1965,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>5.37997741927252</v>
+        <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>75.31968386981528</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>7.397468951499714</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.322054304721958</v>
+        <v>0.5232715263635499</v>
       </c>
       <c r="C2" t="n">
-        <v>2.057743188101315</v>
+        <v>3.369358120975054</v>
       </c>
       <c r="D2" t="n">
-        <v>21.39522771865074</v>
+        <v>7.669413065576083</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>30.87596529856219</v>
+        <v>4.334416114249668</v>
       </c>
       <c r="C3" t="n">
-        <v>30.38509144643878</v>
+        <v>21.56899706230243</v>
       </c>
       <c r="D3" t="n">
-        <v>115.6744232528804</v>
+        <v>37.21805546799658</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>41.86172210908399</v>
+        <v>16.11931555602838</v>
       </c>
       <c r="C4" t="n">
-        <v>96.83075781756715</v>
+        <v>63.5455836527833</v>
       </c>
       <c r="D4" t="n">
-        <v>161.7419525269578</v>
+        <v>73.75575977695013</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>42.3378697456437</v>
+        <v>29.89421759431538</v>
       </c>
       <c r="C5" t="n">
-        <v>92.72607066611126</v>
+        <v>180.3961406553514</v>
       </c>
       <c r="D5" t="n">
-        <v>106.519625910779</v>
+        <v>73.23837873681207</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>41.53970886209105</v>
+        <v>25.15728492132452</v>
       </c>
       <c r="C6" t="n">
-        <v>75.43160310809944</v>
+        <v>315.0497105267312</v>
       </c>
       <c r="D6" t="n">
-        <v>47.13468902859362</v>
+        <v>48.5434969841878</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>21.85861263505523</v>
+        <v>9.162651323735481</v>
       </c>
       <c r="C7" t="n">
-        <v>73.12155076000668</v>
+        <v>293.9234816790441</v>
       </c>
       <c r="D7" t="n">
-        <v>32.5184292077671</v>
+        <v>38.92629647338602</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.43106935762236</v>
+        <v>4.172427743048944</v>
       </c>
       <c r="C8" t="n">
-        <v>55.07604620824605</v>
+        <v>141.2784033796372</v>
       </c>
       <c r="D8" t="n">
-        <v>28.87319998189869</v>
+        <v>39.13737222979909</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.103124566674919</v>
+        <v>2.773437264497239</v>
       </c>
       <c r="C9" t="n">
-        <v>37.27499683484289</v>
+        <v>51.58593311964863</v>
       </c>
       <c r="D9" t="n">
-        <v>28.84374755077128</v>
+        <v>40.82499653339935</v>
       </c>
     </row>
     <row r="10">
@@ -2136,13 +2136,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2.135301256736813</v>
+        <v>1.423534171157875</v>
       </c>
       <c r="C10" t="n">
-        <v>31.17539834835747</v>
+        <v>31.74481201682062</v>
       </c>
       <c r="D10" t="n">
-        <v>30.17892442854695</v>
+        <v>32.59893251951534</v>
       </c>
     </row>
     <row r="11">
@@ -2150,13 +2150,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>1.776963344686726</v>
+        <v>0.5330890034060179</v>
       </c>
       <c r="C11" t="n">
-        <v>30.38607319414302</v>
+        <v>26.83214650476957</v>
       </c>
       <c r="D11" t="n">
-        <v>29.67528785626833</v>
+        <v>32.69612554223576</v>
       </c>
     </row>
     <row r="12">
@@ -2164,13 +2164,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>1.084831213192725</v>
+        <v>0.4339324852770902</v>
       </c>
       <c r="C12" t="n">
-        <v>21.91359050649305</v>
+        <v>22.78145547704723</v>
       </c>
       <c r="D12" t="n">
-        <v>28.20561154301086</v>
+        <v>29.50740899884213</v>
       </c>
     </row>
     <row r="13">
@@ -2178,13 +2178,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0.5203262832508095</v>
+        <v>0.2601631416254048</v>
       </c>
       <c r="C13" t="n">
         <v>17.17076734727672</v>
       </c>
       <c r="D13" t="n">
-        <v>26.27647730416588</v>
+        <v>24.45533531278805</v>
       </c>
     </row>
     <row r="14">
@@ -2195,10 +2195,10 @@
         <v>0.3072870314292517</v>
       </c>
       <c r="C14" t="n">
-        <v>15.05706454003333</v>
+        <v>19.66637001147211</v>
       </c>
       <c r="D14" t="n">
-        <v>19.0517959486136</v>
+        <v>16.90078672860884</v>
       </c>
     </row>
     <row r="15">
@@ -2206,13 +2206,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>3.941717032550943</v>
       </c>
       <c r="C15" t="n">
-        <v>14.33351648200343</v>
+        <v>31.53373626040754</v>
       </c>
       <c r="D15" t="n">
-        <v>17.5585576904542</v>
+        <v>10.75013736150257</v>
       </c>
     </row>
     <row r="16">
@@ -2223,10 +2223,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>13.63942085510094</v>
+        <v>40.09163099832699</v>
       </c>
       <c r="D16" t="n">
-        <v>15.29268398905256</v>
+        <v>4.133157834879071</v>
       </c>
     </row>
     <row r="17">
@@ -2237,10 +2237,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>14.16661937228147</v>
+        <v>0.4722206457427158</v>
       </c>
       <c r="D17" t="n">
-        <v>11.8055161435679</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2251,10 +2251,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>14.44641746799181</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>7.490734983403163</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2262,13 +2262,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>4.212679398923063</v>
+        <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>65.59743635465912</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>6.018113427032947</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.750497214401069</v>
+        <v>0.6047565858160352</v>
       </c>
       <c r="C2" t="n">
-        <v>5.412375093512666</v>
+        <v>10.25337302315369</v>
       </c>
       <c r="D2" t="n">
-        <v>21.71429572253095</v>
+        <v>16.82126516456485</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>24.35716054236337</v>
+        <v>3.072870314292516</v>
       </c>
       <c r="C3" t="n">
-        <v>18.06906649666254</v>
+        <v>17.16094987023424</v>
       </c>
       <c r="D3" t="n">
-        <v>106.4607210485241</v>
+        <v>35.22510762837555</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>50.80838893788518</v>
+        <v>12.48194031179395</v>
       </c>
       <c r="C4" t="n">
-        <v>86.67163257402116</v>
+        <v>59.32112328140927</v>
       </c>
       <c r="D4" t="n">
-        <v>180.8349818791497</v>
+        <v>74.33008218393451</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>52.05717201768713</v>
+        <v>27.9798095710341</v>
       </c>
       <c r="C5" t="n">
-        <v>135.6529890343031</v>
+        <v>150.9437095279471</v>
       </c>
       <c r="D5" t="n">
-        <v>136.659280431156</v>
+        <v>81.53414683769762</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>49.06676851055134</v>
+        <v>31.43654323768712</v>
       </c>
       <c r="C6" t="n">
-        <v>110.6920536538279</v>
+        <v>304.0207568172226</v>
       </c>
       <c r="D6" t="n">
-        <v>66.09321894530378</v>
+        <v>58.20389439397641</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>33.53650157707104</v>
+        <v>16.76825078853552</v>
       </c>
       <c r="C7" t="n">
-        <v>90.30900781825558</v>
+        <v>368.6020842979862</v>
       </c>
       <c r="D7" t="n">
-        <v>37.66867766424586</v>
+        <v>43.05847256056086</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>15.52143120414207</v>
+        <v>6.175193059712437</v>
       </c>
       <c r="C8" t="n">
-        <v>75.27059648460295</v>
+        <v>245.088405626695</v>
       </c>
       <c r="D8" t="n">
-        <v>31.04286240828414</v>
+        <v>40.63944621729671</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>6.989061906533041</v>
+        <v>3.217187226816797</v>
       </c>
       <c r="C9" t="n">
-        <v>52.02968308196819</v>
+        <v>100.0656165030604</v>
       </c>
       <c r="D9" t="n">
-        <v>29.62030998483051</v>
+        <v>42.04530892977813</v>
       </c>
     </row>
     <row r="10">
@@ -2447,13 +2447,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2.847068342315751</v>
+        <v>1.70824100538945</v>
       </c>
       <c r="C10" t="n">
-        <v>37.5813021185679</v>
+        <v>43.13308538608361</v>
       </c>
       <c r="D10" t="n">
-        <v>30.89069151412589</v>
+        <v>34.16482010778901</v>
       </c>
     </row>
     <row r="11">
@@ -2461,13 +2461,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>1.776963344686726</v>
+        <v>0.5330890034060179</v>
       </c>
       <c r="C11" t="n">
-        <v>33.58460721457913</v>
+        <v>31.09685853201771</v>
       </c>
       <c r="D11" t="n">
-        <v>30.20837685967435</v>
+        <v>33.22921454564179</v>
       </c>
     </row>
     <row r="12">
@@ -2475,13 +2475,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>1.084831213192725</v>
+        <v>0.4339324852770902</v>
       </c>
       <c r="C12" t="n">
-        <v>26.68684784454105</v>
+        <v>25.60201663134832</v>
       </c>
       <c r="D12" t="n">
-        <v>28.63954402828795</v>
+        <v>30.15830772675777</v>
       </c>
     </row>
     <row r="13">
@@ -2492,10 +2492,10 @@
         <v>0.2601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>19.51223562190536</v>
+        <v>19.77239876353076</v>
       </c>
       <c r="D13" t="n">
-        <v>26.53664044579129</v>
+        <v>24.97566159603886</v>
       </c>
     </row>
     <row r="14">
@@ -2503,13 +2503,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>0.921861094287755</v>
       </c>
       <c r="C14" t="n">
-        <v>16.59349969717959</v>
+        <v>20.28094407433061</v>
       </c>
       <c r="D14" t="n">
-        <v>19.97365704290136</v>
+        <v>17.51536079146734</v>
       </c>
     </row>
     <row r="15">
@@ -2517,13 +2517,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>2.5083653843506</v>
       </c>
       <c r="C15" t="n">
-        <v>15.76686813020377</v>
+        <v>32.25041208450772</v>
       </c>
       <c r="D15" t="n">
-        <v>17.20021977840412</v>
+        <v>10.39179944945249</v>
       </c>
     </row>
     <row r="16">
@@ -2534,10 +2534,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>15.29268398905256</v>
+        <v>40.09163099832699</v>
       </c>
       <c r="D16" t="n">
-        <v>14.87936820556466</v>
+        <v>3.719842051391165</v>
       </c>
     </row>
     <row r="17">
@@ -2548,10 +2548,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>15.11106066376691</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>11.33329549782518</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2559,13 +2559,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>3.21031499288707</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>35.31346492175777</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>6.955682484588652</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2576,10 +2576,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>35.50686921949439</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>4.212679398923063</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.956443248114646</v>
+        <v>0.4152792788964008</v>
       </c>
       <c r="C2" t="n">
-        <v>2.444551783574558</v>
+        <v>5.495823648373645</v>
       </c>
       <c r="D2" t="n">
-        <v>14.99619618237003</v>
+        <v>12.24533911507046</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>25.73651606683013</v>
+        <v>4.344233591292136</v>
       </c>
       <c r="C3" t="n">
-        <v>20.62651926622549</v>
+        <v>27.5331143656018</v>
       </c>
       <c r="D3" t="n">
-        <v>104.1388877279804</v>
+        <v>41.51811041259761</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>56.13044324260714</v>
+        <v>19.65458903902115</v>
       </c>
       <c r="C4" t="n">
-        <v>79.46069568632835</v>
+        <v>85.21668247632739</v>
       </c>
       <c r="D4" t="n">
-        <v>193.2275831498572</v>
+        <v>76.43593100954392</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>54.14338588921161</v>
+        <v>19.24225500323749</v>
       </c>
       <c r="C5" t="n">
-        <v>162.1356333563608</v>
+        <v>242.7616635676301</v>
       </c>
       <c r="D5" t="n">
-        <v>148.4893402673301</v>
+        <v>77.28808801683016</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>41.21769561509809</v>
+        <v>10.38492721552276</v>
       </c>
       <c r="C6" t="n">
-        <v>137.4996564659913</v>
+        <v>311.3063065304382</v>
       </c>
       <c r="D6" t="n">
-        <v>64.24164277509429</v>
+        <v>53.45419900083034</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>10.24061030299848</v>
+        <v>4.07228947721577</v>
       </c>
       <c r="C7" t="n">
-        <v>96.47732864403831</v>
+        <v>172.3536634621615</v>
       </c>
       <c r="D7" t="n">
-        <v>37.42913122440964</v>
+        <v>34.43480072645687</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.840016181936775</v>
+        <v>2.169662426385451</v>
       </c>
       <c r="C8" t="n">
-        <v>62.66986470059513</v>
+        <v>73.68507394224434</v>
       </c>
       <c r="D8" t="n">
-        <v>32.3780392860598</v>
+        <v>30.95941385342316</v>
       </c>
     </row>
     <row r="9">
@@ -2744,13 +2744,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.996874830438012</v>
+        <v>1.220312396378785</v>
       </c>
       <c r="C9" t="n">
-        <v>28.6218725696115</v>
+        <v>32.8374972116473</v>
       </c>
       <c r="D9" t="n">
-        <v>32.50468473990763</v>
+        <v>26.07031028627404</v>
       </c>
     </row>
     <row r="10">
@@ -2758,13 +2758,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.281180754042088</v>
+        <v>0.2847068342315751</v>
       </c>
       <c r="C10" t="n">
-        <v>26.33538216642069</v>
+        <v>24.34243432679967</v>
       </c>
       <c r="D10" t="n">
-        <v>23.63066724122073</v>
+        <v>26.05067533218912</v>
       </c>
     </row>
     <row r="11">
@@ -2772,13 +2772,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>0.7107853378746906</v>
+        <v>0.1776963344686726</v>
       </c>
       <c r="C11" t="n">
-        <v>21.32356013624072</v>
+        <v>20.43507846389736</v>
       </c>
       <c r="D11" t="n">
-        <v>22.92282714645877</v>
+        <v>24.16670148773948</v>
       </c>
     </row>
     <row r="12">
@@ -2789,10 +2789,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>15.83853571261379</v>
+        <v>16.05550195525234</v>
       </c>
       <c r="D12" t="n">
-        <v>21.47965802121596</v>
+        <v>20.39482680802324</v>
       </c>
     </row>
     <row r="13">
@@ -2800,13 +2800,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>0.5203262832508095</v>
       </c>
       <c r="C13" t="n">
-        <v>13.52848336452105</v>
+        <v>16.65044106402591</v>
       </c>
       <c r="D13" t="n">
-        <v>16.3902779224005</v>
+        <v>14.30897278939726</v>
       </c>
     </row>
     <row r="14">
@@ -2814,13 +2814,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>13.21334235145782</v>
+        <v>27.04125876577415</v>
       </c>
       <c r="D14" t="n">
-        <v>14.44249047717483</v>
+        <v>8.604036880019047</v>
       </c>
     </row>
     <row r="15">
@@ -2831,10 +2831,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>12.90016483380309</v>
+        <v>34.04210164475815</v>
       </c>
       <c r="D15" t="n">
-        <v>12.541826921753</v>
+        <v>2.866703296400686</v>
       </c>
     </row>
     <row r="16">
@@ -2845,10 +2845,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>12.81278928812512</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>9.506263020221864</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -2856,13 +2856,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2.361103228713579</v>
+        <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>30.22212132753381</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>5.66664774891259</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2873,10 +2873,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>30.49799243242716</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>3.21031499288707</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.742823159216341</v>
+        <v>0.2542726553999239</v>
       </c>
       <c r="C2" t="n">
-        <v>2.344413517741383</v>
+        <v>2.538799563182252</v>
       </c>
       <c r="D2" t="n">
-        <v>15.43503740616835</v>
+        <v>8.466592201424493</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>19.80185119465817</v>
+        <v>2.886338250485623</v>
       </c>
       <c r="C3" t="n">
-        <v>14.68694565553228</v>
+        <v>24.25898577193868</v>
       </c>
       <c r="D3" t="n">
-        <v>93.17276587154355</v>
+        <v>41.37575699548182</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>52.9270004836498</v>
+        <v>13.24770352110646</v>
       </c>
       <c r="C4" t="n">
-        <v>65.91944960165209</v>
+        <v>74.3173194637793</v>
       </c>
       <c r="D4" t="n">
-        <v>200.004587552273</v>
+        <v>76.20620204675016</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>67.54424205218056</v>
+        <v>18.8986433067511</v>
       </c>
       <c r="C5" t="n">
-        <v>155.9997102048182</v>
+        <v>181.206082511355</v>
       </c>
       <c r="D5" t="n">
-        <v>178.2362957060084</v>
+        <v>78.53981633974485</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>54.46049039768332</v>
+        <v>10.58618549489336</v>
       </c>
       <c r="C6" t="n">
-        <v>193.0066899164017</v>
+        <v>289.2483991114208</v>
       </c>
       <c r="D6" t="n">
-        <v>89.80144425516001</v>
+        <v>53.97747052719389</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>23.2360046641135</v>
+        <v>3.473423377625215</v>
       </c>
       <c r="C7" t="n">
-        <v>142.7696781423882</v>
+        <v>212.8968984044421</v>
       </c>
       <c r="D7" t="n">
-        <v>44.43586458961913</v>
+        <v>32.39865598784899</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>6.592435834017332</v>
+        <v>1.084831213192726</v>
       </c>
       <c r="C8" t="n">
-        <v>90.54168202416209</v>
+        <v>87.37063693944488</v>
       </c>
       <c r="D8" t="n">
-        <v>34.63115026730623</v>
+        <v>26.62008900065226</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.551562283337459</v>
+        <v>0.4437499623195582</v>
       </c>
       <c r="C9" t="n">
-        <v>47.59218345877262</v>
+        <v>32.61562223048752</v>
       </c>
       <c r="D9" t="n">
-        <v>33.50312215512664</v>
+        <v>20.63437324785945</v>
       </c>
     </row>
     <row r="10">
@@ -3069,13 +3069,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.423534171157875</v>
+        <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>30.17892442854695</v>
+        <v>17.65182372235765</v>
       </c>
       <c r="D10" t="n">
-        <v>25.19655482949439</v>
+        <v>19.92947839621025</v>
       </c>
     </row>
     <row r="11">
@@ -3083,13 +3083,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>0.5330890034060179</v>
+        <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>24.87748682561417</v>
+        <v>13.14952875068177</v>
       </c>
       <c r="D11" t="n">
-        <v>23.63361248433346</v>
+        <v>17.59193711239859</v>
       </c>
     </row>
     <row r="12">
@@ -3100,10 +3100,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>18.22516438163779</v>
+        <v>11.28224461720434</v>
       </c>
       <c r="D12" t="n">
-        <v>21.91359050649305</v>
+        <v>13.66887328622834</v>
       </c>
     </row>
     <row r="13">
@@ -3111,13 +3111,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>0.5203262832508095</v>
       </c>
       <c r="C13" t="n">
-        <v>15.86995163914969</v>
+        <v>14.04880964777186</v>
       </c>
       <c r="D13" t="n">
-        <v>16.3902779224005</v>
+        <v>8.325220532012953</v>
       </c>
     </row>
     <row r="14">
@@ -3128,10 +3128,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>14.13520344574558</v>
+        <v>16.28621266575034</v>
       </c>
       <c r="D14" t="n">
-        <v>14.44249047717483</v>
+        <v>3.072870314292517</v>
       </c>
     </row>
     <row r="15">
@@ -3142,10 +3142,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>13.97517856995334</v>
+        <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>12.18348900970292</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3153,13 +3153,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.653263133951629</v>
+        <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>24.38563122578652</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>8.266315669758143</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3170,10 +3170,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>34.94432778496098</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>4.722206457427158</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -3184,10 +3184,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>1.070104997629023</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>1.070104997629023</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.407646281440679</v>
+        <v>0.2739076094848601</v>
       </c>
       <c r="C2" t="n">
-        <v>1.687624303600267</v>
+        <v>8.534332793017523</v>
       </c>
       <c r="D2" t="n">
-        <v>12.85402269170349</v>
+        <v>8.509789100411352</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.4666743168825</v>
+        <v>1.786780821729195</v>
       </c>
       <c r="C3" t="n">
-        <v>12.20803270230909</v>
+        <v>15.66869335977909</v>
       </c>
       <c r="D3" t="n">
-        <v>86.18272221730625</v>
+        <v>38.94593142747097</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>47.86020058203201</v>
+        <v>9.201921231905354</v>
       </c>
       <c r="C4" t="n">
-        <v>54.7265440255342</v>
+        <v>67.22124705748335</v>
       </c>
       <c r="D4" t="n">
-        <v>201.5105885305876</v>
+        <v>79.60108560803563</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>74.46556336712058</v>
+        <v>19.88039101099791</v>
       </c>
       <c r="C5" t="n">
-        <v>147.7775731817512</v>
+        <v>157.2023511425205</v>
       </c>
       <c r="D5" t="n">
-        <v>200.0065510476815</v>
+        <v>87.13010875190443</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>64.64415933383549</v>
+        <v>17.99249017573129</v>
       </c>
       <c r="C6" t="n">
-        <v>220.9815907489146</v>
+        <v>292.9112997959657</v>
       </c>
       <c r="D6" t="n">
-        <v>107.9549410543878</v>
+        <v>66.1334706011779</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>22.57725195456389</v>
+        <v>7.72537268471815</v>
       </c>
       <c r="C7" t="n">
-        <v>189.2416874706151</v>
+        <v>321.4114356502505</v>
       </c>
       <c r="D7" t="n">
-        <v>50.96350507515617</v>
+        <v>40.00425545264903</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5.340707511102648</v>
+        <v>2.253110981246429</v>
       </c>
       <c r="C8" t="n">
-        <v>117.5790137991192</v>
+        <v>183.6702692490145</v>
       </c>
       <c r="D8" t="n">
-        <v>36.63391558396972</v>
+        <v>29.45733986592554</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.996874830438012</v>
+        <v>0.6656249434793372</v>
       </c>
       <c r="C9" t="n">
-        <v>57.13280764864312</v>
+        <v>70.0015565559103</v>
       </c>
       <c r="D9" t="n">
-        <v>33.05937219280708</v>
+        <v>22.40937309713768</v>
       </c>
     </row>
     <row r="10">
@@ -3380,13 +3380,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.5694136684631501</v>
+        <v>0.1423534171157875</v>
       </c>
       <c r="C10" t="n">
-        <v>31.74481201682062</v>
+        <v>27.47420950334699</v>
       </c>
       <c r="D10" t="n">
-        <v>25.76596849795754</v>
+        <v>20.4988920646734</v>
       </c>
     </row>
     <row r="11">
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>24.34439782220815</v>
+        <v>16.70345544005523</v>
       </c>
       <c r="D11" t="n">
-        <v>24.16670148773948</v>
+        <v>18.30272245027328</v>
       </c>
     </row>
     <row r="12">
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>17.7912318963607</v>
+        <v>13.0179745583127</v>
       </c>
       <c r="D12" t="n">
-        <v>20.39482680802324</v>
+        <v>14.31977201414398</v>
       </c>
     </row>
     <row r="13">
@@ -3422,13 +3422,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>0.2601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>11.70734137314322</v>
+        <v>14.04880964777186</v>
       </c>
       <c r="D13" t="n">
-        <v>16.3902779224005</v>
+        <v>8.845546815263763</v>
       </c>
     </row>
     <row r="14">
@@ -3439,10 +3439,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>11.67690719431156</v>
+        <v>16.59349969717959</v>
       </c>
       <c r="D14" t="n">
-        <v>11.36962016288231</v>
+        <v>3.380157345721768</v>
       </c>
     </row>
     <row r="15">
@@ -3450,13 +3450,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.075013736150257</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>20.42526098685489</v>
+        <v>3.583379120500858</v>
       </c>
       <c r="D15" t="n">
-        <v>6.808420328951629</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>29.75873641112932</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>3.719842051391165</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3481,10 +3481,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>0.4722206457427158</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>0.4722206457427158</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.424156065963627</v>
+        <v>0.9395325529641976</v>
       </c>
       <c r="C2" t="n">
-        <v>4.856705892908971</v>
+        <v>20.07968579496001</v>
       </c>
       <c r="D2" t="n">
-        <v>15.53419392429728</v>
+        <v>10.67552453597982</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>15.08946221427348</v>
+        <v>1.34499435481813</v>
       </c>
       <c r="C3" t="n">
-        <v>9.429686699290613</v>
+        <v>25.30945581548277</v>
       </c>
       <c r="D3" t="n">
-        <v>78.54963381678731</v>
+        <v>36.78117773960675</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>41.63199314629023</v>
+        <v>6.240970155896973</v>
       </c>
       <c r="C4" t="n">
-        <v>43.43153668817465</v>
+        <v>51.95703375185395</v>
       </c>
       <c r="D4" t="n">
-        <v>196.6990430320739</v>
+        <v>80.9156457840221</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>74.22012644105888</v>
+        <v>17.35239067256238</v>
       </c>
       <c r="C5" t="n">
-        <v>126.7190849256571</v>
+        <v>140.2426595516569</v>
       </c>
       <c r="D5" t="n">
-        <v>220.9177771481386</v>
+        <v>95.22952731194061</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>78.49072895453251</v>
+        <v>22.33966901013618</v>
       </c>
       <c r="C6" t="n">
-        <v>227.6231139681443</v>
+        <v>273.3892466970178</v>
       </c>
       <c r="D6" t="n">
-        <v>136.0908485103971</v>
+        <v>76.35739119320418</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>41.20198765183014</v>
+        <v>13.95358012045992</v>
       </c>
       <c r="C7" t="n">
-        <v>245.7147606620044</v>
+        <v>373.9319925843421</v>
       </c>
       <c r="D7" t="n">
-        <v>64.37810570598458</v>
+        <v>48.74770050667112</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>11.34900346109313</v>
+        <v>4.923464736797754</v>
       </c>
       <c r="C8" t="n">
-        <v>170.4853975809798</v>
+        <v>300.08100328008</v>
       </c>
       <c r="D8" t="n">
-        <v>40.22220344299182</v>
+        <v>32.96217917008666</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.995312245657018</v>
+        <v>1.331249886958674</v>
       </c>
       <c r="C9" t="n">
-        <v>91.63436721898876</v>
+        <v>143.3312378292173</v>
       </c>
       <c r="D9" t="n">
-        <v>34.39062207976576</v>
+        <v>24.18437294641592</v>
       </c>
     </row>
     <row r="10">
@@ -3691,13 +3691,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.8541205026947251</v>
+        <v>0.2847068342315751</v>
       </c>
       <c r="C10" t="n">
-        <v>44.98367980858886</v>
+        <v>52.3860574986098</v>
       </c>
       <c r="D10" t="n">
-        <v>27.3318560862312</v>
+        <v>21.35301256736813</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>29.14219885286231</v>
+        <v>23.27821981539612</v>
       </c>
       <c r="D11" t="n">
-        <v>24.52209415667683</v>
+        <v>19.01350778814797</v>
       </c>
     </row>
     <row r="12">
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>21.04572553593887</v>
+        <v>15.62156946997525</v>
       </c>
       <c r="D12" t="n">
-        <v>20.82875929330033</v>
+        <v>14.97067074205961</v>
       </c>
     </row>
     <row r="13">
@@ -3736,10 +3736,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>13.78864650614645</v>
+        <v>14.56913593102267</v>
       </c>
       <c r="D13" t="n">
-        <v>16.65044106402591</v>
+        <v>9.365873098514571</v>
       </c>
     </row>
     <row r="14">
@@ -3750,10 +3750,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>12.29148125717007</v>
+        <v>16.28621266575034</v>
       </c>
       <c r="D14" t="n">
-        <v>11.67690719431156</v>
+        <v>3.994731408580272</v>
       </c>
     </row>
     <row r="15">
@@ -3761,13 +3761,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0.7166758241001715</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>21.14193681095506</v>
+        <v>8.241771977151972</v>
       </c>
       <c r="D15" t="n">
-        <v>6.450082416901544</v>
+        <v>0.3583379120500857</v>
       </c>
     </row>
     <row r="16">
@@ -3778,10 +3778,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>29.34542062764141</v>
+        <v>0.8266315669758143</v>
       </c>
       <c r="D16" t="n">
-        <v>3.306526267903257</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.427502219703868</v>
+        <v>4.407065444363932</v>
       </c>
       <c r="C2" t="n">
-        <v>3.421390749300134</v>
+        <v>22.45158824842031</v>
       </c>
       <c r="D2" t="n">
-        <v>14.35707842690536</v>
+        <v>6.6483954531594</v>
       </c>
     </row>
     <row r="3">
@@ -3904,13 +3904,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>0.06872233929727672</v>
+        <v>0.07363107781851078</v>
       </c>
       <c r="C3" t="n">
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>4.138066573400306</v>
+        <v>4.196971435655114</v>
       </c>
     </row>
     <row r="4">
@@ -3918,13 +3918,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2.233476027161494</v>
+        <v>2.616357631817749</v>
       </c>
       <c r="C4" t="n">
-        <v>3.994731408580271</v>
+        <v>4.390375733391735</v>
       </c>
       <c r="D4" t="n">
-        <v>23.03670988015141</v>
+        <v>24.32574461582747</v>
       </c>
     </row>
     <row r="5">
@@ -3932,13 +3932,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>6.111379458936396</v>
+        <v>7.706719478337463</v>
       </c>
       <c r="C5" t="n">
-        <v>12.64000169217769</v>
+        <v>14.38260386721577</v>
       </c>
       <c r="D5" t="n">
-        <v>25.47635292520474</v>
+        <v>27.95526587842793</v>
       </c>
     </row>
     <row r="6">
@@ -3946,13 +3946,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>7.3258013690897</v>
+        <v>10.2641722479004</v>
       </c>
       <c r="C6" t="n">
-        <v>15.8994040702771</v>
+        <v>19.64280806657019</v>
       </c>
       <c r="D6" t="n">
-        <v>31.27553661419064</v>
+        <v>36.14598697495907</v>
       </c>
     </row>
     <row r="7">
@@ -3960,13 +3960,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>7.72537268471815</v>
+        <v>12.0970952117292</v>
       </c>
       <c r="C7" t="n">
-        <v>17.54677671800324</v>
+        <v>23.2360046641135</v>
       </c>
       <c r="D7" t="n">
-        <v>29.70375853969149</v>
+        <v>35.69241953559704</v>
       </c>
     </row>
     <row r="8">
@@ -3974,13 +3974,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.261406931236909</v>
+        <v>14.26970288122739</v>
       </c>
       <c r="C8" t="n">
-        <v>18.52557917913731</v>
+        <v>25.61870634232051</v>
       </c>
       <c r="D8" t="n">
-        <v>35.04839304161113</v>
+        <v>44.31118263117978</v>
       </c>
     </row>
     <row r="9">
@@ -3988,13 +3988,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>8.320311793491715</v>
+        <v>15.08749871886498</v>
       </c>
       <c r="C9" t="n">
-        <v>20.74531073843935</v>
+        <v>30.7296848906294</v>
       </c>
       <c r="D9" t="n">
-        <v>38.71718421238145</v>
+        <v>49.36718330805084</v>
       </c>
     </row>
     <row r="10">
@@ -4002,13 +4002,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>7.544731107136738</v>
+        <v>14.94710879715769</v>
       </c>
       <c r="C10" t="n">
-        <v>24.62714116103124</v>
+        <v>37.72365553568369</v>
       </c>
       <c r="D10" t="n">
-        <v>51.53193699591508</v>
+        <v>69.04140730115694</v>
       </c>
     </row>
     <row r="11">
@@ -4016,13 +4016,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>6.04167537193487</v>
+        <v>12.61643974727576</v>
       </c>
       <c r="C11" t="n">
-        <v>24.34439782220815</v>
+        <v>38.20471191076462</v>
       </c>
       <c r="D11" t="n">
-        <v>43.5356019448248</v>
+        <v>58.10670137125595</v>
       </c>
     </row>
     <row r="12">
@@ -4030,13 +4030,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>5.207189823325082</v>
+        <v>11.28224461720434</v>
       </c>
       <c r="C12" t="n">
-        <v>22.56448923440869</v>
+        <v>36.66729500591412</v>
       </c>
       <c r="D12" t="n">
-        <v>42.52538355715483</v>
+        <v>59.44875048296136</v>
       </c>
     </row>
     <row r="13">
@@ -4044,13 +4044,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>4.682936549257286</v>
+        <v>10.926851948267</v>
       </c>
       <c r="C13" t="n">
-        <v>21.853703896534</v>
+        <v>36.94316611080748</v>
       </c>
       <c r="D13" t="n">
-        <v>43.70740779306801</v>
+        <v>60.87817514034472</v>
       </c>
     </row>
     <row r="14">
@@ -4058,13 +4058,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.916592502868027</v>
+        <v>11.67690719431156</v>
       </c>
       <c r="C14" t="n">
-        <v>23.04652735719387</v>
+        <v>39.33274002294421</v>
       </c>
       <c r="D14" t="n">
-        <v>44.55661955724149</v>
+        <v>63.60841550585509</v>
       </c>
     </row>
     <row r="15">
@@ -4072,13 +4072,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>5.733406592801372</v>
+        <v>13.61684065790326</v>
       </c>
       <c r="C15" t="n">
-        <v>25.80032966760617</v>
+        <v>45.50891483036089</v>
       </c>
       <c r="D15" t="n">
-        <v>41.92553570986004</v>
+        <v>61.27578296056467</v>
       </c>
     </row>
     <row r="16">
@@ -4086,13 +4086,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>6.199736752318607</v>
+        <v>14.87936820556466</v>
       </c>
       <c r="C16" t="n">
-        <v>28.9321048441535</v>
+        <v>51.25115715250048</v>
       </c>
       <c r="D16" t="n">
-        <v>40.09163099832699</v>
+        <v>57.864209688307</v>
       </c>
     </row>
     <row r="17">
@@ -4100,13 +4100,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>6.611089040398022</v>
+        <v>16.99994324673777</v>
       </c>
       <c r="C17" t="n">
-        <v>31.16656261901925</v>
+        <v>56.19425684338318</v>
       </c>
       <c r="D17" t="n">
-        <v>35.8887690764464</v>
+        <v>53.8331536146696</v>
       </c>
     </row>
     <row r="18">
@@ -4114,13 +4114,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>6.955682484588652</v>
+        <v>18.1917849596934</v>
       </c>
       <c r="C18" t="n">
-        <v>33.70830742531424</v>
+        <v>62.06608986248335</v>
       </c>
       <c r="D18" t="n">
-        <v>30.49799243242716</v>
+        <v>45.47946239923349</v>
       </c>
     </row>
     <row r="19">
@@ -4128,13 +4128,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>7.823547455142832</v>
+        <v>20.46158565191202</v>
       </c>
       <c r="C19" t="n">
-        <v>36.10868056219768</v>
+        <v>66.80105904006572</v>
       </c>
       <c r="D19" t="n">
-        <v>22.8688310227252</v>
+        <v>34.9050578767911</v>
       </c>
     </row>
     <row r="20">
@@ -4142,13 +4142,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>7.397468951499714</v>
+        <v>20.84741249968101</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>73.30219233758808</v>
       </c>
       <c r="D20" t="n">
-        <v>13.4499435481813</v>
+        <v>20.17491532227195</v>
       </c>
     </row>
     <row r="21">
@@ -4156,13 +4156,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>11.44977350273866</v>
+        <v>27.41820207255788</v>
       </c>
       <c r="C21" t="n">
-        <v>54.95891281314559</v>
+        <v>99.77179087514119</v>
       </c>
       <c r="D21" t="n">
-        <v>0.763318233515911</v>
+        <v>0.761616724237719</v>
       </c>
     </row>
   </sheetData>
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.840597019013522</v>
+        <v>0.8943721585688442</v>
       </c>
       <c r="C2" t="n">
-        <v>2.719441140763665</v>
+        <v>17.80301286881166</v>
       </c>
       <c r="D2" t="n">
-        <v>11.4344155113626</v>
+        <v>9.226464924511523</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>20.36635612460008</v>
+        <v>2.159844949342983</v>
       </c>
       <c r="C3" t="n">
-        <v>13.79355524466769</v>
+        <v>50.62382036948678</v>
       </c>
       <c r="D3" t="n">
-        <v>84.73464435354221</v>
+        <v>36.49156216685395</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>56.93449461238528</v>
+        <v>4.454189334167779</v>
       </c>
       <c r="C4" t="n">
-        <v>64.11990605976767</v>
+        <v>57.11317269455819</v>
       </c>
       <c r="D4" t="n">
-        <v>203.9610308003876</v>
+        <v>80.71144226153878</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>46.95208395560371</v>
+        <v>14.13716694115407</v>
       </c>
       <c r="C5" t="n">
-        <v>190.0172681569702</v>
+        <v>118.5460352878024</v>
       </c>
       <c r="D5" t="n">
-        <v>201.8227843005381</v>
+        <v>100.1137221405685</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>25.55980148006571</v>
+        <v>22.86294053649972</v>
       </c>
       <c r="C6" t="n">
-        <v>210.9186767803848</v>
+        <v>252.5388889542241</v>
       </c>
       <c r="D6" t="n">
-        <v>103.1247423494935</v>
+        <v>86.82282172047518</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>7.485826244881928</v>
+        <v>19.3433750167749</v>
       </c>
       <c r="C7" t="n">
-        <v>119.892993138029</v>
+        <v>383.57373678775</v>
       </c>
       <c r="D7" t="n">
-        <v>37.06981156465531</v>
+        <v>56.65273302126644</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>2.002765316663493</v>
+        <v>9.012443924985718</v>
       </c>
       <c r="C8" t="n">
-        <v>67.5098808825319</v>
+        <v>388.7033685424396</v>
       </c>
       <c r="D8" t="n">
-        <v>25.2849121228766</v>
+        <v>37.38495257771854</v>
       </c>
     </row>
     <row r="9">
@@ -4299,13 +4299,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>0.5546874528994477</v>
+        <v>2.773437264497239</v>
       </c>
       <c r="C9" t="n">
-        <v>34.27968458918587</v>
+        <v>240.9562295395201</v>
       </c>
       <c r="D9" t="n">
-        <v>20.85624822901923</v>
+        <v>26.18124777685393</v>
       </c>
     </row>
     <row r="10">
@@ -4313,13 +4313,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0</v>
+        <v>0.5694136684631501</v>
       </c>
       <c r="C10" t="n">
-        <v>22.776546738526</v>
+        <v>99.50503856393547</v>
       </c>
       <c r="D10" t="n">
-        <v>19.21771131063132</v>
+        <v>22.34948648717864</v>
       </c>
     </row>
     <row r="11">
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>16.8811517745239</v>
+        <v>38.02701557629594</v>
       </c>
       <c r="D11" t="n">
-        <v>16.70345544005523</v>
+        <v>19.54659679155399</v>
       </c>
     </row>
     <row r="12">
@@ -4344,10 +4344,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>11.0652783745658</v>
+        <v>19.52696183746906</v>
       </c>
       <c r="D12" t="n">
-        <v>13.4519070435898</v>
+        <v>15.4046032273367</v>
       </c>
     </row>
     <row r="13">
@@ -4358,10 +4358,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
+        <v>15.86995163914969</v>
+      </c>
+      <c r="D13" t="n">
         <v>10.14636252339079</v>
-      </c>
-      <c r="D13" t="n">
-        <v>9.626036240139976</v>
       </c>
     </row>
     <row r="14">
@@ -4369,13 +4369,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0.3072870314292517</v>
+        <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>17.51536079146734</v>
+        <v>16.28621266575034</v>
       </c>
       <c r="D14" t="n">
-        <v>5.223879534297279</v>
+        <v>4.302018440009523</v>
       </c>
     </row>
     <row r="15">
@@ -4386,10 +4386,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>24.72531593145592</v>
+        <v>11.10847527355266</v>
       </c>
       <c r="D15" t="n">
-        <v>2.5083653843506</v>
+        <v>0.7166758241001715</v>
       </c>
     </row>
     <row r="16">
@@ -4400,7 +4400,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>0</v>
+        <v>2.89321048441535</v>
       </c>
       <c r="D16" t="n">
         <v>0</v>
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.857507714163971</v>
+        <v>4.999059310024759</v>
       </c>
       <c r="C2" t="n">
-        <v>2.486766934857171</v>
+        <v>12.00775617064274</v>
       </c>
       <c r="D2" t="n">
-        <v>28.7622624913188</v>
+        <v>9.322676199527711</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>13.6512018275519</v>
+        <v>7.107853378746907</v>
       </c>
       <c r="C3" t="n">
-        <v>8.619744843286995</v>
+        <v>44.33081758526473</v>
       </c>
       <c r="D3" t="n">
-        <v>15.19745446174063</v>
+        <v>7.593818492349079</v>
       </c>
     </row>
     <row r="4">
@@ -4540,13 +4540,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1.008254892261474</v>
+        <v>0.9189158511750145</v>
       </c>
       <c r="C4" t="n">
-        <v>1.493238258159399</v>
+        <v>1.710204500797944</v>
       </c>
       <c r="D4" t="n">
-        <v>19.62906359871073</v>
+        <v>18.45489334443154</v>
       </c>
     </row>
     <row r="5">
@@ -4554,13 +4554,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>4.736932672990861</v>
+        <v>3.632466505713199</v>
       </c>
       <c r="C5" t="n">
-        <v>9.35114688295087</v>
+        <v>8.29576810088555</v>
       </c>
       <c r="D5" t="n">
-        <v>28.49522711576368</v>
+        <v>24.20008090968388</v>
       </c>
     </row>
     <row r="6">
@@ -4568,13 +4568,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>8.050331174823848</v>
+        <v>5.75598678999905</v>
       </c>
       <c r="C6" t="n">
-        <v>18.47551004622073</v>
+        <v>14.32958949118645</v>
       </c>
       <c r="D6" t="n">
-        <v>32.8453511932813</v>
+        <v>28.6591789823729</v>
       </c>
     </row>
     <row r="7">
@@ -4582,13 +4582,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>8.683558444063037</v>
+        <v>6.108434215823654</v>
       </c>
       <c r="C7" t="n">
-        <v>20.9603134856694</v>
+        <v>16.58859095865835</v>
       </c>
       <c r="D7" t="n">
-        <v>32.21899615797182</v>
+        <v>27.90716024091983</v>
       </c>
     </row>
     <row r="8">
@@ -4596,13 +4596,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.762098260402782</v>
+        <v>6.508987279156353</v>
       </c>
       <c r="C8" t="n">
-        <v>21.69662426385451</v>
+        <v>17.19040230136165</v>
       </c>
       <c r="D8" t="n">
-        <v>35.79943003535994</v>
+        <v>32.04424506661589</v>
       </c>
     </row>
     <row r="9">
@@ -4610,13 +4610,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>8.874999246391162</v>
+        <v>6.656249434793372</v>
       </c>
       <c r="C9" t="n">
-        <v>22.74218556887735</v>
+        <v>18.74843590800133</v>
       </c>
       <c r="D9" t="n">
-        <v>39.2718716652809</v>
+        <v>34.72343455150543</v>
       </c>
     </row>
     <row r="10">
@@ -4624,13 +4624,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8.256498192715677</v>
+        <v>6.405903770210439</v>
       </c>
       <c r="C10" t="n">
-        <v>25.62361508084176</v>
+        <v>21.78007281871549</v>
       </c>
       <c r="D10" t="n">
-        <v>50.67781649322036</v>
+        <v>46.12250714551515</v>
       </c>
     </row>
     <row r="11">
@@ -4638,13 +4638,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>6.75246070980956</v>
+        <v>5.330890034060179</v>
       </c>
       <c r="C11" t="n">
-        <v>27.36523550817559</v>
+        <v>22.7451308119901</v>
       </c>
       <c r="D11" t="n">
-        <v>46.37874329632356</v>
+        <v>41.04785326226338</v>
       </c>
     </row>
     <row r="12">
@@ -4652,13 +4652,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>5.641122308602172</v>
+        <v>4.339324852770901</v>
       </c>
       <c r="C12" t="n">
-        <v>25.81898287398687</v>
+        <v>21.69662426385451</v>
       </c>
       <c r="D12" t="n">
-        <v>43.17628228507047</v>
+        <v>39.4878561602152</v>
       </c>
     </row>
     <row r="13">
@@ -4666,13 +4666,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>4.943099690882691</v>
+        <v>3.902447124381071</v>
       </c>
       <c r="C13" t="n">
-        <v>23.93500902953724</v>
+        <v>20.55288818840698</v>
       </c>
       <c r="D13" t="n">
-        <v>44.22773407631881</v>
+        <v>40.06512381031234</v>
       </c>
     </row>
     <row r="14">
@@ -4680,13 +4680,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.609305471438775</v>
+        <v>3.994731408580272</v>
       </c>
       <c r="C14" t="n">
-        <v>23.96838845148163</v>
+        <v>21.20280516861837</v>
       </c>
       <c r="D14" t="n">
-        <v>44.86390658867074</v>
+        <v>40.86917518009047</v>
       </c>
     </row>
     <row r="15">
@@ -4694,13 +4694,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>5.375068680751286</v>
+        <v>4.30005494460103</v>
       </c>
       <c r="C15" t="n">
-        <v>26.15866757965626</v>
+        <v>23.29196428325557</v>
       </c>
       <c r="D15" t="n">
-        <v>42.28387362191012</v>
+        <v>39.77550823755952</v>
       </c>
     </row>
     <row r="16">
@@ -4708,13 +4708,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>5.7864209688307</v>
+        <v>4.959789401854886</v>
       </c>
       <c r="C16" t="n">
-        <v>28.9321048441535</v>
+        <v>26.03889435973815</v>
       </c>
       <c r="D16" t="n">
-        <v>40.5049467818149</v>
+        <v>36.78510473042374</v>
       </c>
     </row>
     <row r="17">
@@ -4722,13 +4722,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>6.138868394655306</v>
+        <v>5.194427103169874</v>
       </c>
       <c r="C17" t="n">
-        <v>31.63878326476196</v>
+        <v>28.80545939030567</v>
       </c>
       <c r="D17" t="n">
-        <v>36.36098972218912</v>
+        <v>34.47210713921825</v>
       </c>
     </row>
     <row r="18">
@@ -4736,13 +4736,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>6.42062998577414</v>
+        <v>5.885577486959628</v>
       </c>
       <c r="C18" t="n">
-        <v>34.24335992412875</v>
+        <v>31.03304493124168</v>
       </c>
       <c r="D18" t="n">
-        <v>31.03304493124168</v>
+        <v>28.89283493598363</v>
       </c>
     </row>
     <row r="19">
@@ -4750,13 +4750,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>7.221736112439537</v>
+        <v>6.018113427032947</v>
       </c>
       <c r="C19" t="n">
-        <v>36.71049190490098</v>
+        <v>33.09962384868121</v>
       </c>
       <c r="D19" t="n">
-        <v>23.47064236542849</v>
+        <v>21.66520833731861</v>
       </c>
     </row>
     <row r="20">
@@ -4767,10 +4767,10 @@
         <v>6.724971774090649</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>14.12244072559037</v>
+        <v>12.77744637077223</v>
       </c>
     </row>
     <row r="21">
@@ -4778,13 +4778,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>13.39784643691723</v>
+        <v>11.67693928012672</v>
       </c>
       <c r="C21" t="n">
-        <v>70.14166664033138</v>
+        <v>59.94162163798386</v>
       </c>
       <c r="D21" t="n">
-        <v>1.576217227872615</v>
+        <v>0.778462618675115</v>
       </c>
     </row>
   </sheetData>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.532729150507524</v>
+        <v>3.433171721751096</v>
       </c>
       <c r="C2" t="n">
-        <v>4.82921695719006</v>
+        <v>5.979825266567322</v>
       </c>
       <c r="D2" t="n">
-        <v>28.90756115154733</v>
+        <v>14.64865749506666</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>19.68404147014855</v>
+        <v>13.58247948825462</v>
       </c>
       <c r="C3" t="n">
-        <v>9.29224202069606</v>
+        <v>46.05869354473911</v>
       </c>
       <c r="D3" t="n">
-        <v>35.68162031085032</v>
+        <v>13.88682127657113</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>15.851298432769</v>
+        <v>8.870090507869932</v>
       </c>
       <c r="C4" t="n">
-        <v>13.70716144669397</v>
+        <v>71.43294470870217</v>
       </c>
       <c r="D4" t="n">
-        <v>23.03670988015141</v>
+        <v>18.16135078086175</v>
       </c>
     </row>
     <row r="5">
@@ -4865,13 +4865,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>3.067961575771283</v>
+        <v>2.454369260617026</v>
       </c>
       <c r="C5" t="n">
-        <v>5.375068680751288</v>
+        <v>5.129631754689585</v>
       </c>
       <c r="D5" t="n">
-        <v>29.40334374219198</v>
+        <v>25.72178985126644</v>
       </c>
     </row>
     <row r="6">
@@ -4879,13 +4879,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>7.446556336712058</v>
+        <v>5.514476854754335</v>
       </c>
       <c r="C6" t="n">
-        <v>16.50317890838889</v>
+        <v>13.72581465307466</v>
       </c>
       <c r="D6" t="n">
-        <v>34.57617239586842</v>
+        <v>30.06798693796707</v>
       </c>
     </row>
     <row r="7">
@@ -4893,13 +4893,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.462084373530759</v>
+        <v>6.827073535332318</v>
       </c>
       <c r="C7" t="n">
-        <v>24.49362347325367</v>
+        <v>19.22360179685679</v>
       </c>
       <c r="D7" t="n">
-        <v>34.97378021608837</v>
+        <v>30.48228446915921</v>
       </c>
     </row>
     <row r="8">
@@ -4907,13 +4907,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>9.596583809012571</v>
+        <v>6.842781498600267</v>
       </c>
       <c r="C8" t="n">
-        <v>25.61870634232051</v>
+        <v>20.36144738607885</v>
       </c>
       <c r="D8" t="n">
-        <v>36.63391558396972</v>
+        <v>32.96217917008666</v>
       </c>
     </row>
     <row r="9">
@@ -4921,13 +4921,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>9.429686699290611</v>
+        <v>7.09999939711293</v>
       </c>
       <c r="C9" t="n">
-        <v>25.73749781453438</v>
+        <v>20.85624822901923</v>
       </c>
       <c r="D9" t="n">
-        <v>40.27030908049991</v>
+        <v>35.38905949498476</v>
       </c>
     </row>
     <row r="10">
@@ -4935,13 +4935,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8.825911861178826</v>
+        <v>6.8329640215578</v>
       </c>
       <c r="C10" t="n">
-        <v>27.3318560862312</v>
+        <v>22.91890015564179</v>
       </c>
       <c r="D10" t="n">
-        <v>50.1084028247572</v>
+        <v>45.26838664282043</v>
       </c>
     </row>
     <row r="11">
@@ -4949,13 +4949,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>7.640942382152923</v>
+        <v>5.863979037466197</v>
       </c>
       <c r="C11" t="n">
-        <v>29.14219885286231</v>
+        <v>24.87748682561417</v>
       </c>
       <c r="D11" t="n">
-        <v>47.97801030654161</v>
+        <v>43.35790561035613</v>
       </c>
     </row>
     <row r="12">
@@ -4963,13 +4963,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>6.075054793879263</v>
+        <v>4.773257338047991</v>
       </c>
       <c r="C12" t="n">
-        <v>29.29044275620359</v>
+        <v>24.5171854181556</v>
       </c>
       <c r="D12" t="n">
-        <v>44.69504598354028</v>
+        <v>40.57268737340794</v>
       </c>
     </row>
     <row r="13">
@@ -4977,13 +4977,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>5.203262832508096</v>
+        <v>3.902447124381071</v>
       </c>
       <c r="C13" t="n">
-        <v>26.79680358741669</v>
+        <v>22.89435646303562</v>
       </c>
       <c r="D13" t="n">
-        <v>44.74806035956962</v>
+        <v>40.32528695193774</v>
       </c>
     </row>
     <row r="14">
@@ -4991,13 +4991,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.609305471438775</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>25.50482360862789</v>
+        <v>22.43195329433537</v>
       </c>
       <c r="D14" t="n">
-        <v>44.86390658867074</v>
+        <v>41.17646221151972</v>
       </c>
     </row>
     <row r="15">
@@ -5005,13 +5005,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>5.0167307687012</v>
+        <v>3.941717032550943</v>
       </c>
       <c r="C15" t="n">
-        <v>26.51700549170635</v>
+        <v>24.00864010735575</v>
       </c>
       <c r="D15" t="n">
-        <v>43.00054944601029</v>
+        <v>40.1338461496096</v>
       </c>
     </row>
     <row r="16">
@@ -5019,13 +5019,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>5.373105185342793</v>
+        <v>4.546473618366978</v>
       </c>
       <c r="C16" t="n">
-        <v>29.34542062764141</v>
+        <v>26.03889435973815</v>
       </c>
       <c r="D16" t="n">
-        <v>40.5049467818149</v>
+        <v>37.19842051391164</v>
       </c>
     </row>
     <row r="17">
@@ -5033,13 +5033,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>5.66664774891259</v>
+        <v>4.722206457427158</v>
       </c>
       <c r="C17" t="n">
-        <v>31.63878326476196</v>
+        <v>28.80545939030567</v>
       </c>
       <c r="D17" t="n">
-        <v>36.83321036793183</v>
+        <v>34.47210713921825</v>
       </c>
     </row>
     <row r="18">
@@ -5047,13 +5047,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>5.885577486959628</v>
+        <v>5.350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>34.77841242294325</v>
+        <v>31.56809743005619</v>
       </c>
       <c r="D18" t="n">
-        <v>31.56809743005619</v>
+        <v>29.42788743479814</v>
       </c>
     </row>
     <row r="19">
@@ -5061,13 +5061,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>6.619924769736241</v>
+        <v>5.416302084329653</v>
       </c>
       <c r="C19" t="n">
-        <v>36.71049190490098</v>
+        <v>33.09962384868121</v>
       </c>
       <c r="D19" t="n">
-        <v>24.07245370813179</v>
+        <v>22.26701968002191</v>
       </c>
     </row>
     <row r="20">
@@ -5078,10 +5078,10 @@
         <v>6.052474596681584</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>14.79493790299943</v>
+        <v>13.4499435481813</v>
       </c>
     </row>
     <row r="21">
@@ -5089,13 +5089,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>15.43968952312328</v>
+        <v>13.62454509692302</v>
       </c>
       <c r="C21" t="n">
-        <v>86.13721523426673</v>
+        <v>73.73283228923043</v>
       </c>
       <c r="D21" t="n">
-        <v>3.25046095223648</v>
+        <v>1.602887658461531</v>
       </c>
     </row>
   </sheetData>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.987679248201297</v>
+        <v>3.473423377625215</v>
       </c>
       <c r="C2" t="n">
-        <v>3.3703398686793</v>
+        <v>4.98335134675681</v>
       </c>
       <c r="D2" t="n">
-        <v>26.92835777978576</v>
+        <v>18.23105486786327</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.43583922742335</v>
+        <v>12.66945412330509</v>
       </c>
       <c r="C3" t="n">
-        <v>15.0501923061036</v>
+        <v>31.83316931020283</v>
       </c>
       <c r="D3" t="n">
-        <v>50.5256455990621</v>
+        <v>22.83545160078081</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>28.51191682673587</v>
+        <v>19.19513111343364</v>
       </c>
       <c r="C4" t="n">
-        <v>19.33552103514093</v>
+        <v>98.23465703464009</v>
       </c>
       <c r="D4" t="n">
-        <v>35.72285371442869</v>
+        <v>21.22440361811179</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>13.71992416684918</v>
+        <v>8.29576810088555</v>
       </c>
       <c r="C5" t="n">
-        <v>16.73879835740812</v>
+        <v>79.91426312569038</v>
       </c>
       <c r="D5" t="n">
-        <v>30.92505268377453</v>
+        <v>26.70353755551325</v>
       </c>
     </row>
     <row r="6">
@@ -5190,13 +5190,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>5.957245069369646</v>
+        <v>4.508185457901354</v>
       </c>
       <c r="C6" t="n">
-        <v>12.07549676223577</v>
+        <v>10.62643715076748</v>
       </c>
       <c r="D6" t="n">
-        <v>36.54850353370026</v>
+        <v>31.55729820530948</v>
       </c>
     </row>
     <row r="7">
@@ -5204,13 +5204,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.462084373530759</v>
+        <v>7.006733365209485</v>
       </c>
       <c r="C7" t="n">
-        <v>24.49362347325367</v>
+        <v>19.82246789644735</v>
       </c>
       <c r="D7" t="n">
-        <v>37.12969817461437</v>
+        <v>32.81786225756237</v>
       </c>
     </row>
     <row r="8">
@@ -5218,13 +5218,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.43106935762236</v>
+        <v>7.510369937488099</v>
       </c>
       <c r="C8" t="n">
-        <v>29.87458264023044</v>
+        <v>23.61594102565702</v>
       </c>
       <c r="D8" t="n">
-        <v>38.38633523605029</v>
+        <v>34.29735604786232</v>
       </c>
     </row>
     <row r="9">
@@ -5232,13 +5232,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>9.984374152190059</v>
+        <v>7.321874378272709</v>
       </c>
       <c r="C9" t="n">
-        <v>29.7312474754104</v>
+        <v>23.85156047467625</v>
       </c>
       <c r="D9" t="n">
-        <v>41.15780900513902</v>
+        <v>36.0546844384641</v>
       </c>
     </row>
     <row r="10">
@@ -5246,13 +5246,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9.395325529641976</v>
+        <v>7.260024272905163</v>
       </c>
       <c r="C10" t="n">
-        <v>29.60951076008381</v>
+        <v>24.62714116103124</v>
       </c>
       <c r="D10" t="n">
-        <v>49.25428232206248</v>
+        <v>44.69897297435728</v>
       </c>
     </row>
     <row r="11">
@@ -5260,13 +5260,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>8.174031385558941</v>
+        <v>6.397068040872215</v>
       </c>
       <c r="C11" t="n">
-        <v>31.27455486648638</v>
+        <v>26.47675383583222</v>
       </c>
       <c r="D11" t="n">
-        <v>49.75497365122833</v>
+        <v>44.95717262057418</v>
       </c>
     </row>
     <row r="12">
@@ -5274,13 +5274,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>6.725953521794898</v>
+        <v>5.207189823325082</v>
       </c>
       <c r="C12" t="n">
-        <v>31.89403766786613</v>
+        <v>26.90381408717959</v>
       </c>
       <c r="D12" t="n">
-        <v>46.2138096820101</v>
+        <v>41.44055234396211</v>
       </c>
     </row>
     <row r="13">
@@ -5288,13 +5288,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>5.463425974133501</v>
+        <v>4.162610266006476</v>
       </c>
       <c r="C13" t="n">
-        <v>30.17892442854696</v>
+        <v>25.23582473766426</v>
       </c>
       <c r="D13" t="n">
-        <v>45.00822350119503</v>
+        <v>41.10577637681396</v>
       </c>
     </row>
     <row r="14">
@@ -5302,13 +5302,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.609305471438775</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>27.65583282863265</v>
+        <v>24.27567548291088</v>
       </c>
       <c r="D14" t="n">
-        <v>45.47848065152925</v>
+        <v>41.48374924294897</v>
       </c>
     </row>
     <row r="15">
@@ -5316,13 +5316,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4.658392856651115</v>
+        <v>3.583379120500858</v>
       </c>
       <c r="C15" t="n">
-        <v>27.5920192278566</v>
+        <v>24.72531593145592</v>
       </c>
       <c r="D15" t="n">
-        <v>43.00054944601029</v>
+        <v>40.1338461496096</v>
       </c>
     </row>
     <row r="16">
@@ -5330,13 +5330,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>4.959789401854886</v>
+        <v>4.133157834879071</v>
       </c>
       <c r="C16" t="n">
-        <v>29.75873641112932</v>
+        <v>26.45221014322606</v>
       </c>
       <c r="D16" t="n">
-        <v>40.91826256530281</v>
+        <v>37.61173629739955</v>
       </c>
     </row>
     <row r="17">
@@ -5344,13 +5344,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>5.194427103169874</v>
+        <v>4.249985811684442</v>
       </c>
       <c r="C17" t="n">
-        <v>32.11100391050468</v>
+        <v>28.80545939030567</v>
       </c>
       <c r="D17" t="n">
-        <v>37.30543101367455</v>
+        <v>34.94432778496098</v>
       </c>
     </row>
     <row r="18">
@@ -5358,13 +5358,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>5.350524988145117</v>
+        <v>4.815472489330605</v>
       </c>
       <c r="C18" t="n">
-        <v>34.77841242294325</v>
+        <v>31.56809743005619</v>
       </c>
       <c r="D18" t="n">
-        <v>31.56809743005619</v>
+        <v>29.96293993361265</v>
       </c>
     </row>
     <row r="19">
@@ -5372,13 +5372,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>6.018113427032947</v>
+        <v>4.814490741626358</v>
       </c>
       <c r="C19" t="n">
-        <v>36.71049190490098</v>
+        <v>33.7014351913845</v>
       </c>
       <c r="D19" t="n">
-        <v>24.67426505083508</v>
+        <v>22.8688310227252</v>
       </c>
     </row>
     <row r="20">
@@ -5389,10 +5389,10 @@
         <v>5.37997741927252</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>15.46743508040849</v>
+        <v>14.12244072559037</v>
       </c>
     </row>
     <row r="21">
@@ -5400,13 +5400,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>16.73312042259591</v>
+        <v>14.82707574292261</v>
       </c>
       <c r="C21" t="n">
-        <v>102.0720345778351</v>
+        <v>87.31500159721092</v>
       </c>
       <c r="D21" t="n">
-        <v>5.019936126778774</v>
+        <v>2.471179290487101</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.478553100324701</v>
+        <v>2.400373136883451</v>
       </c>
       <c r="C2" t="n">
-        <v>3.634430001121692</v>
+        <v>4.865541622247192</v>
       </c>
       <c r="D2" t="n">
-        <v>31.69081589308704</v>
+        <v>14.1882178217749</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>19.1293540172491</v>
+        <v>12.2816637801276</v>
       </c>
       <c r="C3" t="n">
-        <v>13.90645623065607</v>
+        <v>24.39643045053324</v>
       </c>
       <c r="D3" t="n">
-        <v>59.75407401898212</v>
+        <v>32.1178761444344</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>31.51115606320987</v>
+        <v>22.1305567491316</v>
       </c>
       <c r="C4" t="n">
-        <v>29.37978179729005</v>
+        <v>87.57778570504097</v>
       </c>
       <c r="D4" t="n">
-        <v>51.72730478906019</v>
+        <v>27.89930625928586</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>28.10252803406495</v>
+        <v>18.99681807717579</v>
       </c>
       <c r="C5" t="n">
-        <v>27.16986771503048</v>
+        <v>136.8310862793992</v>
       </c>
       <c r="D5" t="n">
-        <v>36.86462629446773</v>
+        <v>28.44613973055134</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>12.27675504160637</v>
+        <v>8.010079518949729</v>
       </c>
       <c r="C6" t="n">
-        <v>19.76356303419254</v>
+        <v>72.93600044390405</v>
       </c>
       <c r="D6" t="n">
-        <v>38.48058301565798</v>
+        <v>32.92585450502953</v>
       </c>
     </row>
     <row r="7">
@@ -5515,13 +5515,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>8.623671834103982</v>
+        <v>6.407867265618931</v>
       </c>
       <c r="C7" t="n">
-        <v>20.9603134856694</v>
+        <v>17.72643654788041</v>
       </c>
       <c r="D7" t="n">
-        <v>39.22572952318131</v>
+        <v>34.97378021608837</v>
       </c>
     </row>
     <row r="8">
@@ -5529,13 +5529,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.76486357706628</v>
+        <v>7.927612711792993</v>
       </c>
       <c r="C8" t="n">
-        <v>31.87734795689393</v>
+        <v>25.53525778745954</v>
       </c>
       <c r="D8" t="n">
-        <v>40.13875488813084</v>
+        <v>35.79943003535994</v>
       </c>
     </row>
     <row r="9">
@@ -5543,13 +5543,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>10.76093658624928</v>
+        <v>7.876561831172157</v>
       </c>
       <c r="C9" t="n">
-        <v>34.39062207976576</v>
+        <v>27.06874770149305</v>
       </c>
       <c r="D9" t="n">
-        <v>41.82343394861835</v>
+        <v>36.72030938194344</v>
       </c>
     </row>
     <row r="10">
@@ -5557,13 +5557,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9.964739198105127</v>
+        <v>7.402377690020952</v>
       </c>
       <c r="C10" t="n">
-        <v>33.02599277086271</v>
+        <v>27.3318560862312</v>
       </c>
       <c r="D10" t="n">
-        <v>49.25428232206248</v>
+        <v>44.4142661401257</v>
       </c>
     </row>
     <row r="11">
@@ -5571,13 +5571,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>8.884816723433632</v>
+        <v>6.930157044278233</v>
       </c>
       <c r="C11" t="n">
-        <v>33.7623035490478</v>
+        <v>28.25371718051895</v>
       </c>
       <c r="D11" t="n">
-        <v>50.82115165804038</v>
+        <v>46.02335062738621</v>
       </c>
     </row>
     <row r="12">
@@ -5585,13 +5585,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>7.159886007071988</v>
+        <v>5.641122308602172</v>
       </c>
       <c r="C12" t="n">
-        <v>34.49763257952867</v>
+        <v>29.07347651356504</v>
       </c>
       <c r="D12" t="n">
-        <v>47.08167465256428</v>
+        <v>42.30841731451629</v>
       </c>
     </row>
     <row r="13">
@@ -5599,13 +5599,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>5.723589115758904</v>
+        <v>4.422773407631881</v>
       </c>
       <c r="C13" t="n">
-        <v>33.04071898642641</v>
+        <v>27.83745615391831</v>
       </c>
       <c r="D13" t="n">
-        <v>45.78871292607123</v>
+        <v>41.62610266006477</v>
       </c>
     </row>
     <row r="14">
@@ -5613,13 +5613,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.609305471438775</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>30.72870314292517</v>
+        <v>26.11939767148639</v>
       </c>
       <c r="D14" t="n">
-        <v>45.47848065152925</v>
+        <v>41.79103627437823</v>
       </c>
     </row>
     <row r="15">
@@ -5627,13 +5627,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4.30005494460103</v>
+        <v>3.225041208450772</v>
       </c>
       <c r="C15" t="n">
-        <v>29.02537087605695</v>
+        <v>25.80032966760617</v>
       </c>
       <c r="D15" t="n">
-        <v>43.71722527011046</v>
+        <v>40.1338461496096</v>
       </c>
     </row>
     <row r="16">
@@ -5641,13 +5641,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>4.546473618366978</v>
+        <v>3.719842051391165</v>
       </c>
       <c r="C16" t="n">
-        <v>30.17205219461722</v>
+        <v>26.86552592671396</v>
       </c>
       <c r="D16" t="n">
-        <v>41.33157834879071</v>
+        <v>38.02505208088746</v>
       </c>
     </row>
     <row r="17">
@@ -5655,13 +5655,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>4.722206457427158</v>
+        <v>3.777765165941727</v>
       </c>
       <c r="C17" t="n">
-        <v>32.11100391050468</v>
+        <v>28.80545939030567</v>
       </c>
       <c r="D17" t="n">
-        <v>37.30543101367455</v>
+        <v>34.94432778496098</v>
       </c>
     </row>
     <row r="18">
@@ -5669,13 +5669,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>4.815472489330605</v>
+        <v>4.280419990516093</v>
       </c>
       <c r="C18" t="n">
-        <v>34.77841242294325</v>
+        <v>31.56809743005619</v>
       </c>
       <c r="D18" t="n">
-        <v>32.1031499288707</v>
+        <v>30.49799243242716</v>
       </c>
     </row>
     <row r="19">
@@ -5683,13 +5683,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>5.416302084329653</v>
+        <v>4.212679398923063</v>
       </c>
       <c r="C19" t="n">
-        <v>37.31230324760427</v>
+        <v>33.7014351913845</v>
       </c>
       <c r="D19" t="n">
-        <v>24.67426505083508</v>
+        <v>23.47064236542849</v>
       </c>
     </row>
     <row r="20">
@@ -5700,10 +5700,10 @@
         <v>4.707480241863455</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>16.13993225781756</v>
+        <v>14.79493790299943</v>
       </c>
     </row>
     <row r="21">
@@ -5711,13 +5711,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>18.06145476456269</v>
+        <v>16.05577597736903</v>
       </c>
       <c r="C21" t="n">
-        <v>117.829490606909</v>
+        <v>100.559860068785</v>
       </c>
       <c r="D21" t="n">
-        <v>6.880554196023881</v>
+        <v>3.380163363656639</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7.868707849538185</v>
+        <v>1.921280257211008</v>
       </c>
       <c r="C2" t="n">
-        <v>3.346777923777377</v>
+        <v>7.302239424187775</v>
       </c>
       <c r="D2" t="n">
-        <v>25.79934791990193</v>
+        <v>12.49764827506189</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.68756755033803</v>
+        <v>10.07273144557228</v>
       </c>
       <c r="C3" t="n">
-        <v>13.19959788359837</v>
+        <v>21.27938148954962</v>
       </c>
       <c r="D3" t="n">
-        <v>66.37105354560562</v>
+        <v>35.49508824704343</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>25.37228766855457</v>
+        <v>22.79421819720244</v>
       </c>
       <c r="C4" t="n">
-        <v>27.2101193709046</v>
+        <v>72.39014872034281</v>
       </c>
       <c r="D4" t="n">
-        <v>59.83163208761761</v>
+        <v>36.38651516249953</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>23.16924582022473</v>
+        <v>26.11448893296516</v>
       </c>
       <c r="C5" t="n">
-        <v>31.21957699504858</v>
+        <v>150.0355929015188</v>
       </c>
       <c r="D5" t="n">
-        <v>38.23907308041327</v>
+        <v>31.93134408062751</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>13.92707293244525</v>
+        <v>16.42267559664065</v>
       </c>
       <c r="C6" t="n">
-        <v>21.61513920440203</v>
+        <v>146.3147691024234</v>
       </c>
       <c r="D6" t="n">
-        <v>31.83905979642831</v>
+        <v>34.37491411649783</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>5.809001166028376</v>
+        <v>8.084692344472483</v>
       </c>
       <c r="C7" t="n">
-        <v>16.10949807898591</v>
+        <v>61.26400198811371</v>
       </c>
       <c r="D7" t="n">
-        <v>31.02126395879071</v>
+        <v>36.9500383447372</v>
       </c>
     </row>
     <row r="8">
@@ -5840,13 +5840,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.840016181936775</v>
+        <v>7.677267047210056</v>
       </c>
       <c r="C8" t="n">
-        <v>18.44213062427633</v>
+        <v>24.86766934857171</v>
       </c>
       <c r="D8" t="n">
-        <v>30.12492830481337</v>
+        <v>37.38495257771854</v>
       </c>
     </row>
     <row r="9">
@@ -5854,13 +5854,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4.881249585515139</v>
+        <v>8.320311793491715</v>
       </c>
       <c r="C9" t="n">
-        <v>22.2984356065578</v>
+        <v>30.06405994715006</v>
       </c>
       <c r="D9" t="n">
-        <v>29.84218496599028</v>
+        <v>37.49687181600267</v>
       </c>
     </row>
     <row r="10">
@@ -5868,13 +5868,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.270602513473626</v>
+        <v>7.687084524252525</v>
       </c>
       <c r="C10" t="n">
-        <v>21.49536598448391</v>
+        <v>30.46363126277853</v>
       </c>
       <c r="D10" t="n">
-        <v>33.73775985644164</v>
+        <v>44.27191272300992</v>
       </c>
     </row>
     <row r="11">
@@ -5882,13 +5882,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>3.731623023842126</v>
+        <v>7.107853378746905</v>
       </c>
       <c r="C11" t="n">
-        <v>20.25738212942868</v>
+        <v>30.56376952861169</v>
       </c>
       <c r="D11" t="n">
-        <v>34.47308888692249</v>
+        <v>46.37874329632356</v>
       </c>
     </row>
     <row r="12">
@@ -5896,13 +5896,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.037527396939631</v>
+        <v>6.075054793879263</v>
       </c>
       <c r="C12" t="n">
-        <v>20.17786056538469</v>
+        <v>31.02617269731195</v>
       </c>
       <c r="D12" t="n">
-        <v>32.11100391050467</v>
+        <v>43.61021477034756</v>
       </c>
     </row>
     <row r="13">
@@ -5910,13 +5910,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.341468274628643</v>
+        <v>4.682936549257286</v>
       </c>
       <c r="C13" t="n">
-        <v>18.99190933865455</v>
+        <v>29.91876128692155</v>
       </c>
       <c r="D13" t="n">
-        <v>30.17892442854696</v>
+        <v>42.14642894331557</v>
       </c>
     </row>
     <row r="14">
@@ -5924,13 +5924,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.536435157146258</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>17.51536079146734</v>
+        <v>28.27040689149115</v>
       </c>
       <c r="D14" t="n">
-        <v>29.80684204863741</v>
+        <v>41.79103627437823</v>
       </c>
     </row>
     <row r="15">
@@ -5938,13 +5938,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.433351648200343</v>
+        <v>3.225041208450772</v>
       </c>
       <c r="C15" t="n">
-        <v>16.12520604225386</v>
+        <v>27.23368131580652</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>40.49218406165969</v>
       </c>
     </row>
     <row r="16">
@@ -5952,13 +5952,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>3.306526267903257</v>
       </c>
       <c r="C16" t="n">
-        <v>15.70599977254047</v>
+        <v>27.69215749368978</v>
       </c>
       <c r="D16" t="n">
-        <v>26.03889435973815</v>
+        <v>38.43836786437537</v>
       </c>
     </row>
     <row r="17">
@@ -5966,13 +5966,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>1.416661937228147</v>
+        <v>3.305544520199011</v>
       </c>
       <c r="C17" t="n">
-        <v>16.52772260099505</v>
+        <v>28.80545939030567</v>
       </c>
       <c r="D17" t="n">
-        <v>23.61103228713579</v>
+        <v>34.94432778496098</v>
       </c>
     </row>
     <row r="18">
@@ -5980,13 +5980,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1.605157496443535</v>
+        <v>3.745367491701582</v>
       </c>
       <c r="C18" t="n">
-        <v>17.65673246087889</v>
+        <v>31.56809743005619</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>31.03304493124168</v>
       </c>
     </row>
     <row r="19">
@@ -5994,13 +5994,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1.203622685406589</v>
+        <v>3.610868056219768</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>33.7014351913845</v>
       </c>
       <c r="D19" t="n">
-        <v>15.64709491028566</v>
+        <v>23.47064236542849</v>
       </c>
     </row>
     <row r="20">
@@ -6008,13 +6008,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>1.34499435481813</v>
+        <v>4.03498306445439</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>10.08745766113597</v>
+        <v>15.46743508040849</v>
       </c>
     </row>
     <row r="21">
@@ -6022,13 +6022,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.061060765604214</v>
+        <v>17.30553548269331</v>
       </c>
       <c r="C21" t="n">
-        <v>66.19744467753951</v>
+        <v>113.3512574116412</v>
       </c>
       <c r="D21" t="n">
-        <v>5.295795574203161</v>
+        <v>4.326383870673327</v>
       </c>
     </row>
   </sheetData>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.87616092054466</v>
+        <v>3.091523520673206</v>
       </c>
       <c r="C2" t="n">
-        <v>7.013605599139213</v>
+        <v>12.696943059024</v>
       </c>
       <c r="D2" t="n">
-        <v>26.5032610238469</v>
+        <v>17.21690948937631</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>24.47497026687298</v>
+        <v>8.202502068982101</v>
       </c>
       <c r="C3" t="n">
-        <v>13.12596680577985</v>
+        <v>24.90203051822035</v>
       </c>
       <c r="D3" t="n">
-        <v>72.39898444968104</v>
+        <v>36.77626900108552</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>32.31520743298801</v>
+        <v>20.82875929330033</v>
       </c>
       <c r="C4" t="n">
-        <v>31.00064725700153</v>
+        <v>62.52456604036662</v>
       </c>
       <c r="D4" t="n">
-        <v>81.82179891504191</v>
+        <v>44.04414725562465</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>32.29949946972007</v>
+        <v>30.01693605734623</v>
       </c>
       <c r="C5" t="n">
-        <v>43.12326790904115</v>
+        <v>141.8134558784518</v>
       </c>
       <c r="D5" t="n">
-        <v>52.54804586981054</v>
+        <v>37.15915060574178</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>24.11074186859742</v>
+        <v>24.83527167433157</v>
       </c>
       <c r="C6" t="n">
-        <v>38.15856976866503</v>
+        <v>188.4180011467521</v>
       </c>
       <c r="D6" t="n">
-        <v>36.99127174831558</v>
+        <v>36.30699359845555</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>12.21686843164731</v>
+        <v>13.23494080095125</v>
       </c>
       <c r="C7" t="n">
-        <v>25.33203601268044</v>
+        <v>131.750541909922</v>
       </c>
       <c r="D7" t="n">
-        <v>33.89582123682538</v>
+        <v>38.74663664350886</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5.9248473951295</v>
+        <v>8.428304040958867</v>
       </c>
       <c r="C8" t="n">
-        <v>20.61179305066178</v>
+        <v>50.65327280061418</v>
       </c>
       <c r="D8" t="n">
-        <v>32.21114217633784</v>
+        <v>39.05392367493811</v>
       </c>
     </row>
     <row r="9">
@@ -6165,13 +6165,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.103124566674919</v>
+        <v>8.320311793491715</v>
       </c>
       <c r="C9" t="n">
-        <v>23.40781051235669</v>
+        <v>31.28437234352885</v>
       </c>
       <c r="D9" t="n">
-        <v>30.95155987178918</v>
+        <v>38.38437174064178</v>
       </c>
     </row>
     <row r="10">
@@ -6179,13 +6179,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.697662764820988</v>
+        <v>8.114144775599888</v>
       </c>
       <c r="C10" t="n">
-        <v>25.0542014123786</v>
+        <v>33.59540643932586</v>
       </c>
       <c r="D10" t="n">
-        <v>34.16482010778901</v>
+        <v>44.27191272300992</v>
       </c>
     </row>
     <row r="11">
@@ -6193,13 +6193,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.08701569277947</v>
+        <v>7.285549713215578</v>
       </c>
       <c r="C11" t="n">
-        <v>23.45591614986479</v>
+        <v>33.05151821117311</v>
       </c>
       <c r="D11" t="n">
-        <v>35.36157055926586</v>
+        <v>46.55643963079223</v>
       </c>
     </row>
     <row r="12">
@@ -6207,13 +6207,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.254493639578176</v>
+        <v>6.292021036517808</v>
       </c>
       <c r="C12" t="n">
-        <v>22.34752299177014</v>
+        <v>33.1958351236974</v>
       </c>
       <c r="D12" t="n">
-        <v>32.97886888105885</v>
+        <v>44.69504598354028</v>
       </c>
     </row>
     <row r="13">
@@ -6221,13 +6221,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.601631416254048</v>
+        <v>4.943099690882691</v>
       </c>
       <c r="C13" t="n">
-        <v>21.33337761328319</v>
+        <v>32.26022956155019</v>
       </c>
       <c r="D13" t="n">
-        <v>30.95941385342317</v>
+        <v>42.40659208494097</v>
       </c>
     </row>
     <row r="14">
@@ -6235,13 +6235,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>19.66637001147211</v>
+        <v>30.11412908006666</v>
       </c>
       <c r="D14" t="n">
-        <v>30.11412908006666</v>
+        <v>42.09832330580748</v>
       </c>
     </row>
     <row r="15">
@@ -6249,13 +6249,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.433351648200343</v>
+        <v>3.225041208450772</v>
       </c>
       <c r="C15" t="n">
-        <v>17.91689560250429</v>
+        <v>29.02537087605695</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>40.85052197370977</v>
       </c>
     </row>
     <row r="16">
@@ -6263,13 +6263,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>2.89321048441535</v>
       </c>
       <c r="C16" t="n">
-        <v>16.53263133951629</v>
+        <v>28.51878906066559</v>
       </c>
       <c r="D16" t="n">
-        <v>26.45221014322606</v>
+        <v>38.43836786437537</v>
       </c>
     </row>
     <row r="17">
@@ -6277,13 +6277,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>2.833323874456295</v>
       </c>
       <c r="C17" t="n">
-        <v>16.99994324673777</v>
+        <v>29.27768003604838</v>
       </c>
       <c r="D17" t="n">
-        <v>24.0832529328785</v>
+        <v>35.41654843070368</v>
       </c>
     </row>
     <row r="18">
@@ -6291,13 +6291,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1.070104997629023</v>
+        <v>3.21031499288707</v>
       </c>
       <c r="C18" t="n">
-        <v>17.65673246087889</v>
+        <v>31.56809743005619</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>31.03304493124168</v>
       </c>
     </row>
     <row r="19">
@@ -6305,13 +6305,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1.203622685406589</v>
+        <v>3.009056713516474</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>33.7014351913845</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>24.07245370813179</v>
       </c>
     </row>
     <row r="20">
@@ -6319,13 +6319,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>0.672497177409065</v>
+        <v>3.362485887045325</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>35.64235040268044</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>16.13993225781756</v>
       </c>
     </row>
     <row r="21">
@@ -6333,13 +6333,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.287092513710725</v>
+        <v>17.68643551316699</v>
       </c>
       <c r="C21" t="n">
-        <v>76.51447139396262</v>
+        <v>126.458013919144</v>
       </c>
       <c r="D21" t="n">
-        <v>6.376205949496884</v>
+        <v>5.305930653950099</v>
       </c>
     </row>
   </sheetData>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.892449720889356</v>
+        <v>2.766565030567512</v>
       </c>
       <c r="C2" t="n">
-        <v>5.579272203234622</v>
+        <v>8.12592574805085</v>
       </c>
       <c r="D2" t="n">
-        <v>31.28437234352886</v>
+        <v>13.70912494210246</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>24.1755372170777</v>
+        <v>12.34547738090364</v>
       </c>
       <c r="C3" t="n">
-        <v>21.8684301120977</v>
+        <v>42.60294162579034</v>
       </c>
       <c r="D3" t="n">
-        <v>76.80212290322798</v>
+        <v>40.50200153870216</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>41.14700978039232</v>
+        <v>14.42187377538565</v>
       </c>
       <c r="C4" t="n">
-        <v>32.1492920709703</v>
+        <v>108.5979858006694</v>
       </c>
       <c r="D4" t="n">
-        <v>98.97489480364219</v>
+        <v>42.57643443777567</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>41.74882112309562</v>
+        <v>13.98990478551705</v>
       </c>
       <c r="C5" t="n">
-        <v>50.97724954301564</v>
+        <v>112.581917984503</v>
       </c>
       <c r="D5" t="n">
-        <v>71.05399009486291</v>
+        <v>32.37313054753858</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>35.01894061048373</v>
+        <v>8.211337798320324</v>
       </c>
       <c r="C6" t="n">
-        <v>55.50703345041042</v>
+        <v>86.78257006460107</v>
       </c>
       <c r="D6" t="n">
-        <v>45.08185457901354</v>
+        <v>25.51954982419159</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>21.55917958525995</v>
+        <v>5.569454726192155</v>
       </c>
       <c r="C7" t="n">
-        <v>42.22006002113408</v>
+        <v>35.57264631567892</v>
       </c>
       <c r="D7" t="n">
-        <v>37.42913122440964</v>
+        <v>27.42806736124739</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.01382658331747</v>
+        <v>5.757950285407543</v>
       </c>
       <c r="C8" t="n">
-        <v>28.20561154301086</v>
+        <v>23.03180114163017</v>
       </c>
       <c r="D8" t="n">
-        <v>34.46425315758427</v>
+        <v>28.28906009787184</v>
       </c>
     </row>
     <row r="9">
@@ -6479,10 +6479,10 @@
         <v>5.768749510154256</v>
       </c>
       <c r="C9" t="n">
-        <v>25.07187287105504</v>
+        <v>25.62656032395449</v>
       </c>
       <c r="D9" t="n">
-        <v>32.28280975874785</v>
+        <v>33.72499713628642</v>
       </c>
     </row>
     <row r="10">
@@ -6490,13 +6490,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>5.124723016168351</v>
+        <v>5.267076433284139</v>
       </c>
       <c r="C10" t="n">
-        <v>27.47420950334699</v>
+        <v>25.90832191507333</v>
       </c>
       <c r="D10" t="n">
-        <v>34.73423377625215</v>
+        <v>36.44247478164161</v>
       </c>
     </row>
     <row r="11">
@@ -6504,13 +6504,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.442408361716816</v>
+        <v>4.620104696185489</v>
       </c>
       <c r="C11" t="n">
-        <v>27.00984283923824</v>
+        <v>26.47675383583222</v>
       </c>
       <c r="D11" t="n">
-        <v>36.07235589714055</v>
+        <v>35.7169632282032</v>
       </c>
     </row>
     <row r="12">
@@ -6518,13 +6518,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.471459882216721</v>
+        <v>3.688426124855267</v>
       </c>
       <c r="C12" t="n">
-        <v>25.16808414607123</v>
+        <v>26.25291535926396</v>
       </c>
       <c r="D12" t="n">
-        <v>33.62976760897449</v>
+        <v>34.49763257952867</v>
       </c>
     </row>
     <row r="13">
@@ -6532,13 +6532,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.601631416254048</v>
+        <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
-        <v>23.67484588791184</v>
+        <v>24.97566159603886</v>
       </c>
       <c r="D13" t="n">
-        <v>31.73990327829938</v>
+        <v>34.86186097780424</v>
       </c>
     </row>
     <row r="14">
@@ -6546,13 +6546,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>2.458296251434013</v>
       </c>
       <c r="C14" t="n">
-        <v>21.81737923147687</v>
+        <v>24.27567548291088</v>
       </c>
       <c r="D14" t="n">
-        <v>30.11412908006666</v>
+        <v>34.10886048864694</v>
       </c>
     </row>
     <row r="15">
@@ -6560,13 +6560,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.433351648200343</v>
+        <v>2.150027472300515</v>
       </c>
       <c r="C15" t="n">
-        <v>19.35024725070463</v>
+        <v>24.00864010735575</v>
       </c>
       <c r="D15" t="n">
-        <v>28.66703296400686</v>
+        <v>32.6087499965578</v>
       </c>
     </row>
     <row r="16">
@@ -6574,13 +6574,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>2.066578917439536</v>
       </c>
       <c r="C16" t="n">
-        <v>17.77257868998001</v>
+        <v>24.79894700927443</v>
       </c>
       <c r="D16" t="n">
-        <v>26.86552592671396</v>
+        <v>30.17205219461722</v>
       </c>
     </row>
     <row r="17">
@@ -6588,13 +6588,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>2.361103228713579</v>
       </c>
       <c r="C17" t="n">
-        <v>17.47216389248049</v>
+        <v>26.9165768073348</v>
       </c>
       <c r="D17" t="n">
-        <v>24.0832529328785</v>
+        <v>26.44435616159209</v>
       </c>
     </row>
     <row r="18">
@@ -6602,10 +6602,10 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>0.5350524988145117</v>
+        <v>2.140209995258047</v>
       </c>
       <c r="C18" t="n">
-        <v>18.1917849596934</v>
+        <v>28.89283493598363</v>
       </c>
       <c r="D18" t="n">
         <v>20.86704745376595</v>
@@ -6616,13 +6616,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>0.6018113427032947</v>
+        <v>2.407245370813179</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>30.69237847786803</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>13.84166088217578</v>
       </c>
     </row>
     <row r="20">
@@ -6630,13 +6630,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>0.672497177409065</v>
+        <v>13.4499435481813</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>96.16709636949629</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>4.03498306445439</v>
       </c>
     </row>
     <row r="21">
@@ -6644,13 +6644,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.50235094051005</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>86.27703581586557</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>7.50235094051005</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
